--- a/colored_dataset.xlsx
+++ b/colored_dataset.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="121">
+  <fills count="105">
     <fill>
       <patternFill/>
     </fill>
@@ -38,597 +38,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00662FB8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005493A2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0083569A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00805596"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007989BF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B89C3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007670AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007472AB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0063718C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0061718A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006131B8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006230B5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005D43C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005E40C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005C35AB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005D35B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008627B1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008427B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006134AB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005F36AF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00493C81"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004E3E8D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005F4DBA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005C4CB6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004E539D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004E519C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008036AE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008235AF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00574A99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0059489B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00727B9A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00717A96"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0072A6C3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006AA0B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005C7F80"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005D8284"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009074A2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009175A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005E8182"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005F8182"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0047444E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0049444B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D439A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00704182"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0056618A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00546383"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00953798"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00963799"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00546388"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00536186"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005E6596"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00526580"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B7EC9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007580C6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005E648B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00556E86"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008D4C9B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0087549A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00557685"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0055707F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F1F1C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F1F1B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004D3EA7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00473897"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004E4597"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00504198"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00752EAA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00712FA7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0049479D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0048489B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00507084"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00516E85"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D99DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00869BE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004C808B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004C7D87"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00746593"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0072648F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00557684"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00547A87"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000D730F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000D6F0F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0069AFA7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0062A799"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003D9F74"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003E9F75"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00748D7F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006F8875"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004B956E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F9571"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0062434F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00614147"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009C398F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009E3890"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008B4184"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A4284"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7237D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BD2281"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070597B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F5B9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A5692"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006E7FAB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006D7BA6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00646C7B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00636B78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C6692"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0078678C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005A7680"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0058767B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0084439C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B4588"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008580D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008482D2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006D5888"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006E588B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007E62A4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008061A4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006A5881"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0068597E"/>
+        <fgColor rgb="008791FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C82FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009094FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008F95FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A80FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B7EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A8AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008393FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008394FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00878EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008482FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008483FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008491FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009394FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009295FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008594FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008591FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007BA1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D9DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008489FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008389FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B91FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C93FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009194FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F97FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008097FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00898EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008890FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00857EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008383FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008095FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008193FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009291FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00928FFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008194FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DABFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DADFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008D9AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0089A1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F95FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E98FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00959EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E97FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008292FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A81FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008881FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008296FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008093FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009397FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009195FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E92FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006DB0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006CB0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D98FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C99FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D99FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B9AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A9AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B94FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A95FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B95FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008877FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A75FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00798CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00798EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008896FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008897FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D94FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C91FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0068ABFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006AACFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008388FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00818CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00738DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00879AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007995FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085ACFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085AFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0097A0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0098A0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092A0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A1A9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A4AAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00899EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008D96FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008C99FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008689FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00868BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008499FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00849BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B97FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A98FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F96FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009197FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008D9DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008C80FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008C7FFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008998FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008997FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B93FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008C93FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00889BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00879CFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -650,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -758,22 +678,6 @@
     <xf numFmtId="0" fontId="0" fillId="102" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="103" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="104" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="105" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="106" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="110" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="111" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="112" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="113" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="114" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="115" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="116" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="118" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="119" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="120" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1501,40 +1405,40 @@
       <c r="A9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>0.47</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>1220</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="8" t="n">
         <v>5.34</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="8" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1542,40 +1446,40 @@
       <c r="A10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.47</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>1260</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="9" t="n">
         <v>620</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.24</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" s="9" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="9" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1583,40 +1487,40 @@
       <c r="A11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>11.9</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <v>12.9</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="10" t="n">
         <v>1260</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="10" t="n">
         <v>620</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="10" t="n">
         <v>1.95</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="10" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="10" t="n">
         <v>21.5</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="10" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1624,40 +1528,40 @@
       <c r="A12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.87</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>1250</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>620</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="11" t="n">
         <v>4.55</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="J12" s="11" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="K12" s="11" t="n">
         <v>60.5</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="11" t="n">
         <v>121</v>
       </c>
     </row>
@@ -1665,40 +1569,40 @@
       <c r="A13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="2" t="n">
         <v>10.4</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="2" t="n">
         <v>0.87</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="2" t="n">
         <v>13.8</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="2" t="n">
         <v>8.1</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="2" t="n">
         <v>1220</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="I13" s="2" t="n">
         <v>4.47</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="J13" s="2" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="K13" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="L13" s="13" t="n">
+      <c r="L13" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="M13" s="13" t="n">
+      <c r="M13" s="2" t="n">
         <v>121</v>
       </c>
     </row>
@@ -1706,40 +1610,40 @@
       <c r="A14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="12" t="n">
         <v>10.4</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="12" t="n">
         <v>0.87</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="12" t="n">
         <v>13.2</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="12" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="12" t="n">
         <v>1460</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="12" t="n">
         <v>5.81</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="12" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="12" t="n">
         <v>51.1</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="12" t="n">
         <v>204</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="12" t="n">
         <v>129</v>
       </c>
     </row>
@@ -1747,40 +1651,40 @@
       <c r="A15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="13" t="n">
         <v>10.4</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="13" t="n">
         <v>0.87</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="13" t="n">
         <v>13.2</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="13" t="n">
         <v>1410</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>700</v>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="13" t="n">
         <v>56</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="13" t="n">
         <v>5.77</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="13" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K15" s="15" t="n">
+      <c r="K15" s="13" t="n">
         <v>55.8</v>
       </c>
-      <c r="L15" s="15" t="n">
+      <c r="L15" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="M15" s="15" t="n">
+      <c r="M15" s="13" t="n">
         <v>133</v>
       </c>
     </row>
@@ -1788,40 +1692,40 @@
       <c r="A16" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="10" t="n">
         <v>0.87</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="10" t="n">
         <v>14.4</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="10" t="n">
         <v>8.1</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="10" t="n">
         <v>1280</v>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="10" t="n">
         <v>630</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="I16" s="16" t="n">
+      <c r="I16" s="10" t="n">
         <v>2.66</v>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="10" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K16" s="16" t="n">
+      <c r="K16" s="10" t="n">
         <v>56.8</v>
       </c>
-      <c r="L16" s="16" t="n">
+      <c r="L16" s="10" t="n">
         <v>130</v>
       </c>
-      <c r="M16" s="16" t="n">
+      <c r="M16" s="10" t="n">
         <v>109</v>
       </c>
     </row>
@@ -1829,40 +1733,40 @@
       <c r="A17" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="14" t="n">
         <v>10.4</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="14" t="n">
         <v>0.87</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="14" t="n">
         <v>14.1</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="14" t="n">
         <v>8.1</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="14" t="n">
         <v>1290</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="14" t="n">
         <v>640</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="14" t="n">
         <v>3.38</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="14" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="14" t="n">
         <v>52.8</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="14" t="n">
         <v>122</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="14" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1870,40 +1774,40 @@
       <c r="A18" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>10.4</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="15" t="n">
         <v>14.6</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="15" t="n">
         <v>930</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="15" t="n">
         <v>460</v>
       </c>
-      <c r="H18" s="18" t="n">
+      <c r="H18" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="18" t="n">
+      <c r="I18" s="15" t="n">
         <v>5.88</v>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="15" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K18" s="18" t="n">
+      <c r="K18" s="15" t="n">
         <v>5.16</v>
       </c>
-      <c r="L18" s="18" t="n">
+      <c r="L18" s="15" t="n">
         <v>204</v>
       </c>
-      <c r="M18" s="18" t="n">
+      <c r="M18" s="15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -1911,40 +1815,40 @@
       <c r="A19" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="16" t="n">
         <v>0.87</v>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="16" t="n">
         <v>14.8</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="16" t="n">
         <v>940</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="16" t="n">
         <v>460</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="16" t="n">
         <v>6.02</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="16" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K19" s="19" t="n">
+      <c r="K19" s="16" t="n">
         <v>127</v>
       </c>
-      <c r="L19" s="19" t="n">
+      <c r="L19" s="16" t="n">
         <v>208</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="M19" s="16" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1952,40 +1856,40 @@
       <c r="A20" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B20" s="20" t="n">
+      <c r="B20" s="17" t="n">
         <v>10.4</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="17" t="n">
         <v>0.87</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="17" t="n">
         <v>14.3</v>
       </c>
-      <c r="E20" s="20" t="n">
+      <c r="E20" s="17" t="n">
         <v>8.1</v>
       </c>
-      <c r="F20" s="20" t="n">
+      <c r="F20" s="17" t="n">
         <v>1230</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="17" t="n">
         <v>610</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I20" s="17" t="n">
         <v>2.93</v>
       </c>
-      <c r="J20" s="20" t="n">
+      <c r="J20" s="17" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="K20" s="17" t="n">
         <v>57.9</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L20" s="17" t="n">
         <v>159</v>
       </c>
-      <c r="M20" s="20" t="n">
+      <c r="M20" s="17" t="n">
         <v>102</v>
       </c>
     </row>
@@ -1993,40 +1897,40 @@
       <c r="A21" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="18" t="n">
         <v>10.4</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="18" t="n">
         <v>0.87</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="18" t="n">
         <v>14.4</v>
       </c>
-      <c r="E21" s="21" t="n">
+      <c r="E21" s="18" t="n">
         <v>8.1</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="18" t="n">
         <v>1290</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="18" t="n">
         <v>640</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="18" t="n">
         <v>3.48</v>
       </c>
-      <c r="J21" s="21" t="n">
+      <c r="J21" s="18" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K21" s="21" t="n">
+      <c r="K21" s="18" t="n">
         <v>53.9</v>
       </c>
-      <c r="L21" s="21" t="n">
+      <c r="L21" s="18" t="n">
         <v>163</v>
       </c>
-      <c r="M21" s="21" t="n">
+      <c r="M21" s="18" t="n">
         <v>102</v>
       </c>
     </row>
@@ -2034,40 +1938,40 @@
       <c r="A22" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>18.2</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="19" t="n">
         <v>0.77</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="19" t="n">
         <v>15.3</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="19" t="n">
         <v>7.8</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="19" t="n">
         <v>1280</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="19" t="n">
         <v>630</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="19" t="n">
         <v>2.03</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="19" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="K22" s="19" t="n">
         <v>622</v>
       </c>
-      <c r="L22" s="22" t="n">
+      <c r="L22" s="19" t="n">
         <v>106</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="19" t="n">
         <v>128</v>
       </c>
     </row>
@@ -2075,40 +1979,40 @@
       <c r="A23" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="20" t="n">
         <v>18.2</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="20" t="n">
         <v>0.77</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="20" t="n">
         <v>15.3</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="20" t="n">
         <v>1290</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="20" t="n">
         <v>630</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="20" t="n">
         <v>1.94</v>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J23" s="20" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="20" t="n">
         <v>397</v>
       </c>
-      <c r="L23" s="23" t="n">
+      <c r="L23" s="20" t="n">
         <v>106</v>
       </c>
-      <c r="M23" s="23" t="n">
+      <c r="M23" s="20" t="n">
         <v>126</v>
       </c>
     </row>
@@ -2116,40 +2020,40 @@
       <c r="A24" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="21" t="n">
         <v>18.2</v>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="21" t="n">
         <v>0.77</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="21" t="n">
         <v>15.2</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="21" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="21" t="n">
         <v>1370</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="21" t="n">
         <v>680</v>
       </c>
-      <c r="H24" s="24" t="n">
+      <c r="H24" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="I24" s="24" t="n">
+      <c r="I24" s="21" t="n">
         <v>5.07</v>
       </c>
-      <c r="J24" s="24" t="n">
+      <c r="J24" s="21" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K24" s="24" t="n">
+      <c r="K24" s="21" t="n">
         <v>55.1</v>
       </c>
-      <c r="L24" s="24" t="n">
+      <c r="L24" s="21" t="n">
         <v>179</v>
       </c>
-      <c r="M24" s="24" t="n">
+      <c r="M24" s="21" t="n">
         <v>124</v>
       </c>
     </row>
@@ -2157,40 +2061,40 @@
       <c r="A25" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="22" t="n">
         <v>18.2</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="22" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="22" t="n">
         <v>15.1</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="22" t="n">
         <v>8.4</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="22" t="n">
         <v>1400</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="22" t="n">
         <v>680</v>
       </c>
-      <c r="H25" s="25" t="n">
+      <c r="H25" s="22" t="n">
         <v>28</v>
       </c>
-      <c r="I25" s="25" t="n">
+      <c r="I25" s="22" t="n">
         <v>4.51</v>
       </c>
-      <c r="J25" s="25" t="n">
+      <c r="J25" s="22" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K25" s="25" t="n">
+      <c r="K25" s="22" t="n">
         <v>46.7</v>
       </c>
-      <c r="L25" s="25" t="n">
+      <c r="L25" s="22" t="n">
         <v>167</v>
       </c>
-      <c r="M25" s="25" t="n">
+      <c r="M25" s="22" t="n">
         <v>126</v>
       </c>
     </row>
@@ -2198,40 +2102,40 @@
       <c r="A26" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="23" t="n">
         <v>18.2</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="23" t="n">
         <v>0.77</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="23" t="n">
         <v>15.4</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="23" t="n">
         <v>1480</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="23" t="n">
         <v>700</v>
       </c>
-      <c r="H26" s="26" t="n">
+      <c r="H26" s="23" t="n">
         <v>36</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="23" t="n">
         <v>1.57</v>
       </c>
-      <c r="J26" s="26" t="n">
+      <c r="J26" s="23" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K26" s="26" t="n">
+      <c r="K26" s="23" t="n">
         <v>58.7</v>
       </c>
-      <c r="L26" s="26" t="n">
+      <c r="L26" s="23" t="n">
         <v>151</v>
       </c>
-      <c r="M26" s="26" t="n">
+      <c r="M26" s="23" t="n">
         <v>128</v>
       </c>
     </row>
@@ -2239,40 +2143,40 @@
       <c r="A27" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="24" t="n">
         <v>18.2</v>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="24" t="n">
         <v>0.77</v>
       </c>
-      <c r="D27" s="27" t="n">
+      <c r="D27" s="24" t="n">
         <v>15.2</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="24" t="n">
         <v>1430</v>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="24" t="n">
         <v>710</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="24" t="n">
         <v>36</v>
       </c>
-      <c r="I27" s="27" t="n">
+      <c r="I27" s="24" t="n">
         <v>1.52</v>
       </c>
-      <c r="J27" s="27" t="n">
+      <c r="J27" s="24" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K27" s="27" t="n">
+      <c r="K27" s="24" t="n">
         <v>78.3</v>
       </c>
-      <c r="L27" s="27" t="n">
+      <c r="L27" s="24" t="n">
         <v>147</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="24" t="n">
         <v>130</v>
       </c>
     </row>
@@ -2280,40 +2184,40 @@
       <c r="A28" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="4" t="n">
         <v>0.77</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="4" t="n">
         <v>15.2</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E28" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="4" t="n">
         <v>990</v>
       </c>
-      <c r="G28" s="28" t="n">
+      <c r="G28" s="4" t="n">
         <v>490</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="4" t="n">
         <v>5.3</v>
       </c>
-      <c r="J28" s="28" t="n">
+      <c r="J28" s="4" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K28" s="28" t="n">
+      <c r="K28" s="4" t="n">
         <v>2.68</v>
       </c>
-      <c r="L28" s="28" t="n">
+      <c r="L28" s="4" t="n">
         <v>212</v>
       </c>
-      <c r="M28" s="28" t="n">
+      <c r="M28" s="4" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2321,40 +2225,40 @@
       <c r="A29" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="25" t="n">
         <v>18.2</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>0.77</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>970</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="25" t="n">
         <v>480</v>
       </c>
-      <c r="H29" s="29" t="n">
+      <c r="H29" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" s="29" t="n">
+      <c r="I29" s="25" t="n">
         <v>5.53</v>
       </c>
-      <c r="J29" s="29" t="n">
+      <c r="J29" s="25" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K29" s="29" t="n">
+      <c r="K29" s="25" t="n">
         <v>3.4</v>
       </c>
-      <c r="L29" s="29" t="n">
+      <c r="L29" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="M29" s="29" t="n">
+      <c r="M29" s="25" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2362,40 +2266,40 @@
       <c r="A30" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>18.2</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>0.77</v>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="D30" s="26" t="n">
         <v>15.4</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E30" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="26" t="n">
         <v>1330</v>
       </c>
-      <c r="G30" s="30" t="n">
+      <c r="G30" s="26" t="n">
         <v>660</v>
       </c>
-      <c r="H30" s="30" t="n">
+      <c r="H30" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="I30" s="30" t="n">
+      <c r="I30" s="26" t="n">
         <v>1.8</v>
       </c>
-      <c r="J30" s="30" t="n">
+      <c r="J30" s="26" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K30" s="30" t="n">
+      <c r="K30" s="26" t="n">
         <v>88.5</v>
       </c>
-      <c r="L30" s="30" t="n">
+      <c r="L30" s="26" t="n">
         <v>155</v>
       </c>
-      <c r="M30" s="30" t="n">
+      <c r="M30" s="26" t="n">
         <v>105</v>
       </c>
     </row>
@@ -2403,40 +2307,40 @@
       <c r="A31" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="27" t="n">
         <v>18.2</v>
       </c>
-      <c r="C31" s="31" t="n">
+      <c r="C31" s="27" t="n">
         <v>0.77</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="27" t="n">
         <v>15.5</v>
       </c>
-      <c r="E31" s="31" t="n">
+      <c r="E31" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F31" s="31" t="n">
+      <c r="F31" s="27" t="n">
         <v>1290</v>
       </c>
-      <c r="G31" s="31" t="n">
+      <c r="G31" s="27" t="n">
         <v>640</v>
       </c>
-      <c r="H31" s="31" t="n">
+      <c r="H31" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="I31" s="31" t="n">
+      <c r="I31" s="27" t="n">
         <v>1.83</v>
       </c>
-      <c r="J31" s="31" t="n">
+      <c r="J31" s="27" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K31" s="31" t="n">
+      <c r="K31" s="27" t="n">
         <v>59.8</v>
       </c>
-      <c r="L31" s="31" t="n">
+      <c r="L31" s="27" t="n">
         <v>163</v>
       </c>
-      <c r="M31" s="31" t="n">
+      <c r="M31" s="27" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2444,40 +2348,40 @@
       <c r="A32" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="28" t="n">
         <v>14.4</v>
       </c>
-      <c r="C32" s="32" t="n">
+      <c r="C32" s="28" t="n">
         <v>0.4</v>
       </c>
-      <c r="D32" s="32" t="n">
+      <c r="D32" s="28" t="n">
         <v>15.6</v>
       </c>
-      <c r="E32" s="32" t="n">
+      <c r="E32" s="28" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F32" s="32" t="n">
+      <c r="F32" s="28" t="n">
         <v>1240</v>
       </c>
-      <c r="G32" s="32" t="n">
+      <c r="G32" s="28" t="n">
         <v>610</v>
       </c>
-      <c r="H32" s="32" t="n">
+      <c r="H32" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="I32" s="32" t="n">
+      <c r="I32" s="28" t="n">
         <v>4.59</v>
       </c>
-      <c r="J32" s="32" t="n">
+      <c r="J32" s="28" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K32" s="32" t="n">
+      <c r="K32" s="28" t="n">
         <v>40.8</v>
       </c>
-      <c r="L32" s="32" t="n">
+      <c r="L32" s="28" t="n">
         <v>110</v>
       </c>
-      <c r="M32" s="32" t="n">
+      <c r="M32" s="28" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2485,40 +2389,40 @@
       <c r="A33" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B33" s="33" t="n">
+      <c r="B33" s="29" t="n">
         <v>14.4</v>
       </c>
-      <c r="C33" s="33" t="n">
+      <c r="C33" s="29" t="n">
         <v>0.4</v>
       </c>
-      <c r="D33" s="33" t="n">
+      <c r="D33" s="29" t="n">
         <v>16.1</v>
       </c>
-      <c r="E33" s="33" t="n">
+      <c r="E33" s="29" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F33" s="33" t="n">
+      <c r="F33" s="29" t="n">
         <v>1240</v>
       </c>
-      <c r="G33" s="33" t="n">
+      <c r="G33" s="29" t="n">
         <v>610</v>
       </c>
-      <c r="H33" s="33" t="n">
+      <c r="H33" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="I33" s="33" t="n">
+      <c r="I33" s="29" t="n">
         <v>4.32</v>
       </c>
-      <c r="J33" s="33" t="n">
+      <c r="J33" s="29" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K33" s="33" t="n">
+      <c r="K33" s="29" t="n">
         <v>44.8</v>
       </c>
-      <c r="L33" s="33" t="n">
+      <c r="L33" s="29" t="n">
         <v>106</v>
       </c>
-      <c r="M33" s="33" t="n">
+      <c r="M33" s="29" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2526,40 +2430,40 @@
       <c r="A34" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B34" s="34" t="n">
+      <c r="B34" s="30" t="n">
         <v>14.4</v>
       </c>
-      <c r="C34" s="34" t="n">
+      <c r="C34" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D34" s="30" t="n">
         <v>17.1</v>
       </c>
-      <c r="E34" s="34" t="n">
+      <c r="E34" s="30" t="n">
         <v>8.5</v>
       </c>
-      <c r="F34" s="34" t="n">
+      <c r="F34" s="30" t="n">
         <v>1480</v>
       </c>
-      <c r="G34" s="34" t="n">
+      <c r="G34" s="30" t="n">
         <v>730</v>
       </c>
-      <c r="H34" s="34" t="n">
+      <c r="H34" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="I34" s="34" t="n">
+      <c r="I34" s="30" t="n">
         <v>7.65</v>
       </c>
-      <c r="J34" s="34" t="n">
+      <c r="J34" s="30" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K34" s="34" t="n">
+      <c r="K34" s="30" t="n">
         <v>247</v>
       </c>
-      <c r="L34" s="34" t="n">
+      <c r="L34" s="30" t="n">
         <v>179</v>
       </c>
-      <c r="M34" s="34" t="n">
+      <c r="M34" s="30" t="n">
         <v>141</v>
       </c>
     </row>
@@ -2567,40 +2471,40 @@
       <c r="A35" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B35" s="35" t="n">
+      <c r="B35" s="31" t="n">
         <v>14.4</v>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="31" t="n">
         <v>16.9</v>
       </c>
-      <c r="E35" s="35" t="n">
+      <c r="E35" s="31" t="n">
         <v>8.4</v>
       </c>
-      <c r="F35" s="35" t="n">
+      <c r="F35" s="31" t="n">
         <v>1470</v>
       </c>
-      <c r="G35" s="35" t="n">
+      <c r="G35" s="31" t="n">
         <v>730</v>
       </c>
-      <c r="H35" s="35" t="n">
+      <c r="H35" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="I35" s="35" t="n">
+      <c r="I35" s="31" t="n">
         <v>7.05</v>
       </c>
-      <c r="J35" s="35" t="n">
+      <c r="J35" s="31" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K35" s="35" t="n">
+      <c r="K35" s="31" t="n">
         <v>362</v>
       </c>
-      <c r="L35" s="35" t="n">
+      <c r="L35" s="31" t="n">
         <v>188</v>
       </c>
-      <c r="M35" s="35" t="n">
+      <c r="M35" s="31" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2608,40 +2512,40 @@
       <c r="A36" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B36" s="36" t="n">
+      <c r="B36" s="32" t="n">
         <v>14.4</v>
       </c>
-      <c r="C36" s="36" t="n">
+      <c r="C36" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="D36" s="36" t="n">
+      <c r="D36" s="32" t="n">
         <v>16.6</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="32" t="n">
         <v>8.1</v>
       </c>
-      <c r="F36" s="36" t="n">
+      <c r="F36" s="32" t="n">
         <v>1310</v>
       </c>
-      <c r="G36" s="36" t="n">
+      <c r="G36" s="32" t="n">
         <v>650</v>
       </c>
-      <c r="H36" s="36" t="n">
+      <c r="H36" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="I36" s="36" t="n">
+      <c r="I36" s="32" t="n">
         <v>1.68</v>
       </c>
-      <c r="J36" s="36" t="n">
+      <c r="J36" s="32" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K36" s="36" t="n">
+      <c r="K36" s="32" t="n">
         <v>91.5</v>
       </c>
-      <c r="L36" s="36" t="n">
+      <c r="L36" s="32" t="n">
         <v>135</v>
       </c>
-      <c r="M36" s="36" t="n">
+      <c r="M36" s="32" t="n">
         <v>116</v>
       </c>
     </row>
@@ -2649,40 +2553,40 @@
       <c r="A37" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="33" t="n">
         <v>14.4</v>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C37" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="D37" s="37" t="n">
+      <c r="D37" s="33" t="n">
         <v>16.6</v>
       </c>
-      <c r="E37" s="37" t="n">
+      <c r="E37" s="33" t="n">
         <v>8.1</v>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F37" s="33" t="n">
         <v>1360</v>
       </c>
-      <c r="G37" s="37" t="n">
+      <c r="G37" s="33" t="n">
         <v>670</v>
       </c>
-      <c r="H37" s="37" t="n">
+      <c r="H37" s="33" t="n">
         <v>46</v>
       </c>
-      <c r="I37" s="37" t="n">
+      <c r="I37" s="33" t="n">
         <v>2.4</v>
       </c>
-      <c r="J37" s="37" t="n">
+      <c r="J37" s="33" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K37" s="37" t="n">
+      <c r="K37" s="33" t="n">
         <v>133</v>
       </c>
-      <c r="L37" s="37" t="n">
+      <c r="L37" s="33" t="n">
         <v>135</v>
       </c>
-      <c r="M37" s="37" t="n">
+      <c r="M37" s="33" t="n">
         <v>114</v>
       </c>
     </row>
@@ -2690,40 +2594,40 @@
       <c r="A38" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="38" t="n">
+      <c r="B38" s="34" t="n">
         <v>14.4</v>
       </c>
-      <c r="C38" s="38" t="n">
+      <c r="C38" s="34" t="n">
         <v>0.4</v>
       </c>
-      <c r="D38" s="38" t="n">
+      <c r="D38" s="34" t="n">
         <v>16.8</v>
       </c>
-      <c r="E38" s="38" t="n">
+      <c r="E38" s="34" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F38" s="38" t="n">
+      <c r="F38" s="34" t="n">
         <v>990</v>
       </c>
-      <c r="G38" s="38" t="n">
+      <c r="G38" s="34" t="n">
         <v>490</v>
       </c>
-      <c r="H38" s="38" t="n">
+      <c r="H38" s="34" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" s="38" t="n">
+      <c r="I38" s="34" t="n">
         <v>5.89</v>
       </c>
-      <c r="J38" s="38" t="n">
+      <c r="J38" s="34" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K38" s="38" t="n">
+      <c r="K38" s="34" t="n">
         <v>2.77</v>
       </c>
-      <c r="L38" s="38" t="n">
+      <c r="L38" s="34" t="n">
         <v>212</v>
       </c>
-      <c r="M38" s="38" t="n">
+      <c r="M38" s="34" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2731,40 +2635,40 @@
       <c r="A39" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="39" t="n">
+      <c r="B39" s="35" t="n">
         <v>14.4</v>
       </c>
-      <c r="C39" s="39" t="n">
+      <c r="C39" s="35" t="n">
         <v>0.4</v>
       </c>
-      <c r="D39" s="39" t="n">
+      <c r="D39" s="35" t="n">
         <v>16.8</v>
       </c>
-      <c r="E39" s="39" t="n">
+      <c r="E39" s="35" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F39" s="39" t="n">
+      <c r="F39" s="35" t="n">
         <v>1000</v>
       </c>
-      <c r="G39" s="39" t="n">
+      <c r="G39" s="35" t="n">
         <v>490</v>
       </c>
-      <c r="H39" s="39" t="n">
+      <c r="H39" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="I39" s="39" t="n">
+      <c r="I39" s="35" t="n">
         <v>6.14</v>
       </c>
-      <c r="J39" s="39" t="n">
+      <c r="J39" s="35" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K39" s="39" t="n">
+      <c r="K39" s="35" t="n">
         <v>3.59</v>
       </c>
-      <c r="L39" s="39" t="n">
+      <c r="L39" s="35" t="n">
         <v>204</v>
       </c>
-      <c r="M39" s="39" t="n">
+      <c r="M39" s="35" t="n">
         <v>66</v>
       </c>
     </row>
@@ -2772,40 +2676,40 @@
       <c r="A40" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="40" t="n">
+      <c r="B40" s="33" t="n">
         <v>14.4</v>
       </c>
-      <c r="C40" s="40" t="n">
+      <c r="C40" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="D40" s="40" t="n">
+      <c r="D40" s="33" t="n">
         <v>17.9</v>
       </c>
-      <c r="E40" s="40" t="n">
+      <c r="E40" s="33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F40" s="40" t="n">
+      <c r="F40" s="33" t="n">
         <v>1340</v>
       </c>
-      <c r="G40" s="40" t="n">
+      <c r="G40" s="33" t="n">
         <v>660</v>
       </c>
-      <c r="H40" s="40" t="n">
+      <c r="H40" s="33" t="n">
         <v>32</v>
       </c>
-      <c r="I40" s="40" t="n">
+      <c r="I40" s="33" t="n">
         <v>1.76</v>
       </c>
-      <c r="J40" s="40" t="n">
+      <c r="J40" s="33" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K40" s="40" t="n">
+      <c r="K40" s="33" t="n">
         <v>48.6</v>
       </c>
-      <c r="L40" s="40" t="n">
+      <c r="L40" s="33" t="n">
         <v>147</v>
       </c>
-      <c r="M40" s="40" t="n">
+      <c r="M40" s="33" t="n">
         <v>109</v>
       </c>
     </row>
@@ -2813,40 +2717,40 @@
       <c r="A41" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B41" s="41" t="n">
+      <c r="B41" s="36" t="n">
         <v>14.4</v>
       </c>
-      <c r="C41" s="41" t="n">
+      <c r="C41" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="D41" s="41" t="n">
+      <c r="D41" s="36" t="n">
         <v>16.7</v>
       </c>
-      <c r="E41" s="41" t="n">
+      <c r="E41" s="36" t="n">
         <v>8.1</v>
       </c>
-      <c r="F41" s="41" t="n">
+      <c r="F41" s="36" t="n">
         <v>1330</v>
       </c>
-      <c r="G41" s="41" t="n">
+      <c r="G41" s="36" t="n">
         <v>660</v>
       </c>
-      <c r="H41" s="41" t="n">
+      <c r="H41" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="I41" s="41" t="n">
+      <c r="I41" s="36" t="n">
         <v>1.75</v>
       </c>
-      <c r="J41" s="41" t="n">
+      <c r="J41" s="36" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K41" s="41" t="n">
+      <c r="K41" s="36" t="n">
         <v>47</v>
       </c>
-      <c r="L41" s="41" t="n">
+      <c r="L41" s="36" t="n">
         <v>151</v>
       </c>
-      <c r="M41" s="41" t="n">
+      <c r="M41" s="36" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2854,40 +2758,40 @@
       <c r="A42" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="42" t="n">
+      <c r="B42" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="C42" s="42" t="n">
+      <c r="C42" s="37" t="n">
         <v>0.6</v>
       </c>
-      <c r="D42" s="42" t="n">
+      <c r="D42" s="37" t="n">
         <v>17.75</v>
       </c>
-      <c r="E42" s="42" t="n">
+      <c r="E42" s="37" t="n">
         <v>7.9</v>
       </c>
-      <c r="F42" s="42" t="n">
+      <c r="F42" s="37" t="n">
         <v>1210</v>
       </c>
-      <c r="G42" s="42" t="n">
+      <c r="G42" s="37" t="n">
         <v>600</v>
       </c>
-      <c r="H42" s="42" t="n">
+      <c r="H42" s="37" t="n">
         <v>92</v>
       </c>
-      <c r="I42" s="42" t="n">
+      <c r="I42" s="37" t="n">
         <v>1.79</v>
       </c>
-      <c r="J42" s="42" t="n">
+      <c r="J42" s="37" t="n">
         <v>27.5</v>
       </c>
-      <c r="K42" s="42" t="n">
+      <c r="K42" s="37" t="n">
         <v>1000</v>
       </c>
-      <c r="L42" s="42" t="n">
+      <c r="L42" s="37" t="n">
         <v>114</v>
       </c>
-      <c r="M42" s="42" t="n">
+      <c r="M42" s="37" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2895,40 +2799,40 @@
       <c r="A43" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="43" t="n">
+      <c r="B43" s="38" t="n">
         <v>18</v>
       </c>
-      <c r="C43" s="43" t="n">
+      <c r="C43" s="38" t="n">
         <v>0.6</v>
       </c>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="38" t="n">
         <v>18.05</v>
       </c>
-      <c r="E43" s="43" t="n">
+      <c r="E43" s="38" t="n">
         <v>7.7</v>
       </c>
-      <c r="F43" s="43" t="n">
+      <c r="F43" s="38" t="n">
         <v>1170</v>
       </c>
-      <c r="G43" s="43" t="n">
+      <c r="G43" s="38" t="n">
         <v>580</v>
       </c>
-      <c r="H43" s="43" t="n">
+      <c r="H43" s="38" t="n">
         <v>92</v>
       </c>
-      <c r="I43" s="43" t="n">
+      <c r="I43" s="38" t="n">
         <v>1.35</v>
       </c>
-      <c r="J43" s="43" t="n">
+      <c r="J43" s="38" t="n">
         <v>27.5</v>
       </c>
-      <c r="K43" s="43" t="n">
+      <c r="K43" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="L43" s="43" t="n">
+      <c r="L43" s="38" t="n">
         <v>114</v>
       </c>
-      <c r="M43" s="43" t="n">
+      <c r="M43" s="38" t="n">
         <v>95</v>
       </c>
     </row>
@@ -2936,40 +2840,40 @@
       <c r="A44" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="44" t="n">
+      <c r="B44" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="C44" s="44" t="n">
+      <c r="C44" s="39" t="n">
         <v>0.6</v>
       </c>
-      <c r="D44" s="44" t="n">
+      <c r="D44" s="39" t="n">
         <v>18.15</v>
       </c>
-      <c r="E44" s="44" t="n">
+      <c r="E44" s="39" t="n">
         <v>8.1</v>
       </c>
-      <c r="F44" s="44" t="n">
+      <c r="F44" s="39" t="n">
         <v>1000</v>
       </c>
-      <c r="G44" s="44" t="n">
+      <c r="G44" s="39" t="n">
         <v>490</v>
       </c>
-      <c r="H44" s="44" t="n">
+      <c r="H44" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="I44" s="44" t="n">
+      <c r="I44" s="39" t="n">
         <v>4.97</v>
       </c>
-      <c r="J44" s="44" t="n">
+      <c r="J44" s="39" t="n">
         <v>27.5</v>
       </c>
-      <c r="K44" s="44" t="n">
+      <c r="K44" s="39" t="n">
         <v>238</v>
       </c>
-      <c r="L44" s="44" t="n">
+      <c r="L44" s="39" t="n">
         <v>135</v>
       </c>
-      <c r="M44" s="44" t="n">
+      <c r="M44" s="39" t="n">
         <v>79</v>
       </c>
     </row>
@@ -2977,40 +2881,40 @@
       <c r="A45" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B45" s="45" t="n">
+      <c r="B45" s="40" t="n">
         <v>18</v>
       </c>
-      <c r="C45" s="45" t="n">
+      <c r="C45" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="D45" s="45" t="n">
+      <c r="D45" s="40" t="n">
         <v>18.15</v>
       </c>
-      <c r="E45" s="45" t="n">
+      <c r="E45" s="40" t="n">
         <v>8.1</v>
       </c>
-      <c r="F45" s="45" t="n">
+      <c r="F45" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="G45" s="45" t="n">
+      <c r="G45" s="40" t="n">
         <v>490</v>
       </c>
-      <c r="H45" s="45" t="n">
+      <c r="H45" s="40" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="45" t="n">
+      <c r="I45" s="40" t="n">
         <v>3.12</v>
       </c>
-      <c r="J45" s="45" t="n">
+      <c r="J45" s="40" t="n">
         <v>27.5</v>
       </c>
-      <c r="K45" s="45" t="n">
+      <c r="K45" s="40" t="n">
         <v>351</v>
       </c>
-      <c r="L45" s="45" t="n">
+      <c r="L45" s="40" t="n">
         <v>139</v>
       </c>
-      <c r="M45" s="45" t="n">
+      <c r="M45" s="40" t="n">
         <v>81</v>
       </c>
     </row>
@@ -3018,40 +2922,40 @@
       <c r="A46" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B46" s="46" t="n">
+      <c r="B46" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C46" s="46" t="n">
+      <c r="C46" s="41" t="n">
         <v>0.6</v>
       </c>
-      <c r="D46" s="46" t="n">
+      <c r="D46" s="41" t="n">
         <v>18.2</v>
       </c>
-      <c r="E46" s="46" t="n">
+      <c r="E46" s="41" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F46" s="46" t="n">
+      <c r="F46" s="41" t="n">
         <v>1310</v>
       </c>
-      <c r="G46" s="46" t="n">
+      <c r="G46" s="41" t="n">
         <v>640</v>
       </c>
-      <c r="H46" s="46" t="n">
+      <c r="H46" s="41" t="n">
         <v>64</v>
       </c>
-      <c r="I46" s="46" t="n">
+      <c r="I46" s="41" t="n">
         <v>1.71</v>
       </c>
-      <c r="J46" s="46" t="n">
+      <c r="J46" s="41" t="n">
         <v>47.5</v>
       </c>
-      <c r="K46" s="46" t="n">
+      <c r="K46" s="41" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="L46" s="46" t="n">
+      <c r="L46" s="41" t="n">
         <v>135</v>
       </c>
-      <c r="M46" s="46" t="n">
+      <c r="M46" s="41" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3059,40 +2963,40 @@
       <c r="A47" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="47" t="n">
+      <c r="B47" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C47" s="47" t="n">
+      <c r="C47" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="D47" s="47" t="n">
+      <c r="D47" s="42" t="n">
         <v>18.1</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="42" t="n">
         <v>8.1</v>
       </c>
-      <c r="F47" s="47" t="n">
+      <c r="F47" s="42" t="n">
         <v>1320</v>
       </c>
-      <c r="G47" s="47" t="n">
+      <c r="G47" s="42" t="n">
         <v>650</v>
       </c>
-      <c r="H47" s="47" t="n">
+      <c r="H47" s="42" t="n">
         <v>64</v>
       </c>
-      <c r="I47" s="47" t="n">
+      <c r="I47" s="42" t="n">
         <v>0.97</v>
       </c>
-      <c r="J47" s="47" t="n">
+      <c r="J47" s="42" t="n">
         <v>47.5</v>
       </c>
-      <c r="K47" s="47" t="n">
+      <c r="K47" s="42" t="n">
         <v>109</v>
       </c>
-      <c r="L47" s="47" t="n">
+      <c r="L47" s="42" t="n">
         <v>130</v>
       </c>
-      <c r="M47" s="47" t="n">
+      <c r="M47" s="42" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3100,40 +3004,40 @@
       <c r="A48" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="48" t="n">
+      <c r="B48" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="C48" s="48" t="n">
+      <c r="C48" s="43" t="n">
         <v>0.6</v>
       </c>
-      <c r="D48" s="48" t="n">
+      <c r="D48" s="43" t="n">
         <v>18.4</v>
       </c>
-      <c r="E48" s="48" t="n">
+      <c r="E48" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="48" t="n">
+      <c r="F48" s="43" t="n">
         <v>750</v>
       </c>
-      <c r="G48" s="48" t="n">
+      <c r="G48" s="43" t="n">
         <v>370</v>
       </c>
-      <c r="H48" s="48" t="n">
+      <c r="H48" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="I48" s="48" t="n">
+      <c r="I48" s="43" t="n">
         <v>4.65</v>
       </c>
-      <c r="J48" s="48" t="n">
+      <c r="J48" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="48" t="n">
+      <c r="K48" s="43" t="n">
         <v>11.6</v>
       </c>
-      <c r="L48" s="48" t="n">
+      <c r="L48" s="43" t="n">
         <v>155</v>
       </c>
-      <c r="M48" s="48" t="n">
+      <c r="M48" s="43" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3141,40 +3045,40 @@
       <c r="A49" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B49" s="49" t="n">
+      <c r="B49" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="C49" s="49" t="n">
+      <c r="C49" s="43" t="n">
         <v>0.6</v>
       </c>
-      <c r="D49" s="49" t="n">
+      <c r="D49" s="43" t="n">
         <v>18.35</v>
       </c>
-      <c r="E49" s="49" t="n">
+      <c r="E49" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="F49" s="49" t="n">
+      <c r="F49" s="43" t="n">
         <v>750</v>
       </c>
-      <c r="G49" s="49" t="n">
+      <c r="G49" s="43" t="n">
         <v>370</v>
       </c>
-      <c r="H49" s="49" t="n">
+      <c r="H49" s="43" t="n">
         <v>26</v>
       </c>
-      <c r="I49" s="49" t="n">
+      <c r="I49" s="43" t="n">
         <v>4.84</v>
       </c>
-      <c r="J49" s="49" t="n">
+      <c r="J49" s="43" t="n">
         <v>25</v>
       </c>
-      <c r="K49" s="49" t="n">
+      <c r="K49" s="43" t="n">
         <v>13.5</v>
       </c>
-      <c r="L49" s="49" t="n">
+      <c r="L49" s="43" t="n">
         <v>159</v>
       </c>
-      <c r="M49" s="49" t="n">
+      <c r="M49" s="43" t="n">
         <v>48</v>
       </c>
     </row>
@@ -3182,40 +3086,40 @@
       <c r="A50" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B50" s="50" t="n">
+      <c r="B50" s="44" t="n">
         <v>18</v>
       </c>
-      <c r="C50" s="50" t="n">
+      <c r="C50" s="44" t="n">
         <v>0.6</v>
       </c>
-      <c r="D50" s="50" t="n">
+      <c r="D50" s="44" t="n">
         <v>18.35</v>
       </c>
-      <c r="E50" s="50" t="n">
+      <c r="E50" s="44" t="n">
         <v>8.1</v>
       </c>
-      <c r="F50" s="50" t="n">
+      <c r="F50" s="44" t="n">
         <v>1350</v>
       </c>
-      <c r="G50" s="50" t="n">
+      <c r="G50" s="44" t="n">
         <v>670</v>
       </c>
-      <c r="H50" s="50" t="n">
+      <c r="H50" s="44" t="n">
         <v>56</v>
       </c>
-      <c r="I50" s="50" t="n">
+      <c r="I50" s="44" t="n">
         <v>1.29</v>
       </c>
-      <c r="J50" s="50" t="n">
+      <c r="J50" s="44" t="n">
         <v>35</v>
       </c>
-      <c r="K50" s="50" t="n">
+      <c r="K50" s="44" t="n">
         <v>93.8</v>
       </c>
-      <c r="L50" s="50" t="n">
+      <c r="L50" s="44" t="n">
         <v>143</v>
       </c>
-      <c r="M50" s="50" t="n">
+      <c r="M50" s="44" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3223,40 +3127,40 @@
       <c r="A51" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="51" t="n">
+      <c r="B51" s="44" t="n">
         <v>18</v>
       </c>
-      <c r="C51" s="51" t="n">
+      <c r="C51" s="44" t="n">
         <v>0.6</v>
       </c>
-      <c r="D51" s="51" t="n">
+      <c r="D51" s="44" t="n">
         <v>18.4</v>
       </c>
-      <c r="E51" s="51" t="n">
+      <c r="E51" s="44" t="n">
         <v>8.1</v>
       </c>
-      <c r="F51" s="51" t="n">
+      <c r="F51" s="44" t="n">
         <v>1340</v>
       </c>
-      <c r="G51" s="51" t="n">
+      <c r="G51" s="44" t="n">
         <v>660</v>
       </c>
-      <c r="H51" s="51" t="n">
+      <c r="H51" s="44" t="n">
         <v>56</v>
       </c>
-      <c r="I51" s="51" t="n">
+      <c r="I51" s="44" t="n">
         <v>1.45</v>
       </c>
-      <c r="J51" s="51" t="n">
+      <c r="J51" s="44" t="n">
         <v>35</v>
       </c>
-      <c r="K51" s="51" t="n">
+      <c r="K51" s="44" t="n">
         <v>159</v>
       </c>
-      <c r="L51" s="51" t="n">
+      <c r="L51" s="44" t="n">
         <v>147</v>
       </c>
-      <c r="M51" s="51" t="n">
+      <c r="M51" s="44" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3264,40 +3168,40 @@
       <c r="A52" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B52" s="52" t="n">
+      <c r="B52" s="45" t="n">
         <v>14.3</v>
       </c>
-      <c r="C52" s="52" t="n">
+      <c r="C52" s="45" t="n">
         <v>0.54</v>
       </c>
-      <c r="D52" s="52" t="n">
+      <c r="D52" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="E52" s="52" t="n">
+      <c r="E52" s="45" t="n">
         <v>8.1</v>
       </c>
-      <c r="F52" s="52" t="n">
+      <c r="F52" s="45" t="n">
         <v>1370</v>
       </c>
-      <c r="G52" s="52" t="n">
+      <c r="G52" s="45" t="n">
         <v>680</v>
       </c>
-      <c r="H52" s="52" t="n">
+      <c r="H52" s="45" t="n">
         <v>56</v>
       </c>
-      <c r="I52" s="52" t="n">
+      <c r="I52" s="45" t="n">
         <v>3.6</v>
       </c>
-      <c r="J52" s="52" t="n">
+      <c r="J52" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="K52" s="52" t="n">
+      <c r="K52" s="45" t="n">
         <v>199</v>
       </c>
-      <c r="L52" s="52" t="n">
+      <c r="L52" s="45" t="n">
         <v>106</v>
       </c>
-      <c r="M52" s="52" t="n">
+      <c r="M52" s="45" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3305,40 +3209,40 @@
       <c r="A53" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B53" s="53" t="n">
+      <c r="B53" s="44" t="n">
         <v>14.3</v>
       </c>
-      <c r="C53" s="53" t="n">
+      <c r="C53" s="44" t="n">
         <v>0.54</v>
       </c>
-      <c r="D53" s="53" t="n">
+      <c r="D53" s="44" t="n">
         <v>25.5</v>
       </c>
-      <c r="E53" s="53" t="n">
+      <c r="E53" s="44" t="n">
         <v>8.1</v>
       </c>
-      <c r="F53" s="53" t="n">
+      <c r="F53" s="44" t="n">
         <v>1400</v>
       </c>
-      <c r="G53" s="53" t="n">
+      <c r="G53" s="44" t="n">
         <v>690</v>
       </c>
-      <c r="H53" s="53" t="n">
+      <c r="H53" s="44" t="n">
         <v>56</v>
       </c>
-      <c r="I53" s="53" t="n">
+      <c r="I53" s="44" t="n">
         <v>1.87</v>
       </c>
-      <c r="J53" s="53" t="n">
+      <c r="J53" s="44" t="n">
         <v>25</v>
       </c>
-      <c r="K53" s="53" t="n">
+      <c r="K53" s="44" t="n">
         <v>220</v>
       </c>
-      <c r="L53" s="53" t="n">
+      <c r="L53" s="44" t="n">
         <v>110</v>
       </c>
-      <c r="M53" s="53" t="n">
+      <c r="M53" s="44" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3346,40 +3250,40 @@
       <c r="A54" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B54" s="54" t="n">
+      <c r="B54" s="46" t="n">
         <v>14.3</v>
       </c>
-      <c r="C54" s="54" t="n">
+      <c r="C54" s="46" t="n">
         <v>0.54</v>
       </c>
-      <c r="D54" s="54" t="n">
+      <c r="D54" s="46" t="n">
         <v>23.6</v>
       </c>
-      <c r="E54" s="54" t="n">
+      <c r="E54" s="46" t="n">
         <v>8.4</v>
       </c>
-      <c r="F54" s="54" t="n">
+      <c r="F54" s="46" t="n">
         <v>1330</v>
       </c>
-      <c r="G54" s="54" t="n">
+      <c r="G54" s="46" t="n">
         <v>660</v>
       </c>
-      <c r="H54" s="54" t="n">
+      <c r="H54" s="46" t="n">
         <v>68.32649572649574</v>
       </c>
-      <c r="I54" s="54" t="n">
+      <c r="I54" s="46" t="n">
         <v>7.48</v>
       </c>
-      <c r="J54" s="54" t="n">
+      <c r="J54" s="46" t="n">
         <v>35</v>
       </c>
-      <c r="K54" s="54" t="n">
+      <c r="K54" s="46" t="n">
         <v>39.9</v>
       </c>
-      <c r="L54" s="54" t="n">
+      <c r="L54" s="46" t="n">
         <v>179</v>
       </c>
-      <c r="M54" s="54" t="n">
+      <c r="M54" s="46" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3387,40 +3291,40 @@
       <c r="A55" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B55" s="55" t="n">
+      <c r="B55" s="47" t="n">
         <v>14.3</v>
       </c>
-      <c r="C55" s="55" t="n">
+      <c r="C55" s="47" t="n">
         <v>0.54</v>
       </c>
-      <c r="D55" s="55" t="n">
+      <c r="D55" s="47" t="n">
         <v>24.3</v>
       </c>
-      <c r="E55" s="55" t="n">
+      <c r="E55" s="47" t="n">
         <v>8.4</v>
       </c>
-      <c r="F55" s="55" t="n">
+      <c r="F55" s="47" t="n">
         <v>1390</v>
       </c>
-      <c r="G55" s="55" t="n">
+      <c r="G55" s="47" t="n">
         <v>690</v>
       </c>
-      <c r="H55" s="55" t="n">
+      <c r="H55" s="47" t="n">
         <v>68.32649572649574</v>
       </c>
-      <c r="I55" s="55" t="n">
+      <c r="I55" s="47" t="n">
         <v>7.15</v>
       </c>
-      <c r="J55" s="55" t="n">
+      <c r="J55" s="47" t="n">
         <v>35</v>
       </c>
-      <c r="K55" s="55" t="n">
+      <c r="K55" s="47" t="n">
         <v>49.9</v>
       </c>
-      <c r="L55" s="55" t="n">
+      <c r="L55" s="47" t="n">
         <v>175</v>
       </c>
-      <c r="M55" s="55" t="n">
+      <c r="M55" s="47" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3428,40 +3332,40 @@
       <c r="A56" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="48" t="n">
         <v>14.3</v>
       </c>
-      <c r="C56" s="56" t="n">
+      <c r="C56" s="48" t="n">
         <v>0.54</v>
       </c>
-      <c r="D56" s="56" t="n">
+      <c r="D56" s="48" t="n">
         <v>16.1</v>
       </c>
-      <c r="E56" s="56" t="n">
+      <c r="E56" s="48" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F56" s="56" t="n">
+      <c r="F56" s="48" t="n">
         <v>1220</v>
       </c>
-      <c r="G56" s="56" t="n">
+      <c r="G56" s="48" t="n">
         <v>600</v>
       </c>
-      <c r="H56" s="56" t="n">
+      <c r="H56" s="48" t="n">
         <v>76</v>
       </c>
-      <c r="I56" s="56" t="n">
+      <c r="I56" s="48" t="n">
         <v>2.27</v>
       </c>
-      <c r="J56" s="56" t="n">
+      <c r="J56" s="48" t="n">
         <v>47.5</v>
       </c>
-      <c r="K56" s="56" t="n">
+      <c r="K56" s="48" t="n">
         <v>114</v>
       </c>
-      <c r="L56" s="56" t="n">
+      <c r="L56" s="48" t="n">
         <v>155</v>
       </c>
-      <c r="M56" s="56" t="n">
+      <c r="M56" s="48" t="n">
         <v>114</v>
       </c>
     </row>
@@ -3469,40 +3373,40 @@
       <c r="A57" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B57" s="57" t="n">
+      <c r="B57" s="49" t="n">
         <v>14.3</v>
       </c>
-      <c r="C57" s="57" t="n">
+      <c r="C57" s="49" t="n">
         <v>0.54</v>
       </c>
-      <c r="D57" s="57" t="n">
+      <c r="D57" s="49" t="n">
         <v>28.1</v>
       </c>
-      <c r="E57" s="57" t="n">
+      <c r="E57" s="49" t="n">
         <v>8.1</v>
       </c>
-      <c r="F57" s="57" t="n">
+      <c r="F57" s="49" t="n">
         <v>1360</v>
       </c>
-      <c r="G57" s="57" t="n">
+      <c r="G57" s="49" t="n">
         <v>670</v>
       </c>
-      <c r="H57" s="57" t="n">
+      <c r="H57" s="49" t="n">
         <v>76</v>
       </c>
-      <c r="I57" s="57" t="n">
+      <c r="I57" s="49" t="n">
         <v>2.35</v>
       </c>
-      <c r="J57" s="57" t="n">
+      <c r="J57" s="49" t="n">
         <v>47.5</v>
       </c>
-      <c r="K57" s="57" t="n">
+      <c r="K57" s="49" t="n">
         <v>113</v>
       </c>
-      <c r="L57" s="57" t="n">
+      <c r="L57" s="49" t="n">
         <v>159</v>
       </c>
-      <c r="M57" s="57" t="n">
+      <c r="M57" s="49" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3510,40 +3414,40 @@
       <c r="A58" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B58" s="58" t="n">
+      <c r="B58" s="50" t="n">
         <v>14.3</v>
       </c>
-      <c r="C58" s="58" t="n">
+      <c r="C58" s="50" t="n">
         <v>0.54</v>
       </c>
-      <c r="D58" s="58" t="n">
+      <c r="D58" s="50" t="n">
         <v>15.1</v>
       </c>
-      <c r="E58" s="58" t="n">
+      <c r="E58" s="50" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F58" s="58" t="n">
+      <c r="F58" s="50" t="n">
         <v>890</v>
       </c>
-      <c r="G58" s="58" t="n">
+      <c r="G58" s="50" t="n">
         <v>440</v>
       </c>
-      <c r="H58" s="58" t="n">
+      <c r="H58" s="50" t="n">
         <v>14</v>
       </c>
-      <c r="I58" s="58" t="n">
+      <c r="I58" s="50" t="n">
         <v>5.16</v>
       </c>
-      <c r="J58" s="58" t="n">
+      <c r="J58" s="50" t="n">
         <v>42.5</v>
       </c>
-      <c r="K58" s="58" t="n">
+      <c r="K58" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="L58" s="58" t="n">
+      <c r="L58" s="50" t="n">
         <v>196</v>
       </c>
-      <c r="M58" s="58" t="n">
+      <c r="M58" s="50" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3551,40 +3455,40 @@
       <c r="A59" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B59" s="59" t="n">
+      <c r="B59" s="51" t="n">
         <v>14.3</v>
       </c>
-      <c r="C59" s="59" t="n">
+      <c r="C59" s="51" t="n">
         <v>0.54</v>
       </c>
-      <c r="D59" s="59" t="n">
+      <c r="D59" s="51" t="n">
         <v>27.5</v>
       </c>
-      <c r="E59" s="59" t="n">
+      <c r="E59" s="51" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F59" s="59" t="n">
+      <c r="F59" s="51" t="n">
         <v>1000</v>
       </c>
-      <c r="G59" s="59" t="n">
+      <c r="G59" s="51" t="n">
         <v>490</v>
       </c>
-      <c r="H59" s="59" t="n">
+      <c r="H59" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="I59" s="59" t="n">
+      <c r="I59" s="51" t="n">
         <v>5.27</v>
       </c>
-      <c r="J59" s="59" t="n">
+      <c r="J59" s="51" t="n">
         <v>42.5</v>
       </c>
-      <c r="K59" s="59" t="n">
+      <c r="K59" s="51" t="n">
         <v>46.5</v>
       </c>
-      <c r="L59" s="59" t="n">
+      <c r="L59" s="51" t="n">
         <v>192</v>
       </c>
-      <c r="M59" s="59" t="n">
+      <c r="M59" s="51" t="n">
         <v>56</v>
       </c>
     </row>
@@ -3592,40 +3496,40 @@
       <c r="A60" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B60" s="60" t="n">
+      <c r="B60" s="52" t="n">
         <v>14.3</v>
       </c>
-      <c r="C60" s="60" t="n">
+      <c r="C60" s="52" t="n">
         <v>0.54</v>
       </c>
-      <c r="D60" s="60" t="n">
+      <c r="D60" s="52" t="n">
         <v>20</v>
       </c>
-      <c r="E60" s="60" t="n">
+      <c r="E60" s="52" t="n">
         <v>8.1</v>
       </c>
-      <c r="F60" s="60" t="n">
+      <c r="F60" s="52" t="n">
         <v>1450</v>
       </c>
-      <c r="G60" s="60" t="n">
+      <c r="G60" s="52" t="n">
         <v>720</v>
       </c>
-      <c r="H60" s="60" t="n">
+      <c r="H60" s="52" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="60" t="n">
+      <c r="I60" s="52" t="n">
         <v>1.48</v>
       </c>
-      <c r="J60" s="60" t="n">
+      <c r="J60" s="52" t="n">
         <v>45</v>
       </c>
-      <c r="K60" s="60" t="n">
+      <c r="K60" s="52" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="L60" s="60" t="n">
+      <c r="L60" s="52" t="n">
         <v>167</v>
       </c>
-      <c r="M60" s="60" t="n">
+      <c r="M60" s="52" t="n">
         <v>109</v>
       </c>
     </row>
@@ -3633,40 +3537,40 @@
       <c r="A61" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B61" s="61" t="n">
+      <c r="B61" s="41" t="n">
         <v>14.3</v>
       </c>
-      <c r="C61" s="61" t="n">
+      <c r="C61" s="41" t="n">
         <v>0.54</v>
       </c>
-      <c r="D61" s="61" t="n">
+      <c r="D61" s="41" t="n">
         <v>25.1</v>
       </c>
-      <c r="E61" s="61" t="n">
+      <c r="E61" s="41" t="n">
         <v>8.1</v>
       </c>
-      <c r="F61" s="61" t="n">
+      <c r="F61" s="41" t="n">
         <v>1370</v>
       </c>
-      <c r="G61" s="61" t="n">
+      <c r="G61" s="41" t="n">
         <v>680</v>
       </c>
-      <c r="H61" s="61" t="n">
+      <c r="H61" s="41" t="n">
         <v>14</v>
       </c>
-      <c r="I61" s="61" t="n">
+      <c r="I61" s="41" t="n">
         <v>1.32</v>
       </c>
-      <c r="J61" s="61" t="n">
+      <c r="J61" s="41" t="n">
         <v>45</v>
       </c>
-      <c r="K61" s="61" t="n">
+      <c r="K61" s="41" t="n">
         <v>123</v>
       </c>
-      <c r="L61" s="61" t="n">
+      <c r="L61" s="41" t="n">
         <v>163</v>
       </c>
-      <c r="M61" s="61" t="n">
+      <c r="M61" s="41" t="n">
         <v>112</v>
       </c>
     </row>
@@ -3674,40 +3578,40 @@
       <c r="A62" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B62" s="62" t="n">
+      <c r="B62" s="53" t="n">
         <v>26</v>
       </c>
-      <c r="C62" s="62" t="n">
+      <c r="C62" s="53" t="n">
         <v>0.87</v>
       </c>
-      <c r="D62" s="62" t="n">
+      <c r="D62" s="53" t="n">
         <v>18.1</v>
       </c>
-      <c r="E62" s="62" t="n">
+      <c r="E62" s="53" t="n">
         <v>7.2</v>
       </c>
-      <c r="F62" s="62" t="n">
+      <c r="F62" s="53" t="n">
         <v>1430</v>
       </c>
-      <c r="G62" s="62" t="n">
+      <c r="G62" s="53" t="n">
         <v>710</v>
       </c>
-      <c r="H62" s="62" t="n">
+      <c r="H62" s="53" t="n">
         <v>650</v>
       </c>
-      <c r="I62" s="62" t="n">
+      <c r="I62" s="53" t="n">
         <v>1.12</v>
       </c>
-      <c r="J62" s="62" t="n">
+      <c r="J62" s="53" t="n">
         <v>30</v>
       </c>
-      <c r="K62" s="62" t="n">
+      <c r="K62" s="53" t="n">
         <v>1000</v>
       </c>
-      <c r="L62" s="62" t="n">
+      <c r="L62" s="53" t="n">
         <v>147</v>
       </c>
-      <c r="M62" s="62" t="n">
+      <c r="M62" s="53" t="n">
         <v>96.87179487179488</v>
       </c>
     </row>
@@ -3715,40 +3619,40 @@
       <c r="A63" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B63" s="63" t="n">
+      <c r="B63" s="54" t="n">
         <v>26</v>
       </c>
-      <c r="C63" s="63" t="n">
+      <c r="C63" s="54" t="n">
         <v>0.87</v>
       </c>
-      <c r="D63" s="63" t="n">
+      <c r="D63" s="54" t="n">
         <v>18.2</v>
       </c>
-      <c r="E63" s="63" t="n">
+      <c r="E63" s="54" t="n">
         <v>7.2</v>
       </c>
-      <c r="F63" s="63" t="n">
+      <c r="F63" s="54" t="n">
         <v>1450</v>
       </c>
-      <c r="G63" s="63" t="n">
+      <c r="G63" s="54" t="n">
         <v>720</v>
       </c>
-      <c r="H63" s="63" t="n">
+      <c r="H63" s="54" t="n">
         <v>650</v>
       </c>
-      <c r="I63" s="63" t="n">
+      <c r="I63" s="54" t="n">
         <v>0.85</v>
       </c>
-      <c r="J63" s="63" t="n">
+      <c r="J63" s="54" t="n">
         <v>30</v>
       </c>
-      <c r="K63" s="63" t="n">
+      <c r="K63" s="54" t="n">
         <v>1000</v>
       </c>
-      <c r="L63" s="63" t="n">
+      <c r="L63" s="54" t="n">
         <v>151</v>
       </c>
-      <c r="M63" s="63" t="n">
+      <c r="M63" s="54" t="n">
         <v>96.87179487179488</v>
       </c>
     </row>
@@ -3756,40 +3660,40 @@
       <c r="A64" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B64" s="64" t="n">
+      <c r="B64" s="52" t="n">
         <v>26</v>
       </c>
-      <c r="C64" s="64" t="n">
+      <c r="C64" s="52" t="n">
         <v>0.87</v>
       </c>
-      <c r="D64" s="64" t="n">
+      <c r="D64" s="52" t="n">
         <v>18.1</v>
       </c>
-      <c r="E64" s="64" t="n">
+      <c r="E64" s="52" t="n">
         <v>8.4</v>
       </c>
-      <c r="F64" s="64" t="n">
+      <c r="F64" s="52" t="n">
         <v>1400</v>
       </c>
-      <c r="G64" s="64" t="n">
+      <c r="G64" s="52" t="n">
         <v>690</v>
       </c>
-      <c r="H64" s="64" t="n">
+      <c r="H64" s="52" t="n">
         <v>80</v>
       </c>
-      <c r="I64" s="64" t="n">
+      <c r="I64" s="52" t="n">
         <v>3.59</v>
       </c>
-      <c r="J64" s="64" t="n">
+      <c r="J64" s="52" t="n">
         <v>35</v>
       </c>
-      <c r="K64" s="64" t="n">
+      <c r="K64" s="52" t="n">
         <v>221</v>
       </c>
-      <c r="L64" s="64" t="n">
+      <c r="L64" s="52" t="n">
         <v>183</v>
       </c>
-      <c r="M64" s="64" t="n">
+      <c r="M64" s="52" t="n">
         <v>124</v>
       </c>
     </row>
@@ -3797,40 +3701,40 @@
       <c r="A65" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B65" s="65" t="n">
+      <c r="B65" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="C65" s="65" t="n">
+      <c r="C65" s="55" t="n">
         <v>0.87</v>
       </c>
-      <c r="D65" s="65" t="n">
+      <c r="D65" s="55" t="n">
         <v>18.1</v>
       </c>
-      <c r="E65" s="65" t="n">
+      <c r="E65" s="55" t="n">
         <v>8.4</v>
       </c>
-      <c r="F65" s="65" t="n">
+      <c r="F65" s="55" t="n">
         <v>1370</v>
       </c>
-      <c r="G65" s="65" t="n">
+      <c r="G65" s="55" t="n">
         <v>680</v>
       </c>
-      <c r="H65" s="65" t="n">
+      <c r="H65" s="55" t="n">
         <v>80</v>
       </c>
-      <c r="I65" s="65" t="n">
+      <c r="I65" s="55" t="n">
         <v>3.46</v>
       </c>
-      <c r="J65" s="65" t="n">
+      <c r="J65" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="K65" s="65" t="n">
+      <c r="K65" s="55" t="n">
         <v>437</v>
       </c>
-      <c r="L65" s="65" t="n">
+      <c r="L65" s="55" t="n">
         <v>179</v>
       </c>
-      <c r="M65" s="65" t="n">
+      <c r="M65" s="55" t="n">
         <v>124</v>
       </c>
     </row>
@@ -3838,40 +3742,40 @@
       <c r="A66" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B66" s="66" t="n">
+      <c r="B66" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="C66" s="66" t="n">
+      <c r="C66" s="56" t="n">
         <v>0.87</v>
       </c>
-      <c r="D66" s="66" t="n">
+      <c r="D66" s="56" t="n">
         <v>18.3</v>
       </c>
-      <c r="E66" s="66" t="n">
+      <c r="E66" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="F66" s="66" t="n">
+      <c r="F66" s="56" t="n">
         <v>1380</v>
       </c>
-      <c r="G66" s="66" t="n">
+      <c r="G66" s="56" t="n">
         <v>680</v>
       </c>
-      <c r="H66" s="66" t="n">
+      <c r="H66" s="56" t="n">
         <v>50</v>
       </c>
-      <c r="I66" s="66" t="n">
+      <c r="I66" s="56" t="n">
         <v>1.56</v>
       </c>
-      <c r="J66" s="66" t="n">
+      <c r="J66" s="56" t="n">
         <v>55</v>
       </c>
-      <c r="K66" s="66" t="n">
+      <c r="K66" s="56" t="n">
         <v>158</v>
       </c>
-      <c r="L66" s="66" t="n">
+      <c r="L66" s="56" t="n">
         <v>143</v>
       </c>
-      <c r="M66" s="66" t="n">
+      <c r="M66" s="56" t="n">
         <v>107</v>
       </c>
     </row>
@@ -3879,40 +3783,40 @@
       <c r="A67" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B67" s="67" t="n">
+      <c r="B67" s="57" t="n">
         <v>26</v>
       </c>
-      <c r="C67" s="67" t="n">
+      <c r="C67" s="57" t="n">
         <v>0.87</v>
       </c>
-      <c r="D67" s="67" t="n">
+      <c r="D67" s="57" t="n">
         <v>18.3</v>
       </c>
-      <c r="E67" s="67" t="n">
+      <c r="E67" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="F67" s="67" t="n">
+      <c r="F67" s="57" t="n">
         <v>1340</v>
       </c>
-      <c r="G67" s="67" t="n">
+      <c r="G67" s="57" t="n">
         <v>660</v>
       </c>
-      <c r="H67" s="67" t="n">
+      <c r="H67" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="I67" s="67" t="n">
+      <c r="I67" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="J67" s="67" t="n">
+      <c r="J67" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="K67" s="67" t="n">
+      <c r="K67" s="57" t="n">
         <v>209</v>
       </c>
-      <c r="L67" s="67" t="n">
+      <c r="L67" s="57" t="n">
         <v>147</v>
       </c>
-      <c r="M67" s="67" t="n">
+      <c r="M67" s="57" t="n">
         <v>107</v>
       </c>
     </row>
@@ -3920,40 +3824,40 @@
       <c r="A68" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B68" s="68" t="n">
+      <c r="B68" s="58" t="n">
         <v>26</v>
       </c>
-      <c r="C68" s="68" t="n">
+      <c r="C68" s="58" t="n">
         <v>0.87</v>
       </c>
-      <c r="D68" s="68" t="n">
+      <c r="D68" s="58" t="n">
         <v>18.3</v>
       </c>
-      <c r="E68" s="68" t="n">
+      <c r="E68" s="58" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F68" s="68" t="n">
+      <c r="F68" s="58" t="n">
         <v>1020</v>
       </c>
-      <c r="G68" s="68" t="n">
+      <c r="G68" s="58" t="n">
         <v>500</v>
       </c>
-      <c r="H68" s="68" t="n">
+      <c r="H68" s="58" t="n">
         <v>70</v>
       </c>
-      <c r="I68" s="68" t="n">
+      <c r="I68" s="58" t="n">
         <v>4.3</v>
       </c>
-      <c r="J68" s="68" t="n">
+      <c r="J68" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="K68" s="68" t="n">
+      <c r="K68" s="58" t="n">
         <v>21.9</v>
       </c>
-      <c r="L68" s="68" t="n">
+      <c r="L68" s="58" t="n">
         <v>212</v>
       </c>
-      <c r="M68" s="68" t="n">
+      <c r="M68" s="58" t="n">
         <v>68</v>
       </c>
     </row>
@@ -3961,40 +3865,40 @@
       <c r="A69" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B69" s="69" t="n">
+      <c r="B69" s="59" t="n">
         <v>26</v>
       </c>
-      <c r="C69" s="69" t="n">
+      <c r="C69" s="59" t="n">
         <v>0.87</v>
       </c>
-      <c r="D69" s="69" t="n">
+      <c r="D69" s="59" t="n">
         <v>18.2</v>
       </c>
-      <c r="E69" s="69" t="n">
+      <c r="E69" s="59" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F69" s="69" t="n">
+      <c r="F69" s="59" t="n">
         <v>1040</v>
       </c>
-      <c r="G69" s="69" t="n">
+      <c r="G69" s="59" t="n">
         <v>510</v>
       </c>
-      <c r="H69" s="69" t="n">
+      <c r="H69" s="59" t="n">
         <v>70</v>
       </c>
-      <c r="I69" s="69" t="n">
+      <c r="I69" s="59" t="n">
         <v>4.02</v>
       </c>
-      <c r="J69" s="69" t="n">
+      <c r="J69" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="K69" s="69" t="n">
+      <c r="K69" s="59" t="n">
         <v>65</v>
       </c>
-      <c r="L69" s="69" t="n">
+      <c r="L69" s="59" t="n">
         <v>216</v>
       </c>
-      <c r="M69" s="69" t="n">
+      <c r="M69" s="59" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4002,40 +3906,40 @@
       <c r="A70" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B70" s="70" t="n">
+      <c r="B70" s="60" t="n">
         <v>26</v>
       </c>
-      <c r="C70" s="70" t="n">
+      <c r="C70" s="60" t="n">
         <v>0.87</v>
       </c>
-      <c r="D70" s="70" t="n">
+      <c r="D70" s="60" t="n">
         <v>18.2</v>
       </c>
-      <c r="E70" s="70" t="n">
+      <c r="E70" s="60" t="n">
         <v>8.1</v>
       </c>
-      <c r="F70" s="70" t="n">
+      <c r="F70" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="G70" s="70" t="n">
+      <c r="G70" s="60" t="n">
         <v>710</v>
       </c>
-      <c r="H70" s="70" t="n">
+      <c r="H70" s="60" t="n">
         <v>64</v>
       </c>
-      <c r="I70" s="70" t="n">
+      <c r="I70" s="60" t="n">
         <v>1.93</v>
       </c>
-      <c r="J70" s="70" t="n">
+      <c r="J70" s="60" t="n">
         <v>50</v>
       </c>
-      <c r="K70" s="70" t="n">
+      <c r="K70" s="60" t="n">
         <v>123</v>
       </c>
-      <c r="L70" s="70" t="n">
+      <c r="L70" s="60" t="n">
         <v>179</v>
       </c>
-      <c r="M70" s="70" t="n">
+      <c r="M70" s="60" t="n">
         <v>124</v>
       </c>
     </row>
@@ -4043,40 +3947,40 @@
       <c r="A71" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B71" s="71" t="n">
+      <c r="B71" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="C71" s="71" t="n">
+      <c r="C71" s="61" t="n">
         <v>0.87</v>
       </c>
-      <c r="D71" s="71" t="n">
+      <c r="D71" s="61" t="n">
         <v>18.2</v>
       </c>
-      <c r="E71" s="71" t="n">
+      <c r="E71" s="61" t="n">
         <v>8.1</v>
       </c>
-      <c r="F71" s="71" t="n">
+      <c r="F71" s="61" t="n">
         <v>1450</v>
       </c>
-      <c r="G71" s="71" t="n">
+      <c r="G71" s="61" t="n">
         <v>720</v>
       </c>
-      <c r="H71" s="71" t="n">
+      <c r="H71" s="61" t="n">
         <v>64</v>
       </c>
-      <c r="I71" s="71" t="n">
+      <c r="I71" s="61" t="n">
         <v>1.84</v>
       </c>
-      <c r="J71" s="71" t="n">
+      <c r="J71" s="61" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="71" t="n">
+      <c r="K71" s="61" t="n">
         <v>148</v>
       </c>
-      <c r="L71" s="71" t="n">
+      <c r="L71" s="61" t="n">
         <v>175</v>
       </c>
-      <c r="M71" s="71" t="n">
+      <c r="M71" s="61" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4084,40 +3988,40 @@
       <c r="A72" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B72" s="72" t="n">
+      <c r="B72" s="62" t="n">
         <v>13.4</v>
       </c>
-      <c r="C72" s="72" t="n">
+      <c r="C72" s="62" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D72" s="72" t="n">
+      <c r="D72" s="62" t="n">
         <v>16.8</v>
       </c>
-      <c r="E72" s="72" t="n">
+      <c r="E72" s="62" t="n">
         <v>8.1</v>
       </c>
-      <c r="F72" s="72" t="n">
+      <c r="F72" s="62" t="n">
         <v>1470</v>
       </c>
-      <c r="G72" s="72" t="n">
+      <c r="G72" s="62" t="n">
         <v>730</v>
       </c>
-      <c r="H72" s="72" t="n">
+      <c r="H72" s="62" t="n">
         <v>128</v>
       </c>
-      <c r="I72" s="72" t="n">
+      <c r="I72" s="62" t="n">
         <v>0.68</v>
       </c>
-      <c r="J72" s="72" t="n">
+      <c r="J72" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="K72" s="72" t="n">
+      <c r="K72" s="62" t="n">
         <v>60.9</v>
       </c>
-      <c r="L72" s="72" t="n">
+      <c r="L72" s="62" t="n">
         <v>181</v>
       </c>
-      <c r="M72" s="72" t="n">
+      <c r="M72" s="62" t="n">
         <v>110</v>
       </c>
     </row>
@@ -4125,40 +4029,40 @@
       <c r="A73" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B73" s="73" t="n">
+      <c r="B73" s="62" t="n">
         <v>13.4</v>
       </c>
-      <c r="C73" s="73" t="n">
+      <c r="C73" s="62" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D73" s="73" t="n">
+      <c r="D73" s="62" t="n">
         <v>15.8</v>
       </c>
-      <c r="E73" s="73" t="n">
+      <c r="E73" s="62" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F73" s="73" t="n">
+      <c r="F73" s="62" t="n">
         <v>1460</v>
       </c>
-      <c r="G73" s="73" t="n">
+      <c r="G73" s="62" t="n">
         <v>720</v>
       </c>
-      <c r="H73" s="73" t="n">
+      <c r="H73" s="62" t="n">
         <v>128</v>
       </c>
-      <c r="I73" s="73" t="n">
+      <c r="I73" s="62" t="n">
         <v>0.73</v>
       </c>
-      <c r="J73" s="73" t="n">
+      <c r="J73" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="K73" s="73" t="n">
+      <c r="K73" s="62" t="n">
         <v>53.4</v>
       </c>
-      <c r="L73" s="73" t="n">
+      <c r="L73" s="62" t="n">
         <v>181</v>
       </c>
-      <c r="M73" s="73" t="n">
+      <c r="M73" s="62" t="n">
         <v>110</v>
       </c>
     </row>
@@ -4166,40 +4070,40 @@
       <c r="A74" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B74" s="74" t="n">
+      <c r="B74" s="63" t="n">
         <v>13.4</v>
       </c>
-      <c r="C74" s="74" t="n">
+      <c r="C74" s="63" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D74" s="74" t="n">
+      <c r="D74" s="63" t="n">
         <v>16</v>
       </c>
-      <c r="E74" s="74" t="n">
+      <c r="E74" s="63" t="n">
         <v>8.6</v>
       </c>
-      <c r="F74" s="74" t="n">
+      <c r="F74" s="63" t="n">
         <v>1520</v>
       </c>
-      <c r="G74" s="74" t="n">
+      <c r="G74" s="63" t="n">
         <v>750</v>
       </c>
-      <c r="H74" s="74" t="n">
+      <c r="H74" s="63" t="n">
         <v>50</v>
       </c>
-      <c r="I74" s="74" t="n">
+      <c r="I74" s="63" t="n">
         <v>8.17</v>
       </c>
-      <c r="J74" s="74" t="n">
+      <c r="J74" s="63" t="n">
         <v>25</v>
       </c>
-      <c r="K74" s="74" t="n">
+      <c r="K74" s="63" t="n">
         <v>25.2</v>
       </c>
-      <c r="L74" s="74" t="n">
+      <c r="L74" s="63" t="n">
         <v>263</v>
       </c>
-      <c r="M74" s="74" t="n">
+      <c r="M74" s="63" t="n">
         <v>125</v>
       </c>
     </row>
@@ -4207,40 +4111,40 @@
       <c r="A75" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B75" s="75" t="n">
+      <c r="B75" s="64" t="n">
         <v>13.4</v>
       </c>
-      <c r="C75" s="75" t="n">
+      <c r="C75" s="64" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D75" s="75" t="n">
+      <c r="D75" s="64" t="n">
         <v>15.8</v>
       </c>
-      <c r="E75" s="75" t="n">
+      <c r="E75" s="64" t="n">
         <v>8.4</v>
       </c>
-      <c r="F75" s="75" t="n">
+      <c r="F75" s="64" t="n">
         <v>1480</v>
       </c>
-      <c r="G75" s="75" t="n">
+      <c r="G75" s="64" t="n">
         <v>730</v>
       </c>
-      <c r="H75" s="75" t="n">
+      <c r="H75" s="64" t="n">
         <v>50</v>
       </c>
-      <c r="I75" s="75" t="n">
+      <c r="I75" s="64" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="J75" s="75" t="n">
+      <c r="J75" s="64" t="n">
         <v>25</v>
       </c>
-      <c r="K75" s="75" t="n">
+      <c r="K75" s="64" t="n">
         <v>29.4</v>
       </c>
-      <c r="L75" s="75" t="n">
+      <c r="L75" s="64" t="n">
         <v>263</v>
       </c>
-      <c r="M75" s="75" t="n">
+      <c r="M75" s="64" t="n">
         <v>125</v>
       </c>
     </row>
@@ -4248,40 +4152,40 @@
       <c r="A76" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B76" s="76" t="n">
+      <c r="B76" s="65" t="n">
         <v>13.4</v>
       </c>
-      <c r="C76" s="76" t="n">
+      <c r="C76" s="65" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D76" s="76" t="n">
+      <c r="D76" s="65" t="n">
         <v>15.4</v>
       </c>
-      <c r="E76" s="76" t="n">
+      <c r="E76" s="65" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F76" s="76" t="n">
+      <c r="F76" s="65" t="n">
         <v>1550</v>
       </c>
-      <c r="G76" s="76" t="n">
+      <c r="G76" s="65" t="n">
         <v>770</v>
       </c>
-      <c r="H76" s="76" t="n">
+      <c r="H76" s="65" t="n">
         <v>40</v>
       </c>
-      <c r="I76" s="76" t="n">
+      <c r="I76" s="65" t="n">
         <v>1.11</v>
       </c>
-      <c r="J76" s="76" t="n">
+      <c r="J76" s="65" t="n">
         <v>55</v>
       </c>
-      <c r="K76" s="76" t="n">
+      <c r="K76" s="65" t="n">
         <v>62.7</v>
       </c>
-      <c r="L76" s="76" t="n">
+      <c r="L76" s="65" t="n">
         <v>222</v>
       </c>
-      <c r="M76" s="76" t="n">
+      <c r="M76" s="65" t="n">
         <v>133</v>
       </c>
     </row>
@@ -4289,40 +4193,40 @@
       <c r="A77" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B77" s="77" t="n">
+      <c r="B77" s="66" t="n">
         <v>13.4</v>
       </c>
-      <c r="C77" s="77" t="n">
+      <c r="C77" s="66" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D77" s="77" t="n">
+      <c r="D77" s="66" t="n">
         <v>15.8</v>
       </c>
-      <c r="E77" s="77" t="n">
+      <c r="E77" s="66" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F77" s="77" t="n">
+      <c r="F77" s="66" t="n">
         <v>1510</v>
       </c>
-      <c r="G77" s="77" t="n">
+      <c r="G77" s="66" t="n">
         <v>750</v>
       </c>
-      <c r="H77" s="77" t="n">
+      <c r="H77" s="66" t="n">
         <v>40</v>
       </c>
-      <c r="I77" s="77" t="n">
+      <c r="I77" s="66" t="n">
         <v>0.73</v>
       </c>
-      <c r="J77" s="77" t="n">
+      <c r="J77" s="66" t="n">
         <v>55</v>
       </c>
-      <c r="K77" s="77" t="n">
+      <c r="K77" s="66" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="L77" s="77" t="n">
+      <c r="L77" s="66" t="n">
         <v>222</v>
       </c>
-      <c r="M77" s="77" t="n">
+      <c r="M77" s="66" t="n">
         <v>133</v>
       </c>
     </row>
@@ -4330,40 +4234,40 @@
       <c r="A78" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B78" s="78" t="n">
+      <c r="B78" s="67" t="n">
         <v>13.4</v>
       </c>
-      <c r="C78" s="78" t="n">
+      <c r="C78" s="67" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D78" s="78" t="n">
+      <c r="D78" s="67" t="n">
         <v>15.6</v>
       </c>
-      <c r="E78" s="78" t="n">
+      <c r="E78" s="67" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F78" s="78" t="n">
+      <c r="F78" s="67" t="n">
         <v>1140</v>
       </c>
-      <c r="G78" s="78" t="n">
+      <c r="G78" s="67" t="n">
         <v>570</v>
       </c>
-      <c r="H78" s="78" t="n">
+      <c r="H78" s="67" t="n">
         <v>36</v>
       </c>
-      <c r="I78" s="78" t="n">
+      <c r="I78" s="67" t="n">
         <v>2.74</v>
       </c>
-      <c r="J78" s="78" t="n">
+      <c r="J78" s="67" t="n">
         <v>30</v>
       </c>
-      <c r="K78" s="78" t="n">
+      <c r="K78" s="67" t="n">
         <v>5.47</v>
       </c>
-      <c r="L78" s="78" t="n">
+      <c r="L78" s="67" t="n">
         <v>316</v>
       </c>
-      <c r="M78" s="78" t="n">
+      <c r="M78" s="67" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4371,40 +4275,40 @@
       <c r="A79" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B79" s="79" t="n">
+      <c r="B79" s="68" t="n">
         <v>13.4</v>
       </c>
-      <c r="C79" s="79" t="n">
+      <c r="C79" s="68" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D79" s="79" t="n">
+      <c r="D79" s="68" t="n">
         <v>15.8</v>
       </c>
-      <c r="E79" s="79" t="n">
+      <c r="E79" s="68" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F79" s="79" t="n">
+      <c r="F79" s="68" t="n">
         <v>1150</v>
       </c>
-      <c r="G79" s="79" t="n">
+      <c r="G79" s="68" t="n">
         <v>560</v>
       </c>
-      <c r="H79" s="79" t="n">
+      <c r="H79" s="68" t="n">
         <v>36</v>
       </c>
-      <c r="I79" s="79" t="n">
+      <c r="I79" s="68" t="n">
         <v>2.44</v>
       </c>
-      <c r="J79" s="79" t="n">
+      <c r="J79" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="K79" s="79" t="n">
+      <c r="K79" s="68" t="n">
         <v>22.7</v>
       </c>
-      <c r="L79" s="79" t="n">
+      <c r="L79" s="68" t="n">
         <v>316</v>
       </c>
-      <c r="M79" s="79" t="n">
+      <c r="M79" s="68" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4412,40 +4316,40 @@
       <c r="A80" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B80" s="80" t="n">
+      <c r="B80" s="69" t="n">
         <v>13.4</v>
       </c>
-      <c r="C80" s="80" t="n">
+      <c r="C80" s="69" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D80" s="80" t="n">
+      <c r="D80" s="69" t="n">
         <v>15.5</v>
       </c>
-      <c r="E80" s="80" t="n">
+      <c r="E80" s="69" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F80" s="80" t="n">
+      <c r="F80" s="69" t="n">
         <v>1420</v>
       </c>
-      <c r="G80" s="80" t="n">
+      <c r="G80" s="69" t="n">
         <v>700</v>
       </c>
-      <c r="H80" s="80" t="n">
+      <c r="H80" s="69" t="n">
         <v>66</v>
       </c>
-      <c r="I80" s="80" t="n">
+      <c r="I80" s="69" t="n">
         <v>0.88</v>
       </c>
-      <c r="J80" s="80" t="n">
+      <c r="J80" s="69" t="n">
         <v>45</v>
       </c>
-      <c r="K80" s="80" t="n">
+      <c r="K80" s="69" t="n">
         <v>66</v>
       </c>
-      <c r="L80" s="80" t="n">
+      <c r="L80" s="69" t="n">
         <v>257</v>
       </c>
-      <c r="M80" s="80" t="n">
+      <c r="M80" s="69" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4453,40 +4357,40 @@
       <c r="A81" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B81" s="81" t="n">
+      <c r="B81" s="70" t="n">
         <v>13.4</v>
       </c>
-      <c r="C81" s="81" t="n">
+      <c r="C81" s="70" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D81" s="81" t="n">
+      <c r="D81" s="70" t="n">
         <v>15.9</v>
       </c>
-      <c r="E81" s="81" t="n">
+      <c r="E81" s="70" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F81" s="81" t="n">
+      <c r="F81" s="70" t="n">
         <v>1480</v>
       </c>
-      <c r="G81" s="81" t="n">
+      <c r="G81" s="70" t="n">
         <v>730</v>
       </c>
-      <c r="H81" s="81" t="n">
+      <c r="H81" s="70" t="n">
         <v>66</v>
       </c>
-      <c r="I81" s="81" t="n">
+      <c r="I81" s="70" t="n">
         <v>1.3</v>
       </c>
-      <c r="J81" s="81" t="n">
+      <c r="J81" s="70" t="n">
         <v>45</v>
       </c>
-      <c r="K81" s="81" t="n">
+      <c r="K81" s="70" t="n">
         <v>87.2</v>
       </c>
-      <c r="L81" s="81" t="n">
+      <c r="L81" s="70" t="n">
         <v>257</v>
       </c>
-      <c r="M81" s="81" t="n">
+      <c r="M81" s="70" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4494,40 +4398,40 @@
       <c r="A82" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B82" s="82" t="n">
+      <c r="B82" s="71" t="n">
         <v>23</v>
       </c>
-      <c r="C82" s="82" t="n">
+      <c r="C82" s="71" t="n">
         <v>0.36</v>
       </c>
-      <c r="D82" s="82" t="n">
+      <c r="D82" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="E82" s="82" t="n">
+      <c r="E82" s="71" t="n">
         <v>7.3</v>
       </c>
-      <c r="F82" s="82" t="n">
+      <c r="F82" s="71" t="n">
         <v>1590</v>
       </c>
-      <c r="G82" s="82" t="n">
+      <c r="G82" s="71" t="n">
         <v>790</v>
       </c>
-      <c r="H82" s="82" t="n">
+      <c r="H82" s="71" t="n">
         <v>620</v>
       </c>
-      <c r="I82" s="82" t="n">
+      <c r="I82" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="82" t="n">
+      <c r="J82" s="71" t="n">
         <v>25</v>
       </c>
-      <c r="K82" s="82" t="n">
+      <c r="K82" s="71" t="n">
         <v>1000</v>
       </c>
-      <c r="L82" s="82" t="n">
+      <c r="L82" s="71" t="n">
         <v>228</v>
       </c>
-      <c r="M82" s="82" t="n">
+      <c r="M82" s="71" t="n">
         <v>118</v>
       </c>
     </row>
@@ -4535,40 +4439,40 @@
       <c r="A83" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B83" s="83" t="n">
+      <c r="B83" s="72" t="n">
         <v>23</v>
       </c>
-      <c r="C83" s="83" t="n">
+      <c r="C83" s="72" t="n">
         <v>0.36</v>
       </c>
-      <c r="D83" s="83" t="n">
+      <c r="D83" s="72" t="n">
         <v>20.8</v>
       </c>
-      <c r="E83" s="83" t="n">
+      <c r="E83" s="72" t="n">
         <v>7.3</v>
       </c>
-      <c r="F83" s="83" t="n">
+      <c r="F83" s="72" t="n">
         <v>1520</v>
       </c>
-      <c r="G83" s="83" t="n">
+      <c r="G83" s="72" t="n">
         <v>750</v>
       </c>
-      <c r="H83" s="83" t="n">
+      <c r="H83" s="72" t="n">
         <v>620</v>
       </c>
-      <c r="I83" s="83" t="n">
+      <c r="I83" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="83" t="n">
+      <c r="J83" s="72" t="n">
         <v>25</v>
       </c>
-      <c r="K83" s="83" t="n">
+      <c r="K83" s="72" t="n">
         <v>1000</v>
       </c>
-      <c r="L83" s="83" t="n">
+      <c r="L83" s="72" t="n">
         <v>228</v>
       </c>
-      <c r="M83" s="83" t="n">
+      <c r="M83" s="72" t="n">
         <v>118</v>
       </c>
     </row>
@@ -4576,40 +4480,40 @@
       <c r="A84" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B84" s="84" t="n">
+      <c r="B84" s="73" t="n">
         <v>23</v>
       </c>
-      <c r="C84" s="84" t="n">
+      <c r="C84" s="73" t="n">
         <v>0.36</v>
       </c>
-      <c r="D84" s="84" t="n">
+      <c r="D84" s="73" t="n">
         <v>21.2</v>
       </c>
-      <c r="E84" s="84" t="n">
+      <c r="E84" s="73" t="n">
         <v>8.5</v>
       </c>
-      <c r="F84" s="84" t="n">
+      <c r="F84" s="73" t="n">
         <v>1430</v>
       </c>
-      <c r="G84" s="84" t="n">
+      <c r="G84" s="73" t="n">
         <v>710</v>
       </c>
-      <c r="H84" s="84" t="n">
+      <c r="H84" s="73" t="n">
         <v>76</v>
       </c>
-      <c r="I84" s="84" t="n">
+      <c r="I84" s="73" t="n">
         <v>5.22</v>
       </c>
-      <c r="J84" s="84" t="n">
+      <c r="J84" s="73" t="n">
         <v>30</v>
       </c>
-      <c r="K84" s="84" t="n">
+      <c r="K84" s="73" t="n">
         <v>147</v>
       </c>
-      <c r="L84" s="84" t="n">
+      <c r="L84" s="73" t="n">
         <v>257</v>
       </c>
-      <c r="M84" s="84" t="n">
+      <c r="M84" s="73" t="n">
         <v>112</v>
       </c>
     </row>
@@ -4617,40 +4521,40 @@
       <c r="A85" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B85" s="85" t="n">
+      <c r="B85" s="74" t="n">
         <v>23</v>
       </c>
-      <c r="C85" s="85" t="n">
+      <c r="C85" s="74" t="n">
         <v>0.36</v>
       </c>
-      <c r="D85" s="85" t="n">
+      <c r="D85" s="74" t="n">
         <v>21.1</v>
       </c>
-      <c r="E85" s="85" t="n">
+      <c r="E85" s="74" t="n">
         <v>8.5</v>
       </c>
-      <c r="F85" s="85" t="n">
+      <c r="F85" s="74" t="n">
         <v>1410</v>
       </c>
-      <c r="G85" s="85" t="n">
+      <c r="G85" s="74" t="n">
         <v>700</v>
       </c>
-      <c r="H85" s="85" t="n">
+      <c r="H85" s="74" t="n">
         <v>76</v>
       </c>
-      <c r="I85" s="85" t="n">
+      <c r="I85" s="74" t="n">
         <v>4.25</v>
       </c>
-      <c r="J85" s="85" t="n">
+      <c r="J85" s="74" t="n">
         <v>30</v>
       </c>
-      <c r="K85" s="85" t="n">
+      <c r="K85" s="74" t="n">
         <v>150</v>
       </c>
-      <c r="L85" s="85" t="n">
+      <c r="L85" s="74" t="n">
         <v>257</v>
       </c>
-      <c r="M85" s="85" t="n">
+      <c r="M85" s="74" t="n">
         <v>112</v>
       </c>
     </row>
@@ -4658,40 +4562,40 @@
       <c r="A86" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B86" s="86" t="n">
+      <c r="B86" s="75" t="n">
         <v>23</v>
       </c>
-      <c r="C86" s="86" t="n">
+      <c r="C86" s="75" t="n">
         <v>0.36</v>
       </c>
-      <c r="D86" s="86" t="n">
+      <c r="D86" s="75" t="n">
         <v>21.3</v>
       </c>
-      <c r="E86" s="86" t="n">
+      <c r="E86" s="75" t="n">
         <v>8.1</v>
       </c>
-      <c r="F86" s="86" t="n">
+      <c r="F86" s="75" t="n">
         <v>1690</v>
       </c>
-      <c r="G86" s="86" t="n">
+      <c r="G86" s="75" t="n">
         <v>840</v>
       </c>
-      <c r="H86" s="86" t="n">
+      <c r="H86" s="75" t="n">
         <v>84</v>
       </c>
-      <c r="I86" s="86" t="n">
+      <c r="I86" s="75" t="n">
         <v>0.63</v>
       </c>
-      <c r="J86" s="86" t="n">
+      <c r="J86" s="75" t="n">
         <v>55</v>
       </c>
-      <c r="K86" s="86" t="n">
+      <c r="K86" s="75" t="n">
         <v>160</v>
       </c>
-      <c r="L86" s="86" t="n">
+      <c r="L86" s="75" t="n">
         <v>222</v>
       </c>
-      <c r="M86" s="86" t="n">
+      <c r="M86" s="75" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4699,40 +4603,40 @@
       <c r="A87" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B87" s="87" t="n">
+      <c r="B87" s="75" t="n">
         <v>23</v>
       </c>
-      <c r="C87" s="87" t="n">
+      <c r="C87" s="75" t="n">
         <v>0.36</v>
       </c>
-      <c r="D87" s="87" t="n">
+      <c r="D87" s="75" t="n">
         <v>21.2</v>
       </c>
-      <c r="E87" s="87" t="n">
+      <c r="E87" s="75" t="n">
         <v>8.1</v>
       </c>
-      <c r="F87" s="87" t="n">
+      <c r="F87" s="75" t="n">
         <v>1670</v>
       </c>
-      <c r="G87" s="87" t="n">
+      <c r="G87" s="75" t="n">
         <v>830</v>
       </c>
-      <c r="H87" s="87" t="n">
+      <c r="H87" s="75" t="n">
         <v>84</v>
       </c>
-      <c r="I87" s="87" t="n">
+      <c r="I87" s="75" t="n">
         <v>0.75</v>
       </c>
-      <c r="J87" s="87" t="n">
+      <c r="J87" s="75" t="n">
         <v>55</v>
       </c>
-      <c r="K87" s="87" t="n">
+      <c r="K87" s="75" t="n">
         <v>154</v>
       </c>
-      <c r="L87" s="87" t="n">
+      <c r="L87" s="75" t="n">
         <v>222</v>
       </c>
-      <c r="M87" s="87" t="n">
+      <c r="M87" s="75" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4740,40 +4644,40 @@
       <c r="A88" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B88" s="88" t="n">
+      <c r="B88" s="67" t="n">
         <v>23</v>
       </c>
-      <c r="C88" s="88" t="n">
+      <c r="C88" s="67" t="n">
         <v>0.36</v>
       </c>
-      <c r="D88" s="88" t="n">
+      <c r="D88" s="67" t="n">
         <v>21.4</v>
       </c>
-      <c r="E88" s="88" t="n">
+      <c r="E88" s="67" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F88" s="88" t="n">
+      <c r="F88" s="67" t="n">
         <v>1120</v>
       </c>
-      <c r="G88" s="88" t="n">
+      <c r="G88" s="67" t="n">
         <v>550</v>
       </c>
-      <c r="H88" s="88" t="n">
+      <c r="H88" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="88" t="n">
+      <c r="I88" s="67" t="n">
         <v>2.68</v>
       </c>
-      <c r="J88" s="88" t="n">
+      <c r="J88" s="67" t="n">
         <v>45</v>
       </c>
-      <c r="K88" s="88" t="n">
+      <c r="K88" s="67" t="n">
         <v>4.52</v>
       </c>
-      <c r="L88" s="88" t="n">
+      <c r="L88" s="67" t="n">
         <v>293</v>
       </c>
-      <c r="M88" s="88" t="n">
+      <c r="M88" s="67" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4781,40 +4685,40 @@
       <c r="A89" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B89" s="89" t="n">
+      <c r="B89" s="76" t="n">
         <v>23</v>
       </c>
-      <c r="C89" s="89" t="n">
+      <c r="C89" s="76" t="n">
         <v>0.36</v>
       </c>
-      <c r="D89" s="89" t="n">
+      <c r="D89" s="76" t="n">
         <v>21.3</v>
       </c>
-      <c r="E89" s="89" t="n">
+      <c r="E89" s="76" t="n">
         <v>8.1</v>
       </c>
-      <c r="F89" s="89" t="n">
+      <c r="F89" s="76" t="n">
         <v>1100</v>
       </c>
-      <c r="G89" s="89" t="n">
+      <c r="G89" s="76" t="n">
         <v>540</v>
       </c>
-      <c r="H89" s="89" t="n">
+      <c r="H89" s="76" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="89" t="n">
+      <c r="I89" s="76" t="n">
         <v>1.75</v>
       </c>
-      <c r="J89" s="89" t="n">
+      <c r="J89" s="76" t="n">
         <v>45</v>
       </c>
-      <c r="K89" s="89" t="n">
+      <c r="K89" s="76" t="n">
         <v>4.91</v>
       </c>
-      <c r="L89" s="89" t="n">
+      <c r="L89" s="76" t="n">
         <v>293</v>
       </c>
-      <c r="M89" s="89" t="n">
+      <c r="M89" s="76" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4822,40 +4726,40 @@
       <c r="A90" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B90" s="90" t="n">
+      <c r="B90" s="77" t="n">
         <v>23</v>
       </c>
-      <c r="C90" s="90" t="n">
+      <c r="C90" s="77" t="n">
         <v>0.36</v>
       </c>
-      <c r="D90" s="90" t="n">
+      <c r="D90" s="77" t="n">
         <v>21.4</v>
       </c>
-      <c r="E90" s="90" t="n">
+      <c r="E90" s="77" t="n">
         <v>8.1</v>
       </c>
-      <c r="F90" s="90" t="n">
+      <c r="F90" s="77" t="n">
         <v>1500</v>
       </c>
-      <c r="G90" s="90" t="n">
+      <c r="G90" s="77" t="n">
         <v>740</v>
       </c>
-      <c r="H90" s="90" t="n">
+      <c r="H90" s="77" t="n">
         <v>50</v>
       </c>
-      <c r="I90" s="90" t="n">
+      <c r="I90" s="77" t="n">
         <v>0.26</v>
       </c>
-      <c r="J90" s="90" t="n">
+      <c r="J90" s="77" t="n">
         <v>45</v>
       </c>
-      <c r="K90" s="90" t="n">
+      <c r="K90" s="77" t="n">
         <v>116</v>
       </c>
-      <c r="L90" s="90" t="n">
+      <c r="L90" s="77" t="n">
         <v>257</v>
       </c>
-      <c r="M90" s="90" t="n">
+      <c r="M90" s="77" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4863,40 +4767,40 @@
       <c r="A91" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B91" s="91" t="n">
+      <c r="B91" s="62" t="n">
         <v>23</v>
       </c>
-      <c r="C91" s="91" t="n">
+      <c r="C91" s="62" t="n">
         <v>0.36</v>
       </c>
-      <c r="D91" s="91" t="n">
+      <c r="D91" s="62" t="n">
         <v>21.3</v>
       </c>
-      <c r="E91" s="91" t="n">
+      <c r="E91" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="F91" s="91" t="n">
+      <c r="F91" s="62" t="n">
         <v>1440</v>
       </c>
-      <c r="G91" s="91" t="n">
+      <c r="G91" s="62" t="n">
         <v>710</v>
       </c>
-      <c r="H91" s="91" t="n">
+      <c r="H91" s="62" t="n">
         <v>50</v>
       </c>
-      <c r="I91" s="91" t="n">
+      <c r="I91" s="62" t="n">
         <v>0.25</v>
       </c>
-      <c r="J91" s="91" t="n">
+      <c r="J91" s="62" t="n">
         <v>45</v>
       </c>
-      <c r="K91" s="91" t="n">
+      <c r="K91" s="62" t="n">
         <v>38.5</v>
       </c>
-      <c r="L91" s="91" t="n">
+      <c r="L91" s="62" t="n">
         <v>257</v>
       </c>
-      <c r="M91" s="91" t="n">
+      <c r="M91" s="62" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4904,40 +4808,40 @@
       <c r="A92" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B92" s="92" t="n">
+      <c r="B92" s="78" t="n">
         <v>15.2</v>
       </c>
-      <c r="C92" s="92" t="n">
+      <c r="C92" s="78" t="n">
         <v>0.52</v>
       </c>
-      <c r="D92" s="92" t="n">
+      <c r="D92" s="78" t="n">
         <v>17.4</v>
       </c>
-      <c r="E92" s="92" t="n">
+      <c r="E92" s="78" t="n">
         <v>8.1</v>
       </c>
-      <c r="F92" s="92" t="n">
+      <c r="F92" s="78" t="n">
         <v>1020</v>
       </c>
-      <c r="G92" s="92" t="n">
+      <c r="G92" s="78" t="n">
         <v>500</v>
       </c>
-      <c r="H92" s="92" t="n">
+      <c r="H92" s="78" t="n">
         <v>82</v>
       </c>
-      <c r="I92" s="92" t="n">
+      <c r="I92" s="78" t="n">
         <v>2.87</v>
       </c>
-      <c r="J92" s="92" t="n">
+      <c r="J92" s="78" t="n">
         <v>35</v>
       </c>
-      <c r="K92" s="92" t="n">
+      <c r="K92" s="78" t="n">
         <v>1000</v>
       </c>
-      <c r="L92" s="92" t="n">
+      <c r="L92" s="78" t="n">
         <v>135</v>
       </c>
-      <c r="M92" s="92" t="n">
+      <c r="M92" s="78" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4945,40 +4849,40 @@
       <c r="A93" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B93" s="93" t="n">
+      <c r="B93" s="79" t="n">
         <v>15.2</v>
       </c>
-      <c r="C93" s="93" t="n">
+      <c r="C93" s="79" t="n">
         <v>0.52</v>
       </c>
-      <c r="D93" s="93" t="n">
+      <c r="D93" s="79" t="n">
         <v>17.3</v>
       </c>
-      <c r="E93" s="93" t="n">
+      <c r="E93" s="79" t="n">
         <v>8</v>
       </c>
-      <c r="F93" s="93" t="n">
+      <c r="F93" s="79" t="n">
         <v>960</v>
       </c>
-      <c r="G93" s="93" t="n">
+      <c r="G93" s="79" t="n">
         <v>470</v>
       </c>
-      <c r="H93" s="93" t="n">
+      <c r="H93" s="79" t="n">
         <v>82</v>
       </c>
-      <c r="I93" s="93" t="n">
+      <c r="I93" s="79" t="n">
         <v>1.82</v>
       </c>
-      <c r="J93" s="93" t="n">
+      <c r="J93" s="79" t="n">
         <v>35</v>
       </c>
-      <c r="K93" s="93" t="n">
+      <c r="K93" s="79" t="n">
         <v>1000</v>
       </c>
-      <c r="L93" s="93" t="n">
+      <c r="L93" s="79" t="n">
         <v>135</v>
       </c>
-      <c r="M93" s="93" t="n">
+      <c r="M93" s="79" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4986,40 +4890,40 @@
       <c r="A94" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B94" s="94" t="n">
+      <c r="B94" s="80" t="n">
         <v>15.2</v>
       </c>
-      <c r="C94" s="94" t="n">
+      <c r="C94" s="80" t="n">
         <v>0.52</v>
       </c>
-      <c r="D94" s="94" t="n">
+      <c r="D94" s="80" t="n">
         <v>17.5</v>
       </c>
-      <c r="E94" s="94" t="n">
+      <c r="E94" s="80" t="n">
         <v>8.1</v>
       </c>
-      <c r="F94" s="94" t="n">
+      <c r="F94" s="80" t="n">
         <v>640</v>
       </c>
-      <c r="G94" s="94" t="n">
+      <c r="G94" s="80" t="n">
         <v>310</v>
       </c>
-      <c r="H94" s="94" t="n">
+      <c r="H94" s="80" t="n">
         <v>66</v>
       </c>
-      <c r="I94" s="94" t="n">
+      <c r="I94" s="80" t="n">
         <v>5.35</v>
       </c>
-      <c r="J94" s="94" t="n">
+      <c r="J94" s="80" t="n">
         <v>40</v>
       </c>
-      <c r="K94" s="94" t="n">
+      <c r="K94" s="80" t="n">
         <v>161</v>
       </c>
-      <c r="L94" s="94" t="n">
+      <c r="L94" s="80" t="n">
         <v>152</v>
       </c>
-      <c r="M94" s="94" t="n">
+      <c r="M94" s="80" t="n">
         <v>49</v>
       </c>
     </row>
@@ -5027,40 +4931,40 @@
       <c r="A95" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B95" s="95" t="n">
+      <c r="B95" s="81" t="n">
         <v>15.2</v>
       </c>
-      <c r="C95" s="95" t="n">
+      <c r="C95" s="81" t="n">
         <v>0.52</v>
       </c>
-      <c r="D95" s="95" t="n">
+      <c r="D95" s="81" t="n">
         <v>17.7</v>
       </c>
-      <c r="E95" s="95" t="n">
+      <c r="E95" s="81" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F95" s="95" t="n">
+      <c r="F95" s="81" t="n">
         <v>620</v>
       </c>
-      <c r="G95" s="95" t="n">
+      <c r="G95" s="81" t="n">
         <v>300</v>
       </c>
-      <c r="H95" s="95" t="n">
+      <c r="H95" s="81" t="n">
         <v>66</v>
       </c>
-      <c r="I95" s="95" t="n">
+      <c r="I95" s="81" t="n">
         <v>5.43</v>
       </c>
-      <c r="J95" s="95" t="n">
+      <c r="J95" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="K95" s="95" t="n">
+      <c r="K95" s="81" t="n">
         <v>161</v>
       </c>
-      <c r="L95" s="95" t="n">
+      <c r="L95" s="81" t="n">
         <v>152</v>
       </c>
-      <c r="M95" s="95" t="n">
+      <c r="M95" s="81" t="n">
         <v>49</v>
       </c>
     </row>
@@ -5068,40 +4972,40 @@
       <c r="A96" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B96" s="96" t="n">
+      <c r="B96" s="82" t="n">
         <v>15.2</v>
       </c>
-      <c r="C96" s="96" t="n">
+      <c r="C96" s="82" t="n">
         <v>0.52</v>
       </c>
-      <c r="D96" s="96" t="n">
+      <c r="D96" s="82" t="n">
         <v>17.8</v>
       </c>
-      <c r="E96" s="96" t="n">
+      <c r="E96" s="82" t="n">
         <v>8.1</v>
       </c>
-      <c r="F96" s="96" t="n">
+      <c r="F96" s="82" t="n">
         <v>740</v>
       </c>
-      <c r="G96" s="96" t="n">
+      <c r="G96" s="82" t="n">
         <v>360</v>
       </c>
-      <c r="H96" s="96" t="n">
+      <c r="H96" s="82" t="n">
         <v>70</v>
       </c>
-      <c r="I96" s="96" t="n">
+      <c r="I96" s="82" t="n">
         <v>3.84</v>
       </c>
-      <c r="J96" s="96" t="n">
+      <c r="J96" s="82" t="n">
         <v>50</v>
       </c>
-      <c r="K96" s="96" t="n">
+      <c r="K96" s="82" t="n">
         <v>124</v>
       </c>
-      <c r="L96" s="96" t="n">
+      <c r="L96" s="82" t="n">
         <v>135</v>
       </c>
-      <c r="M96" s="96" t="n">
+      <c r="M96" s="82" t="n">
         <v>59</v>
       </c>
     </row>
@@ -5109,40 +5013,40 @@
       <c r="A97" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B97" s="97" t="n">
+      <c r="B97" s="82" t="n">
         <v>15.2</v>
       </c>
-      <c r="C97" s="97" t="n">
+      <c r="C97" s="82" t="n">
         <v>0.52</v>
       </c>
-      <c r="D97" s="97" t="n">
+      <c r="D97" s="82" t="n">
         <v>17.6</v>
       </c>
-      <c r="E97" s="97" t="n">
+      <c r="E97" s="82" t="n">
         <v>8.1</v>
       </c>
-      <c r="F97" s="97" t="n">
+      <c r="F97" s="82" t="n">
         <v>750</v>
       </c>
-      <c r="G97" s="97" t="n">
+      <c r="G97" s="82" t="n">
         <v>370</v>
       </c>
-      <c r="H97" s="97" t="n">
+      <c r="H97" s="82" t="n">
         <v>70</v>
       </c>
-      <c r="I97" s="97" t="n">
+      <c r="I97" s="82" t="n">
         <v>3.8</v>
       </c>
-      <c r="J97" s="97" t="n">
+      <c r="J97" s="82" t="n">
         <v>50</v>
       </c>
-      <c r="K97" s="97" t="n">
+      <c r="K97" s="82" t="n">
         <v>124</v>
       </c>
-      <c r="L97" s="97" t="n">
+      <c r="L97" s="82" t="n">
         <v>135</v>
       </c>
-      <c r="M97" s="97" t="n">
+      <c r="M97" s="82" t="n">
         <v>59</v>
       </c>
     </row>
@@ -5150,40 +5054,40 @@
       <c r="A98" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B98" s="98" t="n">
+      <c r="B98" s="83" t="n">
         <v>15.2</v>
       </c>
-      <c r="C98" s="98" t="n">
+      <c r="C98" s="83" t="n">
         <v>0.52</v>
       </c>
-      <c r="D98" s="98" t="n">
+      <c r="D98" s="83" t="n">
         <v>17.8</v>
       </c>
-      <c r="E98" s="98" t="n">
+      <c r="E98" s="83" t="n">
         <v>7.9</v>
       </c>
-      <c r="F98" s="98" t="n">
+      <c r="F98" s="83" t="n">
         <v>290</v>
       </c>
-      <c r="G98" s="98" t="n">
+      <c r="G98" s="83" t="n">
         <v>140</v>
       </c>
-      <c r="H98" s="98" t="n">
+      <c r="H98" s="83" t="n">
         <v>1.8</v>
       </c>
-      <c r="I98" s="98" t="n">
+      <c r="I98" s="83" t="n">
         <v>4.82</v>
       </c>
-      <c r="J98" s="98" t="n">
+      <c r="J98" s="83" t="n">
         <v>25</v>
       </c>
-      <c r="K98" s="98" t="n">
+      <c r="K98" s="83" t="n">
         <v>41.3</v>
       </c>
-      <c r="L98" s="98" t="n">
+      <c r="L98" s="83" t="n">
         <v>94</v>
       </c>
-      <c r="M98" s="98" t="n">
+      <c r="M98" s="83" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5191,40 +5095,40 @@
       <c r="A99" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B99" s="99" t="n">
+      <c r="B99" s="84" t="n">
         <v>15.2</v>
       </c>
-      <c r="C99" s="99" t="n">
+      <c r="C99" s="84" t="n">
         <v>0.52</v>
       </c>
-      <c r="D99" s="99" t="n">
+      <c r="D99" s="84" t="n">
         <v>17.9</v>
       </c>
-      <c r="E99" s="99" t="n">
+      <c r="E99" s="84" t="n">
         <v>7.9</v>
       </c>
-      <c r="F99" s="99" t="n">
+      <c r="F99" s="84" t="n">
         <v>200</v>
       </c>
-      <c r="G99" s="99" t="n">
+      <c r="G99" s="84" t="n">
         <v>140</v>
       </c>
-      <c r="H99" s="99" t="n">
+      <c r="H99" s="84" t="n">
         <v>1.8</v>
       </c>
-      <c r="I99" s="99" t="n">
+      <c r="I99" s="84" t="n">
         <v>5.47</v>
       </c>
-      <c r="J99" s="99" t="n">
+      <c r="J99" s="84" t="n">
         <v>25</v>
       </c>
-      <c r="K99" s="99" t="n">
+      <c r="K99" s="84" t="n">
         <v>41.3</v>
       </c>
-      <c r="L99" s="99" t="n">
+      <c r="L99" s="84" t="n">
         <v>94</v>
       </c>
-      <c r="M99" s="99" t="n">
+      <c r="M99" s="84" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5232,40 +5136,40 @@
       <c r="A100" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B100" s="100" t="n">
+      <c r="B100" s="85" t="n">
         <v>15.2</v>
       </c>
-      <c r="C100" s="100" t="n">
+      <c r="C100" s="85" t="n">
         <v>0.52</v>
       </c>
-      <c r="D100" s="100" t="n">
+      <c r="D100" s="85" t="n">
         <v>18.3</v>
       </c>
-      <c r="E100" s="100" t="n">
+      <c r="E100" s="85" t="n">
         <v>8</v>
       </c>
-      <c r="F100" s="100" t="n">
+      <c r="F100" s="85" t="n">
         <v>990</v>
       </c>
-      <c r="G100" s="100" t="n">
+      <c r="G100" s="85" t="n">
         <v>490</v>
       </c>
-      <c r="H100" s="100" t="n">
+      <c r="H100" s="85" t="n">
         <v>48</v>
       </c>
-      <c r="I100" s="100" t="n">
+      <c r="I100" s="85" t="n">
         <v>1.92</v>
       </c>
-      <c r="J100" s="100" t="n">
+      <c r="J100" s="85" t="n">
         <v>55</v>
       </c>
-      <c r="K100" s="100" t="n">
+      <c r="K100" s="85" t="n">
         <v>87.2</v>
       </c>
-      <c r="L100" s="100" t="n">
+      <c r="L100" s="85" t="n">
         <v>146</v>
       </c>
-      <c r="M100" s="100" t="n">
+      <c r="M100" s="85" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5273,40 +5177,40 @@
       <c r="A101" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B101" s="100" t="n">
+      <c r="B101" s="85" t="n">
         <v>15.2</v>
       </c>
-      <c r="C101" s="100" t="n">
+      <c r="C101" s="85" t="n">
         <v>0.52</v>
       </c>
-      <c r="D101" s="100" t="n">
+      <c r="D101" s="85" t="n">
         <v>18.4</v>
       </c>
-      <c r="E101" s="100" t="n">
+      <c r="E101" s="85" t="n">
         <v>8.1</v>
       </c>
-      <c r="F101" s="100" t="n">
+      <c r="F101" s="85" t="n">
         <v>1000</v>
       </c>
-      <c r="G101" s="100" t="n">
+      <c r="G101" s="85" t="n">
         <v>490</v>
       </c>
-      <c r="H101" s="100" t="n">
+      <c r="H101" s="85" t="n">
         <v>48</v>
       </c>
-      <c r="I101" s="100" t="n">
+      <c r="I101" s="85" t="n">
         <v>1.89</v>
       </c>
-      <c r="J101" s="100" t="n">
+      <c r="J101" s="85" t="n">
         <v>55</v>
       </c>
-      <c r="K101" s="100" t="n">
+      <c r="K101" s="85" t="n">
         <v>87.2</v>
       </c>
-      <c r="L101" s="100" t="n">
+      <c r="L101" s="85" t="n">
         <v>146</v>
       </c>
-      <c r="M101" s="100" t="n">
+      <c r="M101" s="85" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5314,40 +5218,40 @@
       <c r="A102" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B102" s="101" t="n">
+      <c r="B102" s="86" t="n">
         <v>14.4</v>
       </c>
-      <c r="C102" s="101" t="n">
+      <c r="C102" s="86" t="n">
         <v>0.48</v>
       </c>
-      <c r="D102" s="101" t="n">
+      <c r="D102" s="86" t="n">
         <v>16.9</v>
       </c>
-      <c r="E102" s="101" t="n">
+      <c r="E102" s="86" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F102" s="101" t="n">
+      <c r="F102" s="86" t="n">
         <v>1110</v>
       </c>
-      <c r="G102" s="101" t="n">
+      <c r="G102" s="86" t="n">
         <v>550</v>
       </c>
-      <c r="H102" s="101" t="n">
+      <c r="H102" s="86" t="n">
         <v>130</v>
       </c>
-      <c r="I102" s="101" t="n">
+      <c r="I102" s="86" t="n">
         <v>5.47</v>
       </c>
-      <c r="J102" s="101" t="n">
+      <c r="J102" s="86" t="n">
         <v>30</v>
       </c>
-      <c r="K102" s="101" t="n">
+      <c r="K102" s="86" t="n">
         <v>212</v>
       </c>
-      <c r="L102" s="101" t="n">
+      <c r="L102" s="86" t="n">
         <v>111</v>
       </c>
-      <c r="M102" s="101" t="n">
+      <c r="M102" s="86" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5355,40 +5259,40 @@
       <c r="A103" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B103" s="102" t="n">
+      <c r="B103" s="87" t="n">
         <v>14.4</v>
       </c>
-      <c r="C103" s="102" t="n">
+      <c r="C103" s="87" t="n">
         <v>0.48</v>
       </c>
-      <c r="D103" s="102" t="n">
+      <c r="D103" s="87" t="n">
         <v>16.8</v>
       </c>
-      <c r="E103" s="102" t="n">
+      <c r="E103" s="87" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F103" s="102" t="n">
+      <c r="F103" s="87" t="n">
         <v>1060</v>
       </c>
-      <c r="G103" s="102" t="n">
+      <c r="G103" s="87" t="n">
         <v>520</v>
       </c>
-      <c r="H103" s="102" t="n">
+      <c r="H103" s="87" t="n">
         <v>130</v>
       </c>
-      <c r="I103" s="102" t="n">
+      <c r="I103" s="87" t="n">
         <v>3.74</v>
       </c>
-      <c r="J103" s="102" t="n">
+      <c r="J103" s="87" t="n">
         <v>30</v>
       </c>
-      <c r="K103" s="102" t="n">
+      <c r="K103" s="87" t="n">
         <v>81</v>
       </c>
-      <c r="L103" s="102" t="n">
+      <c r="L103" s="87" t="n">
         <v>111</v>
       </c>
-      <c r="M103" s="102" t="n">
+      <c r="M103" s="87" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5396,40 +5300,40 @@
       <c r="A104" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B104" s="103" t="n">
+      <c r="B104" s="88" t="n">
         <v>14.4</v>
       </c>
-      <c r="C104" s="103" t="n">
+      <c r="C104" s="88" t="n">
         <v>0.48</v>
       </c>
-      <c r="D104" s="103" t="n">
+      <c r="D104" s="88" t="n">
         <v>16.9</v>
       </c>
-      <c r="E104" s="103" t="n">
+      <c r="E104" s="88" t="n">
         <v>8.4</v>
       </c>
-      <c r="F104" s="103" t="n">
+      <c r="F104" s="88" t="n">
         <v>1440</v>
       </c>
-      <c r="G104" s="103" t="n">
+      <c r="G104" s="88" t="n">
         <v>710</v>
       </c>
-      <c r="H104" s="103" t="n">
+      <c r="H104" s="88" t="n">
         <v>64</v>
       </c>
-      <c r="I104" s="103" t="n">
+      <c r="I104" s="88" t="n">
         <v>5.11</v>
       </c>
-      <c r="J104" s="103" t="n">
+      <c r="J104" s="88" t="n">
         <v>30</v>
       </c>
-      <c r="K104" s="103" t="n">
+      <c r="K104" s="88" t="n">
         <v>23.6</v>
       </c>
-      <c r="L104" s="103" t="n">
+      <c r="L104" s="88" t="n">
         <v>140</v>
       </c>
-      <c r="M104" s="103" t="n">
+      <c r="M104" s="88" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5437,40 +5341,40 @@
       <c r="A105" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B105" s="104" t="n">
+      <c r="B105" s="89" t="n">
         <v>14.4</v>
       </c>
-      <c r="C105" s="104" t="n">
+      <c r="C105" s="89" t="n">
         <v>0.48</v>
       </c>
-      <c r="D105" s="104" t="n">
+      <c r="D105" s="89" t="n">
         <v>16.9</v>
       </c>
-      <c r="E105" s="104" t="n">
+      <c r="E105" s="89" t="n">
         <v>8.4</v>
       </c>
-      <c r="F105" s="104" t="n">
+      <c r="F105" s="89" t="n">
         <v>1400</v>
       </c>
-      <c r="G105" s="104" t="n">
+      <c r="G105" s="89" t="n">
         <v>690</v>
       </c>
-      <c r="H105" s="104" t="n">
+      <c r="H105" s="89" t="n">
         <v>64</v>
       </c>
-      <c r="I105" s="104" t="n">
+      <c r="I105" s="89" t="n">
         <v>4.62</v>
       </c>
-      <c r="J105" s="104" t="n">
+      <c r="J105" s="89" t="n">
         <v>30</v>
       </c>
-      <c r="K105" s="104" t="n">
+      <c r="K105" s="89" t="n">
         <v>14.1</v>
       </c>
-      <c r="L105" s="104" t="n">
+      <c r="L105" s="89" t="n">
         <v>140</v>
       </c>
-      <c r="M105" s="104" t="n">
+      <c r="M105" s="89" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5478,40 +5382,40 @@
       <c r="A106" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B106" s="105" t="n">
+      <c r="B106" s="90" t="n">
         <v>14.4</v>
       </c>
-      <c r="C106" s="105" t="n">
+      <c r="C106" s="90" t="n">
         <v>0.48</v>
       </c>
-      <c r="D106" s="105" t="n">
+      <c r="D106" s="90" t="n">
         <v>16.9</v>
       </c>
-      <c r="E106" s="105" t="n">
+      <c r="E106" s="90" t="n">
         <v>8.4</v>
       </c>
-      <c r="F106" s="105" t="n">
+      <c r="F106" s="90" t="n">
         <v>1200</v>
       </c>
-      <c r="G106" s="105" t="n">
+      <c r="G106" s="90" t="n">
         <v>590</v>
       </c>
-      <c r="H106" s="105" t="n">
+      <c r="H106" s="90" t="n">
         <v>70</v>
       </c>
-      <c r="I106" s="105" t="n">
+      <c r="I106" s="90" t="n">
         <v>1.73</v>
       </c>
-      <c r="J106" s="105" t="n">
+      <c r="J106" s="90" t="n">
         <v>65</v>
       </c>
-      <c r="K106" s="105" t="n">
+      <c r="K106" s="90" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="L106" s="105" t="n">
+      <c r="L106" s="90" t="n">
         <v>111</v>
       </c>
-      <c r="M106" s="105" t="n">
+      <c r="M106" s="90" t="n">
         <v>85</v>
       </c>
     </row>
@@ -5519,40 +5423,40 @@
       <c r="A107" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B107" s="106" t="n">
+      <c r="B107" s="91" t="n">
         <v>14.4</v>
       </c>
-      <c r="C107" s="106" t="n">
+      <c r="C107" s="91" t="n">
         <v>0.48</v>
       </c>
-      <c r="D107" s="106" t="n">
+      <c r="D107" s="91" t="n">
         <v>16.9</v>
       </c>
-      <c r="E107" s="106" t="n">
+      <c r="E107" s="91" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F107" s="106" t="n">
+      <c r="F107" s="91" t="n">
         <v>1180</v>
       </c>
-      <c r="G107" s="106" t="n">
+      <c r="G107" s="91" t="n">
         <v>580</v>
       </c>
-      <c r="H107" s="106" t="n">
+      <c r="H107" s="91" t="n">
         <v>70</v>
       </c>
-      <c r="I107" s="106" t="n">
+      <c r="I107" s="91" t="n">
         <v>1.33</v>
       </c>
-      <c r="J107" s="106" t="n">
+      <c r="J107" s="91" t="n">
         <v>65</v>
       </c>
-      <c r="K107" s="106" t="n">
+      <c r="K107" s="91" t="n">
         <v>89.2</v>
       </c>
-      <c r="L107" s="106" t="n">
+      <c r="L107" s="91" t="n">
         <v>111</v>
       </c>
-      <c r="M107" s="106" t="n">
+      <c r="M107" s="91" t="n">
         <v>85</v>
       </c>
     </row>
@@ -5560,40 +5464,40 @@
       <c r="A108" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B108" s="107" t="n">
+      <c r="B108" s="92" t="n">
         <v>14.4</v>
       </c>
-      <c r="C108" s="107" t="n">
+      <c r="C108" s="92" t="n">
         <v>0.48</v>
       </c>
-      <c r="D108" s="107" t="n">
+      <c r="D108" s="92" t="n">
         <v>16.9</v>
       </c>
-      <c r="E108" s="107" t="n">
+      <c r="E108" s="92" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F108" s="107" t="n">
+      <c r="F108" s="92" t="n">
         <v>1120</v>
       </c>
-      <c r="G108" s="107" t="n">
+      <c r="G108" s="92" t="n">
         <v>550</v>
       </c>
-      <c r="H108" s="107" t="n">
+      <c r="H108" s="92" t="n">
         <v>24</v>
       </c>
-      <c r="I108" s="107" t="n">
+      <c r="I108" s="92" t="n">
         <v>3.34</v>
       </c>
-      <c r="J108" s="107" t="n">
+      <c r="J108" s="92" t="n">
         <v>20</v>
       </c>
-      <c r="K108" s="107" t="n">
+      <c r="K108" s="92" t="n">
         <v>2.95</v>
       </c>
-      <c r="L108" s="107" t="n">
+      <c r="L108" s="92" t="n">
         <v>211</v>
       </c>
-      <c r="M108" s="107" t="n">
+      <c r="M108" s="92" t="n">
         <v>64</v>
       </c>
     </row>
@@ -5601,40 +5505,40 @@
       <c r="A109" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B109" s="108" t="n">
+      <c r="B109" s="93" t="n">
         <v>14.4</v>
       </c>
-      <c r="C109" s="108" t="n">
+      <c r="C109" s="93" t="n">
         <v>0.48</v>
       </c>
-      <c r="D109" s="108" t="n">
+      <c r="D109" s="93" t="n">
         <v>16.8</v>
       </c>
-      <c r="E109" s="108" t="n">
+      <c r="E109" s="93" t="n">
         <v>8.1</v>
       </c>
-      <c r="F109" s="108" t="n">
+      <c r="F109" s="93" t="n">
         <v>1140</v>
       </c>
-      <c r="G109" s="108" t="n">
+      <c r="G109" s="93" t="n">
         <v>560</v>
       </c>
-      <c r="H109" s="108" t="n">
+      <c r="H109" s="93" t="n">
         <v>24</v>
       </c>
-      <c r="I109" s="108" t="n">
+      <c r="I109" s="93" t="n">
         <v>2.82</v>
       </c>
-      <c r="J109" s="108" t="n">
+      <c r="J109" s="93" t="n">
         <v>20</v>
       </c>
-      <c r="K109" s="108" t="n">
+      <c r="K109" s="93" t="n">
         <v>3.63</v>
       </c>
-      <c r="L109" s="108" t="n">
+      <c r="L109" s="93" t="n">
         <v>211</v>
       </c>
-      <c r="M109" s="108" t="n">
+      <c r="M109" s="93" t="n">
         <v>64</v>
       </c>
     </row>
@@ -5642,40 +5546,40 @@
       <c r="A110" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B110" s="109" t="n">
+      <c r="B110" s="32" t="n">
         <v>14.4</v>
       </c>
-      <c r="C110" s="109" t="n">
+      <c r="C110" s="32" t="n">
         <v>0.48</v>
       </c>
-      <c r="D110" s="109" t="n">
+      <c r="D110" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="E110" s="109" t="n">
+      <c r="E110" s="32" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F110" s="109" t="n">
+      <c r="F110" s="32" t="n">
         <v>1340</v>
       </c>
-      <c r="G110" s="109" t="n">
+      <c r="G110" s="32" t="n">
         <v>660</v>
       </c>
-      <c r="H110" s="109" t="n">
+      <c r="H110" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="I110" s="109" t="n">
+      <c r="I110" s="32" t="n">
         <v>1.39</v>
       </c>
-      <c r="J110" s="109" t="n">
+      <c r="J110" s="32" t="n">
         <v>55</v>
       </c>
-      <c r="K110" s="109" t="n">
+      <c r="K110" s="32" t="n">
         <v>56.5</v>
       </c>
-      <c r="L110" s="109" t="n">
+      <c r="L110" s="32" t="n">
         <v>135</v>
       </c>
-      <c r="M110" s="109" t="n">
+      <c r="M110" s="32" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5683,40 +5587,40 @@
       <c r="A111" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B111" s="110" t="n">
+      <c r="B111" s="94" t="n">
         <v>14.4</v>
       </c>
-      <c r="C111" s="110" t="n">
+      <c r="C111" s="94" t="n">
         <v>0.48</v>
       </c>
-      <c r="D111" s="110" t="n">
+      <c r="D111" s="94" t="n">
         <v>17</v>
       </c>
-      <c r="E111" s="110" t="n">
+      <c r="E111" s="94" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F111" s="110" t="n">
+      <c r="F111" s="94" t="n">
         <v>1350</v>
       </c>
-      <c r="G111" s="110" t="n">
+      <c r="G111" s="94" t="n">
         <v>660</v>
       </c>
-      <c r="H111" s="110" t="n">
+      <c r="H111" s="94" t="n">
         <v>50</v>
       </c>
-      <c r="I111" s="110" t="n">
+      <c r="I111" s="94" t="n">
         <v>1.05</v>
       </c>
-      <c r="J111" s="110" t="n">
+      <c r="J111" s="94" t="n">
         <v>55</v>
       </c>
-      <c r="K111" s="110" t="n">
+      <c r="K111" s="94" t="n">
         <v>118</v>
       </c>
-      <c r="L111" s="110" t="n">
+      <c r="L111" s="94" t="n">
         <v>135</v>
       </c>
-      <c r="M111" s="110" t="n">
+      <c r="M111" s="94" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5724,40 +5628,40 @@
       <c r="A112" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B112" s="111" t="n">
+      <c r="B112" s="95" t="n">
         <v>12.8</v>
       </c>
-      <c r="C112" s="111" t="n">
+      <c r="C112" s="95" t="n">
         <v>0.57</v>
       </c>
-      <c r="D112" s="111" t="n">
+      <c r="D112" s="95" t="n">
         <v>15.2</v>
       </c>
-      <c r="E112" s="111" t="n">
+      <c r="E112" s="95" t="n">
         <v>8.6</v>
       </c>
-      <c r="F112" s="111" t="n">
+      <c r="F112" s="95" t="n">
         <v>940</v>
       </c>
-      <c r="G112" s="111" t="n">
+      <c r="G112" s="95" t="n">
         <v>460</v>
       </c>
-      <c r="H112" s="111" t="n">
+      <c r="H112" s="95" t="n">
         <v>60</v>
       </c>
-      <c r="I112" s="111" t="n">
+      <c r="I112" s="95" t="n">
         <v>5.64</v>
       </c>
-      <c r="J112" s="111" t="n">
+      <c r="J112" s="95" t="n">
         <v>55</v>
       </c>
-      <c r="K112" s="111" t="n">
+      <c r="K112" s="95" t="n">
         <v>177</v>
       </c>
-      <c r="L112" s="111" t="n">
+      <c r="L112" s="95" t="n">
         <v>117</v>
       </c>
-      <c r="M112" s="111" t="n">
+      <c r="M112" s="95" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5765,40 +5669,40 @@
       <c r="A113" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B113" s="112" t="n">
+      <c r="B113" s="96" t="n">
         <v>12.8</v>
       </c>
-      <c r="C113" s="112" t="n">
+      <c r="C113" s="96" t="n">
         <v>0.57</v>
       </c>
-      <c r="D113" s="112" t="n">
+      <c r="D113" s="96" t="n">
         <v>15.3</v>
       </c>
-      <c r="E113" s="112" t="n">
+      <c r="E113" s="96" t="n">
         <v>8.4</v>
       </c>
-      <c r="F113" s="112" t="n">
+      <c r="F113" s="96" t="n">
         <v>930</v>
       </c>
-      <c r="G113" s="112" t="n">
+      <c r="G113" s="96" t="n">
         <v>460</v>
       </c>
-      <c r="H113" s="112" t="n">
+      <c r="H113" s="96" t="n">
         <v>60</v>
       </c>
-      <c r="I113" s="112" t="n">
+      <c r="I113" s="96" t="n">
         <v>3.28</v>
       </c>
-      <c r="J113" s="112" t="n">
+      <c r="J113" s="96" t="n">
         <v>55</v>
       </c>
-      <c r="K113" s="112" t="n">
+      <c r="K113" s="96" t="n">
         <v>128</v>
       </c>
-      <c r="L113" s="112" t="n">
+      <c r="L113" s="96" t="n">
         <v>117</v>
       </c>
-      <c r="M113" s="112" t="n">
+      <c r="M113" s="96" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5806,40 +5710,40 @@
       <c r="A114" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B114" s="113" t="n">
+      <c r="B114" s="97" t="n">
         <v>12.8</v>
       </c>
-      <c r="C114" s="113" t="n">
+      <c r="C114" s="97" t="n">
         <v>0.57</v>
       </c>
-      <c r="D114" s="113" t="n">
+      <c r="D114" s="97" t="n">
         <v>15.2</v>
       </c>
-      <c r="E114" s="113" t="n">
+      <c r="E114" s="97" t="n">
         <v>8.4</v>
       </c>
-      <c r="F114" s="113" t="n">
+      <c r="F114" s="97" t="n">
         <v>1300</v>
       </c>
-      <c r="G114" s="113" t="n">
+      <c r="G114" s="97" t="n">
         <v>640</v>
       </c>
-      <c r="H114" s="113" t="n">
+      <c r="H114" s="97" t="n">
         <v>80</v>
       </c>
-      <c r="I114" s="113" t="n">
+      <c r="I114" s="97" t="n">
         <v>7.93</v>
       </c>
-      <c r="J114" s="113" t="n">
+      <c r="J114" s="97" t="n">
         <v>35</v>
       </c>
-      <c r="K114" s="113" t="n">
+      <c r="K114" s="97" t="n">
         <v>33.4</v>
       </c>
-      <c r="L114" s="113" t="n">
+      <c r="L114" s="97" t="n">
         <v>263</v>
       </c>
-      <c r="M114" s="113" t="n">
+      <c r="M114" s="97" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5847,40 +5751,40 @@
       <c r="A115" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B115" s="114" t="n">
+      <c r="B115" s="98" t="n">
         <v>12.8</v>
       </c>
-      <c r="C115" s="114" t="n">
+      <c r="C115" s="98" t="n">
         <v>0.57</v>
       </c>
-      <c r="D115" s="114" t="n">
+      <c r="D115" s="98" t="n">
         <v>15.2</v>
       </c>
-      <c r="E115" s="114" t="n">
+      <c r="E115" s="98" t="n">
         <v>8.5</v>
       </c>
-      <c r="F115" s="114" t="n">
+      <c r="F115" s="98" t="n">
         <v>1320</v>
       </c>
-      <c r="G115" s="114" t="n">
+      <c r="G115" s="98" t="n">
         <v>650</v>
       </c>
-      <c r="H115" s="114" t="n">
+      <c r="H115" s="98" t="n">
         <v>80</v>
       </c>
-      <c r="I115" s="114" t="n">
+      <c r="I115" s="98" t="n">
         <v>7.9</v>
       </c>
-      <c r="J115" s="114" t="n">
+      <c r="J115" s="98" t="n">
         <v>35</v>
       </c>
-      <c r="K115" s="114" t="n">
+      <c r="K115" s="98" t="n">
         <v>31.7</v>
       </c>
-      <c r="L115" s="114" t="n">
+      <c r="L115" s="98" t="n">
         <v>263</v>
       </c>
-      <c r="M115" s="114" t="n">
+      <c r="M115" s="98" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5888,40 +5792,40 @@
       <c r="A116" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B116" s="115" t="n">
+      <c r="B116" s="99" t="n">
         <v>12.8</v>
       </c>
-      <c r="C116" s="115" t="n">
+      <c r="C116" s="99" t="n">
         <v>0.57</v>
       </c>
-      <c r="D116" s="115" t="n">
+      <c r="D116" s="99" t="n">
         <v>15.1</v>
       </c>
-      <c r="E116" s="115" t="n">
+      <c r="E116" s="99" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F116" s="115" t="n">
+      <c r="F116" s="99" t="n">
         <v>1070</v>
       </c>
-      <c r="G116" s="115" t="n">
+      <c r="G116" s="99" t="n">
         <v>530</v>
       </c>
-      <c r="H116" s="115" t="n">
+      <c r="H116" s="99" t="n">
         <v>46</v>
       </c>
-      <c r="I116" s="115" t="n">
+      <c r="I116" s="99" t="n">
         <v>2.9</v>
       </c>
-      <c r="J116" s="115" t="n">
+      <c r="J116" s="99" t="n">
         <v>65</v>
       </c>
-      <c r="K116" s="115" t="n">
+      <c r="K116" s="99" t="n">
         <v>117</v>
       </c>
-      <c r="L116" s="115" t="n">
+      <c r="L116" s="99" t="n">
         <v>176</v>
       </c>
-      <c r="M116" s="115" t="n">
+      <c r="M116" s="99" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5929,40 +5833,40 @@
       <c r="A117" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B117" s="116" t="n">
+      <c r="B117" s="100" t="n">
         <v>12.8</v>
       </c>
-      <c r="C117" s="116" t="n">
+      <c r="C117" s="100" t="n">
         <v>0.57</v>
       </c>
-      <c r="D117" s="116" t="n">
+      <c r="D117" s="100" t="n">
         <v>15.2</v>
       </c>
-      <c r="E117" s="116" t="n">
+      <c r="E117" s="100" t="n">
         <v>8.4</v>
       </c>
-      <c r="F117" s="116" t="n">
+      <c r="F117" s="100" t="n">
         <v>1080</v>
       </c>
-      <c r="G117" s="116" t="n">
+      <c r="G117" s="100" t="n">
         <v>530</v>
       </c>
-      <c r="H117" s="116" t="n">
+      <c r="H117" s="100" t="n">
         <v>46</v>
       </c>
-      <c r="I117" s="116" t="n">
+      <c r="I117" s="100" t="n">
         <v>3.18</v>
       </c>
-      <c r="J117" s="116" t="n">
+      <c r="J117" s="100" t="n">
         <v>65</v>
       </c>
-      <c r="K117" s="116" t="n">
+      <c r="K117" s="100" t="n">
         <v>113</v>
       </c>
-      <c r="L117" s="116" t="n">
+      <c r="L117" s="100" t="n">
         <v>176</v>
       </c>
-      <c r="M117" s="116" t="n">
+      <c r="M117" s="100" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5970,40 +5874,40 @@
       <c r="A118" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B118" s="117" t="n">
+      <c r="B118" s="101" t="n">
         <v>12.8</v>
       </c>
-      <c r="C118" s="117" t="n">
+      <c r="C118" s="101" t="n">
         <v>0.57</v>
       </c>
-      <c r="D118" s="117" t="n">
+      <c r="D118" s="101" t="n">
         <v>15.3</v>
       </c>
-      <c r="E118" s="117" t="n">
+      <c r="E118" s="101" t="n">
         <v>8</v>
       </c>
-      <c r="F118" s="117" t="n">
+      <c r="F118" s="101" t="n">
         <v>1110</v>
       </c>
-      <c r="G118" s="117" t="n">
+      <c r="G118" s="101" t="n">
         <v>550</v>
       </c>
-      <c r="H118" s="117" t="n">
+      <c r="H118" s="101" t="n">
         <v>18</v>
       </c>
-      <c r="I118" s="117" t="n">
+      <c r="I118" s="101" t="n">
         <v>4.18</v>
       </c>
-      <c r="J118" s="117" t="n">
+      <c r="J118" s="101" t="n">
         <v>25</v>
       </c>
-      <c r="K118" s="117" t="n">
+      <c r="K118" s="101" t="n">
         <v>5.04</v>
       </c>
-      <c r="L118" s="117" t="n">
+      <c r="L118" s="101" t="n">
         <v>316</v>
       </c>
-      <c r="M118" s="117" t="n">
+      <c r="M118" s="101" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6011,40 +5915,40 @@
       <c r="A119" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B119" s="118" t="n">
+      <c r="B119" s="102" t="n">
         <v>12.8</v>
       </c>
-      <c r="C119" s="118" t="n">
+      <c r="C119" s="102" t="n">
         <v>0.57</v>
       </c>
-      <c r="D119" s="118" t="n">
+      <c r="D119" s="102" t="n">
         <v>15.3</v>
       </c>
-      <c r="E119" s="118" t="n">
+      <c r="E119" s="102" t="n">
         <v>8.1</v>
       </c>
-      <c r="F119" s="118" t="n">
+      <c r="F119" s="102" t="n">
         <v>1080</v>
       </c>
-      <c r="G119" s="118" t="n">
+      <c r="G119" s="102" t="n">
         <v>550</v>
       </c>
-      <c r="H119" s="118" t="n">
+      <c r="H119" s="102" t="n">
         <v>18</v>
       </c>
-      <c r="I119" s="118" t="n">
+      <c r="I119" s="102" t="n">
         <v>4.23</v>
       </c>
-      <c r="J119" s="118" t="n">
+      <c r="J119" s="102" t="n">
         <v>25</v>
       </c>
-      <c r="K119" s="118" t="n">
+      <c r="K119" s="102" t="n">
         <v>5.69</v>
       </c>
-      <c r="L119" s="118" t="n">
+      <c r="L119" s="102" t="n">
         <v>316</v>
       </c>
-      <c r="M119" s="118" t="n">
+      <c r="M119" s="102" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6052,40 +5956,40 @@
       <c r="A120" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B120" s="119" t="n">
+      <c r="B120" s="103" t="n">
         <v>12.8</v>
       </c>
-      <c r="C120" s="119" t="n">
+      <c r="C120" s="103" t="n">
         <v>0.57</v>
       </c>
-      <c r="D120" s="119" t="n">
+      <c r="D120" s="103" t="n">
         <v>15.4</v>
       </c>
-      <c r="E120" s="119" t="n">
+      <c r="E120" s="103" t="n">
         <v>8.4</v>
       </c>
-      <c r="F120" s="119" t="n">
+      <c r="F120" s="103" t="n">
         <v>1050</v>
       </c>
-      <c r="G120" s="119" t="n">
+      <c r="G120" s="103" t="n">
         <v>520</v>
       </c>
-      <c r="H120" s="119" t="n">
+      <c r="H120" s="103" t="n">
         <v>44</v>
       </c>
-      <c r="I120" s="119" t="n">
+      <c r="I120" s="103" t="n">
         <v>1.96</v>
       </c>
-      <c r="J120" s="119" t="n">
+      <c r="J120" s="103" t="n">
         <v>70</v>
       </c>
-      <c r="K120" s="119" t="n">
+      <c r="K120" s="103" t="n">
         <v>113</v>
       </c>
-      <c r="L120" s="119" t="n">
+      <c r="L120" s="103" t="n">
         <v>146</v>
       </c>
-      <c r="M120" s="119" t="n">
+      <c r="M120" s="103" t="n">
         <v>82</v>
       </c>
     </row>
@@ -6093,40 +5997,40 @@
       <c r="A121" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B121" s="120" t="n">
+      <c r="B121" s="104" t="n">
         <v>12.8</v>
       </c>
-      <c r="C121" s="120" t="n">
+      <c r="C121" s="104" t="n">
         <v>0.57</v>
       </c>
-      <c r="D121" s="120" t="n">
+      <c r="D121" s="104" t="n">
         <v>15.4</v>
       </c>
-      <c r="E121" s="120" t="n">
+      <c r="E121" s="104" t="n">
         <v>8.4</v>
       </c>
-      <c r="F121" s="120" t="n">
+      <c r="F121" s="104" t="n">
         <v>1070</v>
       </c>
-      <c r="G121" s="120" t="n">
+      <c r="G121" s="104" t="n">
         <v>530</v>
       </c>
-      <c r="H121" s="120" t="n">
+      <c r="H121" s="104" t="n">
         <v>44</v>
       </c>
-      <c r="I121" s="120" t="n">
+      <c r="I121" s="104" t="n">
         <v>1.67</v>
       </c>
-      <c r="J121" s="120" t="n">
+      <c r="J121" s="104" t="n">
         <v>70</v>
       </c>
-      <c r="K121" s="120" t="n">
+      <c r="K121" s="104" t="n">
         <v>133</v>
       </c>
-      <c r="L121" s="120" t="n">
+      <c r="L121" s="104" t="n">
         <v>146</v>
       </c>
-      <c r="M121" s="120" t="n">
+      <c r="M121" s="104" t="n">
         <v>82</v>
       </c>
     </row>

--- a/colored_dataset.xlsx
+++ b/colored_dataset.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="105">
+  <fills count="121">
     <fill>
       <patternFill/>
     </fill>
@@ -38,22 +38,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008791FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C82FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009094FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008F95FF"/>
+        <fgColor rgb="00636CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DF99FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007598FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004DC5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0098FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008BB3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AFBFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008287FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00727DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CF9BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00887DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D6AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007977FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0098CEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008BA6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A4A0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DADFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009478FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A338FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9B7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00866CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008091FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0075C2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A3CAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008D75FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E88FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00747CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0083B1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007E77FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A1C2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006980FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B59DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A59BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B74FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007AC3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0B4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0091A3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092DDFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AC6EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082E9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005FB3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A154FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007479FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B06DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009179FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0064FCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0084B6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AAEDFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B2AFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008569FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B38EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0067E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009DBEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008477FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006CA0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0088CDFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009A8FFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4B4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009143FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085D1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B677FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CA5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A782FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009B58FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B261FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008E9AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0BCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DA9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0061AEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00825FFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008065FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00945DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009567FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007DC4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E73FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008F9CFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AD96FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008966FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0073B1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007662FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0053B6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A1A3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00967BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007777FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005BA6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009E00FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00736AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C92FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007497FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A59AFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00969DFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AE5EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008AC1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008654FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B1A6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00977EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0075CFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009683FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006D94FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B87FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A0EDFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AB7BFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,362 +558,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B7EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A8AFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008393FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008394FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00878EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008482FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008483FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008491FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009394FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009295FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008594FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008591FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007BA1FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D9DFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008489FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008389FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B91FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C93FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009194FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F97FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008097FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00898EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008890FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00857EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008383FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008095FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008193FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009291FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00928FFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008194FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007DABFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007DADFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008D9AFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0089A1FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F95FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007E98FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00959EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007E97FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008292FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A81FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008881FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008296FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008093FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009397FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009195FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007E92FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006DB0FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006CB0FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D98FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C99FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D99FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008B9AFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A9AFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B94FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A95FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B95FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008877FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A75FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00798CFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00798EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008896FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008897FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007D94FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007C91FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0068ABFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006AACFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008388FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00818CFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00738DFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00879AFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007995FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0085ACFF"/>
+        <fgColor rgb="00856EFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009CD1FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -428,127 +573,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0097A0FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0098A0FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0092A0FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A1A9FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A4AAFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00899EFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008D96FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008C99FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008689FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00868BFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008499FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00849BFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008B97FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008A98FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007F96FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009197FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008D9DFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008C80FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008C7FFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008998FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008997FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008B93FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="008C93FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00889BFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00879CFF"/>
+        <fgColor rgb="009497FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008CC0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007D67FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008DBDFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A5FFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009D65FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B8B0FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008E84FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008D88FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0077AEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007974FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B588FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -570,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -678,6 +758,22 @@
     <xf numFmtId="0" fontId="0" fillId="102" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="103" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="104" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1405,40 +1501,40 @@
       <c r="A9" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.47</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="9" t="n">
         <v>1220</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <v>5.34</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="J9" s="9" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K9" s="8" t="n">
+      <c r="K9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="L9" s="9" t="n">
         <v>151</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="9" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1446,40 +1542,40 @@
       <c r="A10" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="10" t="n">
         <v>11.9</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>12.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>1260</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="10" t="n">
         <v>620</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10" t="n">
         <v>2.24</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="10" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="10" t="n">
         <v>139</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="10" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1487,40 +1583,40 @@
       <c r="A11" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>11.9</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.47</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>12.9</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>1260</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="11" t="n">
         <v>620</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="11" t="n">
         <v>1.95</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J11" s="11" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="11" t="n">
         <v>139</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M11" s="11" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1528,40 +1624,40 @@
       <c r="A12" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="12" t="n">
         <v>10.4</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.87</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>1250</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>620</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="12" t="n">
         <v>4.55</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="12" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="12" t="n">
         <v>60.5</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="12" t="n">
         <v>121</v>
       </c>
     </row>
@@ -1569,40 +1665,40 @@
       <c r="A13" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="13" t="n">
         <v>10.4</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.87</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="13" t="n">
         <v>13.8</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="13" t="n">
         <v>8.1</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="13" t="n">
         <v>1220</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="13" t="n">
         <v>4.47</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="13" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="13" t="n">
         <v>118</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" s="13" t="n">
         <v>102</v>
       </c>
-      <c r="M13" s="2" t="n">
+      <c r="M13" s="13" t="n">
         <v>121</v>
       </c>
     </row>
@@ -1610,40 +1706,40 @@
       <c r="A14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="14" t="n">
         <v>10.4</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.87</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="14" t="n">
         <v>13.2</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="14" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="14" t="n">
         <v>1460</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="14" t="n">
         <v>720</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="14" t="n">
         <v>5.81</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="14" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="14" t="n">
         <v>51.1</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="14" t="n">
         <v>204</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="14" t="n">
         <v>129</v>
       </c>
     </row>
@@ -1651,40 +1747,40 @@
       <c r="A15" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="15" t="n">
         <v>10.4</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="15" t="n">
         <v>0.87</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="15" t="n">
         <v>13.2</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="15" t="n">
         <v>1410</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="15" t="n">
         <v>5.77</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="15" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K15" s="15" t="n">
         <v>55.8</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M15" s="15" t="n">
         <v>133</v>
       </c>
     </row>
@@ -1692,40 +1788,40 @@
       <c r="A16" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="16" t="n">
         <v>0.87</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="16" t="n">
         <v>14.4</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="16" t="n">
         <v>8.1</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="16" t="n">
         <v>1280</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="16" t="n">
         <v>630</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I16" s="16" t="n">
         <v>2.66</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J16" s="16" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="16" t="n">
         <v>56.8</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="16" t="n">
         <v>130</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="16" t="n">
         <v>109</v>
       </c>
     </row>
@@ -1733,40 +1829,40 @@
       <c r="A17" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="17" t="n">
         <v>10.4</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>0.87</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>14.1</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="17" t="n">
         <v>8.1</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="17" t="n">
         <v>1290</v>
       </c>
-      <c r="G17" s="14" t="n">
+      <c r="G17" s="17" t="n">
         <v>640</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H17" s="17" t="n">
         <v>36</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="17" t="n">
         <v>3.38</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="17" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="17" t="n">
         <v>52.8</v>
       </c>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="17" t="n">
         <v>122</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="17" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1774,40 +1870,40 @@
       <c r="A18" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="18" t="n">
         <v>10.4</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="18" t="n">
         <v>0.87</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="18" t="n">
         <v>14.6</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="18" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="18" t="n">
         <v>930</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="18" t="n">
         <v>460</v>
       </c>
-      <c r="H18" s="15" t="n">
+      <c r="H18" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="I18" s="15" t="n">
+      <c r="I18" s="18" t="n">
         <v>5.88</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="18" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K18" s="15" t="n">
+      <c r="K18" s="18" t="n">
         <v>5.16</v>
       </c>
-      <c r="L18" s="15" t="n">
+      <c r="L18" s="18" t="n">
         <v>204</v>
       </c>
-      <c r="M18" s="15" t="n">
+      <c r="M18" s="18" t="n">
         <v>59</v>
       </c>
     </row>
@@ -1815,40 +1911,40 @@
       <c r="A19" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="19" t="n">
         <v>10.4</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="19" t="n">
         <v>0.87</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="19" t="n">
         <v>14.8</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="19" t="n">
         <v>940</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="19" t="n">
         <v>460</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="16" t="n">
+      <c r="I19" s="19" t="n">
         <v>6.02</v>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="19" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K19" s="16" t="n">
+      <c r="K19" s="19" t="n">
         <v>127</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="19" t="n">
         <v>208</v>
       </c>
-      <c r="M19" s="16" t="n">
+      <c r="M19" s="19" t="n">
         <v>63</v>
       </c>
     </row>
@@ -1856,40 +1952,40 @@
       <c r="A20" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="20" t="n">
         <v>10.4</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="20" t="n">
         <v>0.87</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="20" t="n">
         <v>14.3</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="20" t="n">
         <v>8.1</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="20" t="n">
         <v>1230</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="20" t="n">
         <v>610</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="I20" s="17" t="n">
+      <c r="I20" s="20" t="n">
         <v>2.93</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="20" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="K20" s="20" t="n">
         <v>57.9</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="20" t="n">
         <v>159</v>
       </c>
-      <c r="M20" s="17" t="n">
+      <c r="M20" s="20" t="n">
         <v>102</v>
       </c>
     </row>
@@ -1897,40 +1993,40 @@
       <c r="A21" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="21" t="n">
         <v>10.4</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="21" t="n">
         <v>0.87</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="21" t="n">
         <v>14.4</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="21" t="n">
         <v>8.1</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="21" t="n">
         <v>1290</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="21" t="n">
         <v>640</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="21" t="n">
         <v>3.48</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="21" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K21" s="21" t="n">
         <v>53.9</v>
       </c>
-      <c r="L21" s="18" t="n">
+      <c r="L21" s="21" t="n">
         <v>163</v>
       </c>
-      <c r="M21" s="18" t="n">
+      <c r="M21" s="21" t="n">
         <v>102</v>
       </c>
     </row>
@@ -1938,40 +2034,40 @@
       <c r="A22" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>18.2</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="22" t="n">
         <v>0.77</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="22" t="n">
         <v>15.3</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="22" t="n">
         <v>7.8</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="22" t="n">
         <v>1280</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="22" t="n">
         <v>630</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="22" t="n">
         <v>110</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="I22" s="22" t="n">
         <v>2.03</v>
       </c>
-      <c r="J22" s="19" t="n">
+      <c r="J22" s="22" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="22" t="n">
         <v>622</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="22" t="n">
         <v>106</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="22" t="n">
         <v>128</v>
       </c>
     </row>
@@ -1979,40 +2075,40 @@
       <c r="A23" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="23" t="n">
         <v>18.2</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.77</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="23" t="n">
         <v>15.3</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="20" t="n">
+      <c r="F23" s="23" t="n">
         <v>1290</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="23" t="n">
         <v>630</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="23" t="n">
         <v>110</v>
       </c>
-      <c r="I23" s="20" t="n">
+      <c r="I23" s="23" t="n">
         <v>1.94</v>
       </c>
-      <c r="J23" s="20" t="n">
+      <c r="J23" s="23" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K23" s="20" t="n">
+      <c r="K23" s="23" t="n">
         <v>397</v>
       </c>
-      <c r="L23" s="20" t="n">
+      <c r="L23" s="23" t="n">
         <v>106</v>
       </c>
-      <c r="M23" s="20" t="n">
+      <c r="M23" s="23" t="n">
         <v>126</v>
       </c>
     </row>
@@ -2020,40 +2116,40 @@
       <c r="A24" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="24" t="n">
         <v>18.2</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="24" t="n">
         <v>0.77</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="24" t="n">
         <v>15.2</v>
       </c>
-      <c r="E24" s="21" t="n">
+      <c r="E24" s="24" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="24" t="n">
         <v>1370</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="24" t="n">
         <v>680</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="H24" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="24" t="n">
         <v>5.07</v>
       </c>
-      <c r="J24" s="21" t="n">
+      <c r="J24" s="24" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K24" s="21" t="n">
+      <c r="K24" s="24" t="n">
         <v>55.1</v>
       </c>
-      <c r="L24" s="21" t="n">
+      <c r="L24" s="24" t="n">
         <v>179</v>
       </c>
-      <c r="M24" s="21" t="n">
+      <c r="M24" s="24" t="n">
         <v>124</v>
       </c>
     </row>
@@ -2061,40 +2157,40 @@
       <c r="A25" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="25" t="n">
         <v>18.2</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="25" t="n">
         <v>0.77</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="25" t="n">
         <v>15.1</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="25" t="n">
         <v>8.4</v>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F25" s="25" t="n">
         <v>1400</v>
       </c>
-      <c r="G25" s="22" t="n">
+      <c r="G25" s="25" t="n">
         <v>680</v>
       </c>
-      <c r="H25" s="22" t="n">
+      <c r="H25" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="25" t="n">
         <v>4.51</v>
       </c>
-      <c r="J25" s="22" t="n">
+      <c r="J25" s="25" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="K25" s="25" t="n">
         <v>46.7</v>
       </c>
-      <c r="L25" s="22" t="n">
+      <c r="L25" s="25" t="n">
         <v>167</v>
       </c>
-      <c r="M25" s="22" t="n">
+      <c r="M25" s="25" t="n">
         <v>126</v>
       </c>
     </row>
@@ -2102,40 +2198,40 @@
       <c r="A26" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="26" t="n">
         <v>18.2</v>
       </c>
-      <c r="C26" s="23" t="n">
+      <c r="C26" s="26" t="n">
         <v>0.77</v>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="26" t="n">
         <v>15.4</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="26" t="n">
         <v>1480</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="H26" s="23" t="n">
+      <c r="H26" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="26" t="n">
         <v>1.57</v>
       </c>
-      <c r="J26" s="23" t="n">
+      <c r="J26" s="26" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="26" t="n">
         <v>58.7</v>
       </c>
-      <c r="L26" s="23" t="n">
+      <c r="L26" s="26" t="n">
         <v>151</v>
       </c>
-      <c r="M26" s="23" t="n">
+      <c r="M26" s="26" t="n">
         <v>128</v>
       </c>
     </row>
@@ -2143,40 +2239,40 @@
       <c r="A27" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="24" t="n">
+      <c r="B27" s="27" t="n">
         <v>18.2</v>
       </c>
-      <c r="C27" s="24" t="n">
+      <c r="C27" s="27" t="n">
         <v>0.77</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="27" t="n">
         <v>15.2</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="27" t="n">
         <v>1430</v>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="27" t="n">
         <v>710</v>
       </c>
-      <c r="H27" s="24" t="n">
+      <c r="H27" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="I27" s="24" t="n">
+      <c r="I27" s="27" t="n">
         <v>1.52</v>
       </c>
-      <c r="J27" s="24" t="n">
+      <c r="J27" s="27" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K27" s="24" t="n">
+      <c r="K27" s="27" t="n">
         <v>78.3</v>
       </c>
-      <c r="L27" s="24" t="n">
+      <c r="L27" s="27" t="n">
         <v>147</v>
       </c>
-      <c r="M27" s="24" t="n">
+      <c r="M27" s="27" t="n">
         <v>130</v>
       </c>
     </row>
@@ -2184,40 +2280,40 @@
       <c r="A28" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="28" t="n">
         <v>18.2</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="28" t="n">
         <v>0.77</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="28" t="n">
         <v>15.2</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="28" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="28" t="n">
         <v>990</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="28" t="n">
         <v>490</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="I28" s="28" t="n">
         <v>5.3</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="28" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K28" s="4" t="n">
+      <c r="K28" s="28" t="n">
         <v>2.68</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="28" t="n">
         <v>212</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="M28" s="28" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2225,40 +2321,40 @@
       <c r="A29" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="29" t="n">
         <v>18.2</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="29" t="n">
         <v>0.77</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="29" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="29" t="n">
         <v>970</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="29" t="n">
         <v>480</v>
       </c>
-      <c r="H29" s="25" t="n">
+      <c r="H29" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" s="25" t="n">
+      <c r="I29" s="29" t="n">
         <v>5.53</v>
       </c>
-      <c r="J29" s="25" t="n">
+      <c r="J29" s="29" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K29" s="25" t="n">
+      <c r="K29" s="29" t="n">
         <v>3.4</v>
       </c>
-      <c r="L29" s="25" t="n">
+      <c r="L29" s="29" t="n">
         <v>204</v>
       </c>
-      <c r="M29" s="25" t="n">
+      <c r="M29" s="29" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2266,40 +2362,40 @@
       <c r="A30" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="30" t="n">
         <v>18.2</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="30" t="n">
         <v>0.77</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="30" t="n">
         <v>15.4</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="30" t="n">
         <v>1330</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="30" t="n">
         <v>660</v>
       </c>
-      <c r="H30" s="26" t="n">
+      <c r="H30" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="30" t="n">
         <v>1.8</v>
       </c>
-      <c r="J30" s="26" t="n">
+      <c r="J30" s="30" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K30" s="26" t="n">
+      <c r="K30" s="30" t="n">
         <v>88.5</v>
       </c>
-      <c r="L30" s="26" t="n">
+      <c r="L30" s="30" t="n">
         <v>155</v>
       </c>
-      <c r="M30" s="26" t="n">
+      <c r="M30" s="30" t="n">
         <v>105</v>
       </c>
     </row>
@@ -2307,40 +2403,40 @@
       <c r="A31" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="31" t="n">
         <v>18.2</v>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="31" t="n">
         <v>0.77</v>
       </c>
-      <c r="D31" s="27" t="n">
+      <c r="D31" s="31" t="n">
         <v>15.5</v>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="F31" s="27" t="n">
+      <c r="F31" s="31" t="n">
         <v>1290</v>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="G31" s="31" t="n">
         <v>640</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="I31" s="27" t="n">
+      <c r="I31" s="31" t="n">
         <v>1.83</v>
       </c>
-      <c r="J31" s="27" t="n">
+      <c r="J31" s="31" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K31" s="27" t="n">
+      <c r="K31" s="31" t="n">
         <v>59.8</v>
       </c>
-      <c r="L31" s="27" t="n">
+      <c r="L31" s="31" t="n">
         <v>163</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="31" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2348,40 +2444,40 @@
       <c r="A32" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" s="32" t="n">
         <v>14.4</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="32" t="n">
         <v>15.6</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" s="32" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="F32" s="32" t="n">
         <v>1240</v>
       </c>
-      <c r="G32" s="28" t="n">
+      <c r="G32" s="32" t="n">
         <v>610</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" s="32" t="n">
         <v>4.59</v>
       </c>
-      <c r="J32" s="28" t="n">
+      <c r="J32" s="32" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K32" s="28" t="n">
+      <c r="K32" s="32" t="n">
         <v>40.8</v>
       </c>
-      <c r="L32" s="28" t="n">
+      <c r="L32" s="32" t="n">
         <v>110</v>
       </c>
-      <c r="M32" s="28" t="n">
+      <c r="M32" s="32" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2389,40 +2485,40 @@
       <c r="A33" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="33" t="n">
         <v>14.4</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="33" t="n">
         <v>16.1</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="33" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="33" t="n">
         <v>1240</v>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G33" s="33" t="n">
         <v>610</v>
       </c>
-      <c r="H33" s="29" t="n">
+      <c r="H33" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="I33" s="29" t="n">
+      <c r="I33" s="33" t="n">
         <v>4.32</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="33" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K33" s="29" t="n">
+      <c r="K33" s="33" t="n">
         <v>44.8</v>
       </c>
-      <c r="L33" s="29" t="n">
+      <c r="L33" s="33" t="n">
         <v>106</v>
       </c>
-      <c r="M33" s="29" t="n">
+      <c r="M33" s="33" t="n">
         <v>99</v>
       </c>
     </row>
@@ -2430,40 +2526,40 @@
       <c r="A34" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="34" t="n">
         <v>14.4</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="34" t="n">
         <v>0.4</v>
       </c>
-      <c r="D34" s="30" t="n">
+      <c r="D34" s="34" t="n">
         <v>17.1</v>
       </c>
-      <c r="E34" s="30" t="n">
+      <c r="E34" s="34" t="n">
         <v>8.5</v>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="34" t="n">
         <v>1480</v>
       </c>
-      <c r="G34" s="30" t="n">
+      <c r="G34" s="34" t="n">
         <v>730</v>
       </c>
-      <c r="H34" s="30" t="n">
+      <c r="H34" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="I34" s="30" t="n">
+      <c r="I34" s="34" t="n">
         <v>7.65</v>
       </c>
-      <c r="J34" s="30" t="n">
+      <c r="J34" s="34" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K34" s="30" t="n">
+      <c r="K34" s="34" t="n">
         <v>247</v>
       </c>
-      <c r="L34" s="30" t="n">
+      <c r="L34" s="34" t="n">
         <v>179</v>
       </c>
-      <c r="M34" s="30" t="n">
+      <c r="M34" s="34" t="n">
         <v>141</v>
       </c>
     </row>
@@ -2471,40 +2567,40 @@
       <c r="A35" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="35" t="n">
         <v>14.4</v>
       </c>
-      <c r="C35" s="31" t="n">
+      <c r="C35" s="35" t="n">
         <v>0.4</v>
       </c>
-      <c r="D35" s="31" t="n">
+      <c r="D35" s="35" t="n">
         <v>16.9</v>
       </c>
-      <c r="E35" s="31" t="n">
+      <c r="E35" s="35" t="n">
         <v>8.4</v>
       </c>
-      <c r="F35" s="31" t="n">
+      <c r="F35" s="35" t="n">
         <v>1470</v>
       </c>
-      <c r="G35" s="31" t="n">
+      <c r="G35" s="35" t="n">
         <v>730</v>
       </c>
-      <c r="H35" s="31" t="n">
+      <c r="H35" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="I35" s="31" t="n">
+      <c r="I35" s="35" t="n">
         <v>7.05</v>
       </c>
-      <c r="J35" s="31" t="n">
+      <c r="J35" s="35" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K35" s="31" t="n">
+      <c r="K35" s="35" t="n">
         <v>362</v>
       </c>
-      <c r="L35" s="31" t="n">
+      <c r="L35" s="35" t="n">
         <v>188</v>
       </c>
-      <c r="M35" s="31" t="n">
+      <c r="M35" s="35" t="n">
         <v>140</v>
       </c>
     </row>
@@ -2512,40 +2608,40 @@
       <c r="A36" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="36" t="n">
         <v>14.4</v>
       </c>
-      <c r="C36" s="32" t="n">
+      <c r="C36" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="D36" s="32" t="n">
+      <c r="D36" s="36" t="n">
         <v>16.6</v>
       </c>
-      <c r="E36" s="32" t="n">
+      <c r="E36" s="36" t="n">
         <v>8.1</v>
       </c>
-      <c r="F36" s="32" t="n">
+      <c r="F36" s="36" t="n">
         <v>1310</v>
       </c>
-      <c r="G36" s="32" t="n">
+      <c r="G36" s="36" t="n">
         <v>650</v>
       </c>
-      <c r="H36" s="32" t="n">
+      <c r="H36" s="36" t="n">
         <v>46</v>
       </c>
-      <c r="I36" s="32" t="n">
+      <c r="I36" s="36" t="n">
         <v>1.68</v>
       </c>
-      <c r="J36" s="32" t="n">
+      <c r="J36" s="36" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K36" s="32" t="n">
+      <c r="K36" s="36" t="n">
         <v>91.5</v>
       </c>
-      <c r="L36" s="32" t="n">
+      <c r="L36" s="36" t="n">
         <v>135</v>
       </c>
-      <c r="M36" s="32" t="n">
+      <c r="M36" s="36" t="n">
         <v>116</v>
       </c>
     </row>
@@ -2553,40 +2649,40 @@
       <c r="A37" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B37" s="33" t="n">
+      <c r="B37" s="37" t="n">
         <v>14.4</v>
       </c>
-      <c r="C37" s="33" t="n">
+      <c r="C37" s="37" t="n">
         <v>0.4</v>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D37" s="37" t="n">
         <v>16.6</v>
       </c>
-      <c r="E37" s="33" t="n">
+      <c r="E37" s="37" t="n">
         <v>8.1</v>
       </c>
-      <c r="F37" s="33" t="n">
+      <c r="F37" s="37" t="n">
         <v>1360</v>
       </c>
-      <c r="G37" s="33" t="n">
+      <c r="G37" s="37" t="n">
         <v>670</v>
       </c>
-      <c r="H37" s="33" t="n">
+      <c r="H37" s="37" t="n">
         <v>46</v>
       </c>
-      <c r="I37" s="33" t="n">
+      <c r="I37" s="37" t="n">
         <v>2.4</v>
       </c>
-      <c r="J37" s="33" t="n">
+      <c r="J37" s="37" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K37" s="33" t="n">
+      <c r="K37" s="37" t="n">
         <v>133</v>
       </c>
-      <c r="L37" s="33" t="n">
+      <c r="L37" s="37" t="n">
         <v>135</v>
       </c>
-      <c r="M37" s="33" t="n">
+      <c r="M37" s="37" t="n">
         <v>114</v>
       </c>
     </row>
@@ -2594,40 +2690,40 @@
       <c r="A38" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B38" s="34" t="n">
+      <c r="B38" s="16" t="n">
         <v>14.4</v>
       </c>
-      <c r="C38" s="34" t="n">
+      <c r="C38" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D38" s="34" t="n">
+      <c r="D38" s="16" t="n">
         <v>16.8</v>
       </c>
-      <c r="E38" s="34" t="n">
+      <c r="E38" s="16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F38" s="34" t="n">
+      <c r="F38" s="16" t="n">
         <v>990</v>
       </c>
-      <c r="G38" s="34" t="n">
+      <c r="G38" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="H38" s="34" t="n">
+      <c r="H38" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" s="34" t="n">
+      <c r="I38" s="16" t="n">
         <v>5.89</v>
       </c>
-      <c r="J38" s="34" t="n">
+      <c r="J38" s="16" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K38" s="34" t="n">
+      <c r="K38" s="16" t="n">
         <v>2.77</v>
       </c>
-      <c r="L38" s="34" t="n">
+      <c r="L38" s="16" t="n">
         <v>212</v>
       </c>
-      <c r="M38" s="34" t="n">
+      <c r="M38" s="16" t="n">
         <v>64</v>
       </c>
     </row>
@@ -2635,40 +2731,40 @@
       <c r="A39" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="38" t="n">
         <v>14.4</v>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="38" t="n">
         <v>0.4</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="38" t="n">
         <v>16.8</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="38" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F39" s="35" t="n">
+      <c r="F39" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="G39" s="35" t="n">
+      <c r="G39" s="38" t="n">
         <v>490</v>
       </c>
-      <c r="H39" s="35" t="n">
+      <c r="H39" s="38" t="n">
         <v>0.1</v>
       </c>
-      <c r="I39" s="35" t="n">
+      <c r="I39" s="38" t="n">
         <v>6.14</v>
       </c>
-      <c r="J39" s="35" t="n">
+      <c r="J39" s="38" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K39" s="35" t="n">
+      <c r="K39" s="38" t="n">
         <v>3.59</v>
       </c>
-      <c r="L39" s="35" t="n">
+      <c r="L39" s="38" t="n">
         <v>204</v>
       </c>
-      <c r="M39" s="35" t="n">
+      <c r="M39" s="38" t="n">
         <v>66</v>
       </c>
     </row>
@@ -2676,40 +2772,40 @@
       <c r="A40" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="33" t="n">
+      <c r="B40" s="39" t="n">
         <v>14.4</v>
       </c>
-      <c r="C40" s="33" t="n">
+      <c r="C40" s="39" t="n">
         <v>0.4</v>
       </c>
-      <c r="D40" s="33" t="n">
+      <c r="D40" s="39" t="n">
         <v>17.9</v>
       </c>
-      <c r="E40" s="33" t="n">
+      <c r="E40" s="39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F40" s="33" t="n">
+      <c r="F40" s="39" t="n">
         <v>1340</v>
       </c>
-      <c r="G40" s="33" t="n">
+      <c r="G40" s="39" t="n">
         <v>660</v>
       </c>
-      <c r="H40" s="33" t="n">
+      <c r="H40" s="39" t="n">
         <v>32</v>
       </c>
-      <c r="I40" s="33" t="n">
+      <c r="I40" s="39" t="n">
         <v>1.76</v>
       </c>
-      <c r="J40" s="33" t="n">
+      <c r="J40" s="39" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K40" s="33" t="n">
+      <c r="K40" s="39" t="n">
         <v>48.6</v>
       </c>
-      <c r="L40" s="33" t="n">
+      <c r="L40" s="39" t="n">
         <v>147</v>
       </c>
-      <c r="M40" s="33" t="n">
+      <c r="M40" s="39" t="n">
         <v>109</v>
       </c>
     </row>
@@ -2717,40 +2813,40 @@
       <c r="A41" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B41" s="36" t="n">
+      <c r="B41" s="40" t="n">
         <v>14.4</v>
       </c>
-      <c r="C41" s="36" t="n">
+      <c r="C41" s="40" t="n">
         <v>0.4</v>
       </c>
-      <c r="D41" s="36" t="n">
+      <c r="D41" s="40" t="n">
         <v>16.7</v>
       </c>
-      <c r="E41" s="36" t="n">
+      <c r="E41" s="40" t="n">
         <v>8.1</v>
       </c>
-      <c r="F41" s="36" t="n">
+      <c r="F41" s="40" t="n">
         <v>1330</v>
       </c>
-      <c r="G41" s="36" t="n">
+      <c r="G41" s="40" t="n">
         <v>660</v>
       </c>
-      <c r="H41" s="36" t="n">
+      <c r="H41" s="40" t="n">
         <v>32</v>
       </c>
-      <c r="I41" s="36" t="n">
+      <c r="I41" s="40" t="n">
         <v>1.75</v>
       </c>
-      <c r="J41" s="36" t="n">
+      <c r="J41" s="40" t="n">
         <v>39.9375</v>
       </c>
-      <c r="K41" s="36" t="n">
+      <c r="K41" s="40" t="n">
         <v>47</v>
       </c>
-      <c r="L41" s="36" t="n">
+      <c r="L41" s="40" t="n">
         <v>151</v>
       </c>
-      <c r="M41" s="36" t="n">
+      <c r="M41" s="40" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2758,40 +2854,40 @@
       <c r="A42" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="C42" s="37" t="n">
+      <c r="C42" s="41" t="n">
         <v>0.6</v>
       </c>
-      <c r="D42" s="37" t="n">
+      <c r="D42" s="41" t="n">
         <v>17.75</v>
       </c>
-      <c r="E42" s="37" t="n">
+      <c r="E42" s="41" t="n">
         <v>7.9</v>
       </c>
-      <c r="F42" s="37" t="n">
+      <c r="F42" s="41" t="n">
         <v>1210</v>
       </c>
-      <c r="G42" s="37" t="n">
+      <c r="G42" s="41" t="n">
         <v>600</v>
       </c>
-      <c r="H42" s="37" t="n">
+      <c r="H42" s="41" t="n">
         <v>92</v>
       </c>
-      <c r="I42" s="37" t="n">
+      <c r="I42" s="41" t="n">
         <v>1.79</v>
       </c>
-      <c r="J42" s="37" t="n">
+      <c r="J42" s="41" t="n">
         <v>27.5</v>
       </c>
-      <c r="K42" s="37" t="n">
+      <c r="K42" s="41" t="n">
         <v>1000</v>
       </c>
-      <c r="L42" s="37" t="n">
+      <c r="L42" s="41" t="n">
         <v>114</v>
       </c>
-      <c r="M42" s="37" t="n">
+      <c r="M42" s="41" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2799,40 +2895,40 @@
       <c r="A43" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="38" t="n">
+      <c r="B43" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="C43" s="38" t="n">
+      <c r="C43" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="D43" s="38" t="n">
+      <c r="D43" s="42" t="n">
         <v>18.05</v>
       </c>
-      <c r="E43" s="38" t="n">
+      <c r="E43" s="42" t="n">
         <v>7.7</v>
       </c>
-      <c r="F43" s="38" t="n">
+      <c r="F43" s="42" t="n">
         <v>1170</v>
       </c>
-      <c r="G43" s="38" t="n">
+      <c r="G43" s="42" t="n">
         <v>580</v>
       </c>
-      <c r="H43" s="38" t="n">
+      <c r="H43" s="42" t="n">
         <v>92</v>
       </c>
-      <c r="I43" s="38" t="n">
+      <c r="I43" s="42" t="n">
         <v>1.35</v>
       </c>
-      <c r="J43" s="38" t="n">
+      <c r="J43" s="42" t="n">
         <v>27.5</v>
       </c>
-      <c r="K43" s="38" t="n">
+      <c r="K43" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="L43" s="38" t="n">
+      <c r="L43" s="42" t="n">
         <v>114</v>
       </c>
-      <c r="M43" s="38" t="n">
+      <c r="M43" s="42" t="n">
         <v>95</v>
       </c>
     </row>
@@ -2840,40 +2936,40 @@
       <c r="A44" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="C44" s="39" t="n">
+      <c r="C44" s="43" t="n">
         <v>0.6</v>
       </c>
-      <c r="D44" s="39" t="n">
+      <c r="D44" s="43" t="n">
         <v>18.15</v>
       </c>
-      <c r="E44" s="39" t="n">
+      <c r="E44" s="43" t="n">
         <v>8.1</v>
       </c>
-      <c r="F44" s="39" t="n">
+      <c r="F44" s="43" t="n">
         <v>1000</v>
       </c>
-      <c r="G44" s="39" t="n">
+      <c r="G44" s="43" t="n">
         <v>490</v>
       </c>
-      <c r="H44" s="39" t="n">
+      <c r="H44" s="43" t="n">
         <v>50</v>
       </c>
-      <c r="I44" s="39" t="n">
+      <c r="I44" s="43" t="n">
         <v>4.97</v>
       </c>
-      <c r="J44" s="39" t="n">
+      <c r="J44" s="43" t="n">
         <v>27.5</v>
       </c>
-      <c r="K44" s="39" t="n">
+      <c r="K44" s="43" t="n">
         <v>238</v>
       </c>
-      <c r="L44" s="39" t="n">
+      <c r="L44" s="43" t="n">
         <v>135</v>
       </c>
-      <c r="M44" s="39" t="n">
+      <c r="M44" s="43" t="n">
         <v>79</v>
       </c>
     </row>
@@ -2881,40 +2977,40 @@
       <c r="A45" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B45" s="40" t="n">
+      <c r="B45" s="44" t="n">
         <v>18</v>
       </c>
-      <c r="C45" s="40" t="n">
+      <c r="C45" s="44" t="n">
         <v>0.6</v>
       </c>
-      <c r="D45" s="40" t="n">
+      <c r="D45" s="44" t="n">
         <v>18.15</v>
       </c>
-      <c r="E45" s="40" t="n">
+      <c r="E45" s="44" t="n">
         <v>8.1</v>
       </c>
-      <c r="F45" s="40" t="n">
+      <c r="F45" s="44" t="n">
         <v>1000</v>
       </c>
-      <c r="G45" s="40" t="n">
+      <c r="G45" s="44" t="n">
         <v>490</v>
       </c>
-      <c r="H45" s="40" t="n">
+      <c r="H45" s="44" t="n">
         <v>50</v>
       </c>
-      <c r="I45" s="40" t="n">
+      <c r="I45" s="44" t="n">
         <v>3.12</v>
       </c>
-      <c r="J45" s="40" t="n">
+      <c r="J45" s="44" t="n">
         <v>27.5</v>
       </c>
-      <c r="K45" s="40" t="n">
+      <c r="K45" s="44" t="n">
         <v>351</v>
       </c>
-      <c r="L45" s="40" t="n">
+      <c r="L45" s="44" t="n">
         <v>139</v>
       </c>
-      <c r="M45" s="40" t="n">
+      <c r="M45" s="44" t="n">
         <v>81</v>
       </c>
     </row>
@@ -2922,40 +3018,40 @@
       <c r="A46" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B46" s="41" t="n">
+      <c r="B46" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="C46" s="41" t="n">
+      <c r="C46" s="45" t="n">
         <v>0.6</v>
       </c>
-      <c r="D46" s="41" t="n">
+      <c r="D46" s="45" t="n">
         <v>18.2</v>
       </c>
-      <c r="E46" s="41" t="n">
+      <c r="E46" s="45" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F46" s="41" t="n">
+      <c r="F46" s="45" t="n">
         <v>1310</v>
       </c>
-      <c r="G46" s="41" t="n">
+      <c r="G46" s="45" t="n">
         <v>640</v>
       </c>
-      <c r="H46" s="41" t="n">
+      <c r="H46" s="45" t="n">
         <v>64</v>
       </c>
-      <c r="I46" s="41" t="n">
+      <c r="I46" s="45" t="n">
         <v>1.71</v>
       </c>
-      <c r="J46" s="41" t="n">
+      <c r="J46" s="45" t="n">
         <v>47.5</v>
       </c>
-      <c r="K46" s="41" t="n">
+      <c r="K46" s="45" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="L46" s="41" t="n">
+      <c r="L46" s="45" t="n">
         <v>135</v>
       </c>
-      <c r="M46" s="41" t="n">
+      <c r="M46" s="45" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2963,40 +3059,40 @@
       <c r="A47" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="42" t="n">
+      <c r="B47" s="46" t="n">
         <v>18</v>
       </c>
-      <c r="C47" s="42" t="n">
+      <c r="C47" s="46" t="n">
         <v>0.6</v>
       </c>
-      <c r="D47" s="42" t="n">
+      <c r="D47" s="46" t="n">
         <v>18.1</v>
       </c>
-      <c r="E47" s="42" t="n">
+      <c r="E47" s="46" t="n">
         <v>8.1</v>
       </c>
-      <c r="F47" s="42" t="n">
+      <c r="F47" s="46" t="n">
         <v>1320</v>
       </c>
-      <c r="G47" s="42" t="n">
+      <c r="G47" s="46" t="n">
         <v>650</v>
       </c>
-      <c r="H47" s="42" t="n">
+      <c r="H47" s="46" t="n">
         <v>64</v>
       </c>
-      <c r="I47" s="42" t="n">
+      <c r="I47" s="46" t="n">
         <v>0.97</v>
       </c>
-      <c r="J47" s="42" t="n">
+      <c r="J47" s="46" t="n">
         <v>47.5</v>
       </c>
-      <c r="K47" s="42" t="n">
+      <c r="K47" s="46" t="n">
         <v>109</v>
       </c>
-      <c r="L47" s="42" t="n">
+      <c r="L47" s="46" t="n">
         <v>130</v>
       </c>
-      <c r="M47" s="42" t="n">
+      <c r="M47" s="46" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3004,40 +3100,40 @@
       <c r="A48" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="43" t="n">
+      <c r="B48" s="47" t="n">
         <v>18</v>
       </c>
-      <c r="C48" s="43" t="n">
+      <c r="C48" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="D48" s="43" t="n">
+      <c r="D48" s="47" t="n">
         <v>18.4</v>
       </c>
-      <c r="E48" s="43" t="n">
+      <c r="E48" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="43" t="n">
+      <c r="F48" s="47" t="n">
         <v>750</v>
       </c>
-      <c r="G48" s="43" t="n">
+      <c r="G48" s="47" t="n">
         <v>370</v>
       </c>
-      <c r="H48" s="43" t="n">
+      <c r="H48" s="47" t="n">
         <v>26</v>
       </c>
-      <c r="I48" s="43" t="n">
+      <c r="I48" s="47" t="n">
         <v>4.65</v>
       </c>
-      <c r="J48" s="43" t="n">
+      <c r="J48" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="K48" s="43" t="n">
+      <c r="K48" s="47" t="n">
         <v>11.6</v>
       </c>
-      <c r="L48" s="43" t="n">
+      <c r="L48" s="47" t="n">
         <v>155</v>
       </c>
-      <c r="M48" s="43" t="n">
+      <c r="M48" s="47" t="n">
         <v>50</v>
       </c>
     </row>
@@ -3045,40 +3141,40 @@
       <c r="A49" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B49" s="43" t="n">
+      <c r="B49" s="48" t="n">
         <v>18</v>
       </c>
-      <c r="C49" s="43" t="n">
+      <c r="C49" s="48" t="n">
         <v>0.6</v>
       </c>
-      <c r="D49" s="43" t="n">
+      <c r="D49" s="48" t="n">
         <v>18.35</v>
       </c>
-      <c r="E49" s="43" t="n">
+      <c r="E49" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="F49" s="43" t="n">
+      <c r="F49" s="48" t="n">
         <v>750</v>
       </c>
-      <c r="G49" s="43" t="n">
+      <c r="G49" s="48" t="n">
         <v>370</v>
       </c>
-      <c r="H49" s="43" t="n">
+      <c r="H49" s="48" t="n">
         <v>26</v>
       </c>
-      <c r="I49" s="43" t="n">
+      <c r="I49" s="48" t="n">
         <v>4.84</v>
       </c>
-      <c r="J49" s="43" t="n">
+      <c r="J49" s="48" t="n">
         <v>25</v>
       </c>
-      <c r="K49" s="43" t="n">
+      <c r="K49" s="48" t="n">
         <v>13.5</v>
       </c>
-      <c r="L49" s="43" t="n">
+      <c r="L49" s="48" t="n">
         <v>159</v>
       </c>
-      <c r="M49" s="43" t="n">
+      <c r="M49" s="48" t="n">
         <v>48</v>
       </c>
     </row>
@@ -3086,40 +3182,40 @@
       <c r="A50" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B50" s="44" t="n">
+      <c r="B50" s="49" t="n">
         <v>18</v>
       </c>
-      <c r="C50" s="44" t="n">
+      <c r="C50" s="49" t="n">
         <v>0.6</v>
       </c>
-      <c r="D50" s="44" t="n">
+      <c r="D50" s="49" t="n">
         <v>18.35</v>
       </c>
-      <c r="E50" s="44" t="n">
+      <c r="E50" s="49" t="n">
         <v>8.1</v>
       </c>
-      <c r="F50" s="44" t="n">
+      <c r="F50" s="49" t="n">
         <v>1350</v>
       </c>
-      <c r="G50" s="44" t="n">
+      <c r="G50" s="49" t="n">
         <v>670</v>
       </c>
-      <c r="H50" s="44" t="n">
+      <c r="H50" s="49" t="n">
         <v>56</v>
       </c>
-      <c r="I50" s="44" t="n">
+      <c r="I50" s="49" t="n">
         <v>1.29</v>
       </c>
-      <c r="J50" s="44" t="n">
+      <c r="J50" s="49" t="n">
         <v>35</v>
       </c>
-      <c r="K50" s="44" t="n">
+      <c r="K50" s="49" t="n">
         <v>93.8</v>
       </c>
-      <c r="L50" s="44" t="n">
+      <c r="L50" s="49" t="n">
         <v>143</v>
       </c>
-      <c r="M50" s="44" t="n">
+      <c r="M50" s="49" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3127,40 +3223,40 @@
       <c r="A51" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="44" t="n">
+      <c r="B51" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="C51" s="44" t="n">
+      <c r="C51" s="50" t="n">
         <v>0.6</v>
       </c>
-      <c r="D51" s="44" t="n">
+      <c r="D51" s="50" t="n">
         <v>18.4</v>
       </c>
-      <c r="E51" s="44" t="n">
+      <c r="E51" s="50" t="n">
         <v>8.1</v>
       </c>
-      <c r="F51" s="44" t="n">
+      <c r="F51" s="50" t="n">
         <v>1340</v>
       </c>
-      <c r="G51" s="44" t="n">
+      <c r="G51" s="50" t="n">
         <v>660</v>
       </c>
-      <c r="H51" s="44" t="n">
+      <c r="H51" s="50" t="n">
         <v>56</v>
       </c>
-      <c r="I51" s="44" t="n">
+      <c r="I51" s="50" t="n">
         <v>1.45</v>
       </c>
-      <c r="J51" s="44" t="n">
+      <c r="J51" s="50" t="n">
         <v>35</v>
       </c>
-      <c r="K51" s="44" t="n">
+      <c r="K51" s="50" t="n">
         <v>159</v>
       </c>
-      <c r="L51" s="44" t="n">
+      <c r="L51" s="50" t="n">
         <v>147</v>
       </c>
-      <c r="M51" s="44" t="n">
+      <c r="M51" s="50" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3168,40 +3264,40 @@
       <c r="A52" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B52" s="45" t="n">
+      <c r="B52" s="51" t="n">
         <v>14.3</v>
       </c>
-      <c r="C52" s="45" t="n">
+      <c r="C52" s="51" t="n">
         <v>0.54</v>
       </c>
-      <c r="D52" s="45" t="n">
+      <c r="D52" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="E52" s="45" t="n">
+      <c r="E52" s="51" t="n">
         <v>8.1</v>
       </c>
-      <c r="F52" s="45" t="n">
+      <c r="F52" s="51" t="n">
         <v>1370</v>
       </c>
-      <c r="G52" s="45" t="n">
+      <c r="G52" s="51" t="n">
         <v>680</v>
       </c>
-      <c r="H52" s="45" t="n">
+      <c r="H52" s="51" t="n">
         <v>56</v>
       </c>
-      <c r="I52" s="45" t="n">
+      <c r="I52" s="51" t="n">
         <v>3.6</v>
       </c>
-      <c r="J52" s="45" t="n">
+      <c r="J52" s="51" t="n">
         <v>25</v>
       </c>
-      <c r="K52" s="45" t="n">
+      <c r="K52" s="51" t="n">
         <v>199</v>
       </c>
-      <c r="L52" s="45" t="n">
+      <c r="L52" s="51" t="n">
         <v>106</v>
       </c>
-      <c r="M52" s="45" t="n">
+      <c r="M52" s="51" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3209,40 +3305,40 @@
       <c r="A53" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B53" s="44" t="n">
+      <c r="B53" s="52" t="n">
         <v>14.3</v>
       </c>
-      <c r="C53" s="44" t="n">
+      <c r="C53" s="52" t="n">
         <v>0.54</v>
       </c>
-      <c r="D53" s="44" t="n">
+      <c r="D53" s="52" t="n">
         <v>25.5</v>
       </c>
-      <c r="E53" s="44" t="n">
+      <c r="E53" s="52" t="n">
         <v>8.1</v>
       </c>
-      <c r="F53" s="44" t="n">
+      <c r="F53" s="52" t="n">
         <v>1400</v>
       </c>
-      <c r="G53" s="44" t="n">
+      <c r="G53" s="52" t="n">
         <v>690</v>
       </c>
-      <c r="H53" s="44" t="n">
+      <c r="H53" s="52" t="n">
         <v>56</v>
       </c>
-      <c r="I53" s="44" t="n">
+      <c r="I53" s="52" t="n">
         <v>1.87</v>
       </c>
-      <c r="J53" s="44" t="n">
+      <c r="J53" s="52" t="n">
         <v>25</v>
       </c>
-      <c r="K53" s="44" t="n">
+      <c r="K53" s="52" t="n">
         <v>220</v>
       </c>
-      <c r="L53" s="44" t="n">
+      <c r="L53" s="52" t="n">
         <v>110</v>
       </c>
-      <c r="M53" s="44" t="n">
+      <c r="M53" s="52" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3250,40 +3346,40 @@
       <c r="A54" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B54" s="46" t="n">
+      <c r="B54" s="53" t="n">
         <v>14.3</v>
       </c>
-      <c r="C54" s="46" t="n">
+      <c r="C54" s="53" t="n">
         <v>0.54</v>
       </c>
-      <c r="D54" s="46" t="n">
+      <c r="D54" s="53" t="n">
         <v>23.6</v>
       </c>
-      <c r="E54" s="46" t="n">
+      <c r="E54" s="53" t="n">
         <v>8.4</v>
       </c>
-      <c r="F54" s="46" t="n">
+      <c r="F54" s="53" t="n">
         <v>1330</v>
       </c>
-      <c r="G54" s="46" t="n">
+      <c r="G54" s="53" t="n">
         <v>660</v>
       </c>
-      <c r="H54" s="46" t="n">
+      <c r="H54" s="53" t="n">
         <v>68.32649572649574</v>
       </c>
-      <c r="I54" s="46" t="n">
+      <c r="I54" s="53" t="n">
         <v>7.48</v>
       </c>
-      <c r="J54" s="46" t="n">
+      <c r="J54" s="53" t="n">
         <v>35</v>
       </c>
-      <c r="K54" s="46" t="n">
+      <c r="K54" s="53" t="n">
         <v>39.9</v>
       </c>
-      <c r="L54" s="46" t="n">
+      <c r="L54" s="53" t="n">
         <v>179</v>
       </c>
-      <c r="M54" s="46" t="n">
+      <c r="M54" s="53" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3291,40 +3387,40 @@
       <c r="A55" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B55" s="47" t="n">
+      <c r="B55" s="54" t="n">
         <v>14.3</v>
       </c>
-      <c r="C55" s="47" t="n">
+      <c r="C55" s="54" t="n">
         <v>0.54</v>
       </c>
-      <c r="D55" s="47" t="n">
+      <c r="D55" s="54" t="n">
         <v>24.3</v>
       </c>
-      <c r="E55" s="47" t="n">
+      <c r="E55" s="54" t="n">
         <v>8.4</v>
       </c>
-      <c r="F55" s="47" t="n">
+      <c r="F55" s="54" t="n">
         <v>1390</v>
       </c>
-      <c r="G55" s="47" t="n">
+      <c r="G55" s="54" t="n">
         <v>690</v>
       </c>
-      <c r="H55" s="47" t="n">
+      <c r="H55" s="54" t="n">
         <v>68.32649572649574</v>
       </c>
-      <c r="I55" s="47" t="n">
+      <c r="I55" s="54" t="n">
         <v>7.15</v>
       </c>
-      <c r="J55" s="47" t="n">
+      <c r="J55" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="K55" s="47" t="n">
+      <c r="K55" s="54" t="n">
         <v>49.9</v>
       </c>
-      <c r="L55" s="47" t="n">
+      <c r="L55" s="54" t="n">
         <v>175</v>
       </c>
-      <c r="M55" s="47" t="n">
+      <c r="M55" s="54" t="n">
         <v>118</v>
       </c>
     </row>
@@ -3332,40 +3428,40 @@
       <c r="A56" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B56" s="48" t="n">
+      <c r="B56" s="55" t="n">
         <v>14.3</v>
       </c>
-      <c r="C56" s="48" t="n">
+      <c r="C56" s="55" t="n">
         <v>0.54</v>
       </c>
-      <c r="D56" s="48" t="n">
+      <c r="D56" s="55" t="n">
         <v>16.1</v>
       </c>
-      <c r="E56" s="48" t="n">
+      <c r="E56" s="55" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F56" s="48" t="n">
+      <c r="F56" s="55" t="n">
         <v>1220</v>
       </c>
-      <c r="G56" s="48" t="n">
+      <c r="G56" s="55" t="n">
         <v>600</v>
       </c>
-      <c r="H56" s="48" t="n">
+      <c r="H56" s="55" t="n">
         <v>76</v>
       </c>
-      <c r="I56" s="48" t="n">
+      <c r="I56" s="55" t="n">
         <v>2.27</v>
       </c>
-      <c r="J56" s="48" t="n">
+      <c r="J56" s="55" t="n">
         <v>47.5</v>
       </c>
-      <c r="K56" s="48" t="n">
+      <c r="K56" s="55" t="n">
         <v>114</v>
       </c>
-      <c r="L56" s="48" t="n">
+      <c r="L56" s="55" t="n">
         <v>155</v>
       </c>
-      <c r="M56" s="48" t="n">
+      <c r="M56" s="55" t="n">
         <v>114</v>
       </c>
     </row>
@@ -3373,40 +3469,40 @@
       <c r="A57" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="B57" s="49" t="n">
+      <c r="B57" s="56" t="n">
         <v>14.3</v>
       </c>
-      <c r="C57" s="49" t="n">
+      <c r="C57" s="56" t="n">
         <v>0.54</v>
       </c>
-      <c r="D57" s="49" t="n">
+      <c r="D57" s="56" t="n">
         <v>28.1</v>
       </c>
-      <c r="E57" s="49" t="n">
+      <c r="E57" s="56" t="n">
         <v>8.1</v>
       </c>
-      <c r="F57" s="49" t="n">
+      <c r="F57" s="56" t="n">
         <v>1360</v>
       </c>
-      <c r="G57" s="49" t="n">
+      <c r="G57" s="56" t="n">
         <v>670</v>
       </c>
-      <c r="H57" s="49" t="n">
+      <c r="H57" s="56" t="n">
         <v>76</v>
       </c>
-      <c r="I57" s="49" t="n">
+      <c r="I57" s="56" t="n">
         <v>2.35</v>
       </c>
-      <c r="J57" s="49" t="n">
+      <c r="J57" s="56" t="n">
         <v>47.5</v>
       </c>
-      <c r="K57" s="49" t="n">
+      <c r="K57" s="56" t="n">
         <v>113</v>
       </c>
-      <c r="L57" s="49" t="n">
+      <c r="L57" s="56" t="n">
         <v>159</v>
       </c>
-      <c r="M57" s="49" t="n">
+      <c r="M57" s="56" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3414,40 +3510,40 @@
       <c r="A58" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="B58" s="50" t="n">
+      <c r="B58" s="57" t="n">
         <v>14.3</v>
       </c>
-      <c r="C58" s="50" t="n">
+      <c r="C58" s="57" t="n">
         <v>0.54</v>
       </c>
-      <c r="D58" s="50" t="n">
+      <c r="D58" s="57" t="n">
         <v>15.1</v>
       </c>
-      <c r="E58" s="50" t="n">
+      <c r="E58" s="57" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F58" s="50" t="n">
+      <c r="F58" s="57" t="n">
         <v>890</v>
       </c>
-      <c r="G58" s="50" t="n">
+      <c r="G58" s="57" t="n">
         <v>440</v>
       </c>
-      <c r="H58" s="50" t="n">
+      <c r="H58" s="57" t="n">
         <v>14</v>
       </c>
-      <c r="I58" s="50" t="n">
+      <c r="I58" s="57" t="n">
         <v>5.16</v>
       </c>
-      <c r="J58" s="50" t="n">
+      <c r="J58" s="57" t="n">
         <v>42.5</v>
       </c>
-      <c r="K58" s="50" t="n">
+      <c r="K58" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="L58" s="50" t="n">
+      <c r="L58" s="57" t="n">
         <v>196</v>
       </c>
-      <c r="M58" s="50" t="n">
+      <c r="M58" s="57" t="n">
         <v>54</v>
       </c>
     </row>
@@ -3455,40 +3551,40 @@
       <c r="A59" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="B59" s="51" t="n">
+      <c r="B59" s="58" t="n">
         <v>14.3</v>
       </c>
-      <c r="C59" s="51" t="n">
+      <c r="C59" s="58" t="n">
         <v>0.54</v>
       </c>
-      <c r="D59" s="51" t="n">
+      <c r="D59" s="58" t="n">
         <v>27.5</v>
       </c>
-      <c r="E59" s="51" t="n">
+      <c r="E59" s="58" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F59" s="51" t="n">
+      <c r="F59" s="58" t="n">
         <v>1000</v>
       </c>
-      <c r="G59" s="51" t="n">
+      <c r="G59" s="58" t="n">
         <v>490</v>
       </c>
-      <c r="H59" s="51" t="n">
+      <c r="H59" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="I59" s="51" t="n">
+      <c r="I59" s="58" t="n">
         <v>5.27</v>
       </c>
-      <c r="J59" s="51" t="n">
+      <c r="J59" s="58" t="n">
         <v>42.5</v>
       </c>
-      <c r="K59" s="51" t="n">
+      <c r="K59" s="58" t="n">
         <v>46.5</v>
       </c>
-      <c r="L59" s="51" t="n">
+      <c r="L59" s="58" t="n">
         <v>192</v>
       </c>
-      <c r="M59" s="51" t="n">
+      <c r="M59" s="58" t="n">
         <v>56</v>
       </c>
     </row>
@@ -3496,40 +3592,40 @@
       <c r="A60" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="B60" s="52" t="n">
+      <c r="B60" s="59" t="n">
         <v>14.3</v>
       </c>
-      <c r="C60" s="52" t="n">
+      <c r="C60" s="59" t="n">
         <v>0.54</v>
       </c>
-      <c r="D60" s="52" t="n">
+      <c r="D60" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="E60" s="52" t="n">
+      <c r="E60" s="59" t="n">
         <v>8.1</v>
       </c>
-      <c r="F60" s="52" t="n">
+      <c r="F60" s="59" t="n">
         <v>1450</v>
       </c>
-      <c r="G60" s="52" t="n">
+      <c r="G60" s="59" t="n">
         <v>720</v>
       </c>
-      <c r="H60" s="52" t="n">
+      <c r="H60" s="59" t="n">
         <v>14</v>
       </c>
-      <c r="I60" s="52" t="n">
+      <c r="I60" s="59" t="n">
         <v>1.48</v>
       </c>
-      <c r="J60" s="52" t="n">
+      <c r="J60" s="59" t="n">
         <v>45</v>
       </c>
-      <c r="K60" s="52" t="n">
+      <c r="K60" s="59" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="L60" s="52" t="n">
+      <c r="L60" s="59" t="n">
         <v>167</v>
       </c>
-      <c r="M60" s="52" t="n">
+      <c r="M60" s="59" t="n">
         <v>109</v>
       </c>
     </row>
@@ -3537,40 +3633,40 @@
       <c r="A61" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="B61" s="41" t="n">
+      <c r="B61" s="60" t="n">
         <v>14.3</v>
       </c>
-      <c r="C61" s="41" t="n">
+      <c r="C61" s="60" t="n">
         <v>0.54</v>
       </c>
-      <c r="D61" s="41" t="n">
+      <c r="D61" s="60" t="n">
         <v>25.1</v>
       </c>
-      <c r="E61" s="41" t="n">
+      <c r="E61" s="60" t="n">
         <v>8.1</v>
       </c>
-      <c r="F61" s="41" t="n">
+      <c r="F61" s="60" t="n">
         <v>1370</v>
       </c>
-      <c r="G61" s="41" t="n">
+      <c r="G61" s="60" t="n">
         <v>680</v>
       </c>
-      <c r="H61" s="41" t="n">
+      <c r="H61" s="60" t="n">
         <v>14</v>
       </c>
-      <c r="I61" s="41" t="n">
+      <c r="I61" s="60" t="n">
         <v>1.32</v>
       </c>
-      <c r="J61" s="41" t="n">
+      <c r="J61" s="60" t="n">
         <v>45</v>
       </c>
-      <c r="K61" s="41" t="n">
+      <c r="K61" s="60" t="n">
         <v>123</v>
       </c>
-      <c r="L61" s="41" t="n">
+      <c r="L61" s="60" t="n">
         <v>163</v>
       </c>
-      <c r="M61" s="41" t="n">
+      <c r="M61" s="60" t="n">
         <v>112</v>
       </c>
     </row>
@@ -3578,40 +3674,40 @@
       <c r="A62" s="1" t="n">
         <v>62</v>
       </c>
-      <c r="B62" s="53" t="n">
+      <c r="B62" s="61" t="n">
         <v>26</v>
       </c>
-      <c r="C62" s="53" t="n">
+      <c r="C62" s="61" t="n">
         <v>0.87</v>
       </c>
-      <c r="D62" s="53" t="n">
+      <c r="D62" s="61" t="n">
         <v>18.1</v>
       </c>
-      <c r="E62" s="53" t="n">
+      <c r="E62" s="61" t="n">
         <v>7.2</v>
       </c>
-      <c r="F62" s="53" t="n">
+      <c r="F62" s="61" t="n">
         <v>1430</v>
       </c>
-      <c r="G62" s="53" t="n">
+      <c r="G62" s="61" t="n">
         <v>710</v>
       </c>
-      <c r="H62" s="53" t="n">
+      <c r="H62" s="61" t="n">
         <v>650</v>
       </c>
-      <c r="I62" s="53" t="n">
+      <c r="I62" s="61" t="n">
         <v>1.12</v>
       </c>
-      <c r="J62" s="53" t="n">
+      <c r="J62" s="61" t="n">
         <v>30</v>
       </c>
-      <c r="K62" s="53" t="n">
+      <c r="K62" s="61" t="n">
         <v>1000</v>
       </c>
-      <c r="L62" s="53" t="n">
+      <c r="L62" s="61" t="n">
         <v>147</v>
       </c>
-      <c r="M62" s="53" t="n">
+      <c r="M62" s="61" t="n">
         <v>96.87179487179488</v>
       </c>
     </row>
@@ -3619,40 +3715,40 @@
       <c r="A63" s="1" t="n">
         <v>63</v>
       </c>
-      <c r="B63" s="54" t="n">
+      <c r="B63" s="62" t="n">
         <v>26</v>
       </c>
-      <c r="C63" s="54" t="n">
+      <c r="C63" s="62" t="n">
         <v>0.87</v>
       </c>
-      <c r="D63" s="54" t="n">
+      <c r="D63" s="62" t="n">
         <v>18.2</v>
       </c>
-      <c r="E63" s="54" t="n">
+      <c r="E63" s="62" t="n">
         <v>7.2</v>
       </c>
-      <c r="F63" s="54" t="n">
+      <c r="F63" s="62" t="n">
         <v>1450</v>
       </c>
-      <c r="G63" s="54" t="n">
+      <c r="G63" s="62" t="n">
         <v>720</v>
       </c>
-      <c r="H63" s="54" t="n">
+      <c r="H63" s="62" t="n">
         <v>650</v>
       </c>
-      <c r="I63" s="54" t="n">
+      <c r="I63" s="62" t="n">
         <v>0.85</v>
       </c>
-      <c r="J63" s="54" t="n">
+      <c r="J63" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="K63" s="54" t="n">
+      <c r="K63" s="62" t="n">
         <v>1000</v>
       </c>
-      <c r="L63" s="54" t="n">
+      <c r="L63" s="62" t="n">
         <v>151</v>
       </c>
-      <c r="M63" s="54" t="n">
+      <c r="M63" s="62" t="n">
         <v>96.87179487179488</v>
       </c>
     </row>
@@ -3660,40 +3756,40 @@
       <c r="A64" s="1" t="n">
         <v>64</v>
       </c>
-      <c r="B64" s="52" t="n">
+      <c r="B64" s="63" t="n">
         <v>26</v>
       </c>
-      <c r="C64" s="52" t="n">
+      <c r="C64" s="63" t="n">
         <v>0.87</v>
       </c>
-      <c r="D64" s="52" t="n">
+      <c r="D64" s="63" t="n">
         <v>18.1</v>
       </c>
-      <c r="E64" s="52" t="n">
+      <c r="E64" s="63" t="n">
         <v>8.4</v>
       </c>
-      <c r="F64" s="52" t="n">
+      <c r="F64" s="63" t="n">
         <v>1400</v>
       </c>
-      <c r="G64" s="52" t="n">
+      <c r="G64" s="63" t="n">
         <v>690</v>
       </c>
-      <c r="H64" s="52" t="n">
+      <c r="H64" s="63" t="n">
         <v>80</v>
       </c>
-      <c r="I64" s="52" t="n">
+      <c r="I64" s="63" t="n">
         <v>3.59</v>
       </c>
-      <c r="J64" s="52" t="n">
+      <c r="J64" s="63" t="n">
         <v>35</v>
       </c>
-      <c r="K64" s="52" t="n">
+      <c r="K64" s="63" t="n">
         <v>221</v>
       </c>
-      <c r="L64" s="52" t="n">
+      <c r="L64" s="63" t="n">
         <v>183</v>
       </c>
-      <c r="M64" s="52" t="n">
+      <c r="M64" s="63" t="n">
         <v>124</v>
       </c>
     </row>
@@ -3701,40 +3797,40 @@
       <c r="A65" s="1" t="n">
         <v>65</v>
       </c>
-      <c r="B65" s="55" t="n">
+      <c r="B65" s="64" t="n">
         <v>26</v>
       </c>
-      <c r="C65" s="55" t="n">
+      <c r="C65" s="64" t="n">
         <v>0.87</v>
       </c>
-      <c r="D65" s="55" t="n">
+      <c r="D65" s="64" t="n">
         <v>18.1</v>
       </c>
-      <c r="E65" s="55" t="n">
+      <c r="E65" s="64" t="n">
         <v>8.4</v>
       </c>
-      <c r="F65" s="55" t="n">
+      <c r="F65" s="64" t="n">
         <v>1370</v>
       </c>
-      <c r="G65" s="55" t="n">
+      <c r="G65" s="64" t="n">
         <v>680</v>
       </c>
-      <c r="H65" s="55" t="n">
+      <c r="H65" s="64" t="n">
         <v>80</v>
       </c>
-      <c r="I65" s="55" t="n">
+      <c r="I65" s="64" t="n">
         <v>3.46</v>
       </c>
-      <c r="J65" s="55" t="n">
+      <c r="J65" s="64" t="n">
         <v>35</v>
       </c>
-      <c r="K65" s="55" t="n">
+      <c r="K65" s="64" t="n">
         <v>437</v>
       </c>
-      <c r="L65" s="55" t="n">
+      <c r="L65" s="64" t="n">
         <v>179</v>
       </c>
-      <c r="M65" s="55" t="n">
+      <c r="M65" s="64" t="n">
         <v>124</v>
       </c>
     </row>
@@ -3742,40 +3838,40 @@
       <c r="A66" s="1" t="n">
         <v>66</v>
       </c>
-      <c r="B66" s="56" t="n">
+      <c r="B66" s="65" t="n">
         <v>26</v>
       </c>
-      <c r="C66" s="56" t="n">
+      <c r="C66" s="65" t="n">
         <v>0.87</v>
       </c>
-      <c r="D66" s="56" t="n">
+      <c r="D66" s="65" t="n">
         <v>18.3</v>
       </c>
-      <c r="E66" s="56" t="n">
+      <c r="E66" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="F66" s="56" t="n">
+      <c r="F66" s="65" t="n">
         <v>1380</v>
       </c>
-      <c r="G66" s="56" t="n">
+      <c r="G66" s="65" t="n">
         <v>680</v>
       </c>
-      <c r="H66" s="56" t="n">
+      <c r="H66" s="65" t="n">
         <v>50</v>
       </c>
-      <c r="I66" s="56" t="n">
+      <c r="I66" s="65" t="n">
         <v>1.56</v>
       </c>
-      <c r="J66" s="56" t="n">
+      <c r="J66" s="65" t="n">
         <v>55</v>
       </c>
-      <c r="K66" s="56" t="n">
+      <c r="K66" s="65" t="n">
         <v>158</v>
       </c>
-      <c r="L66" s="56" t="n">
+      <c r="L66" s="65" t="n">
         <v>143</v>
       </c>
-      <c r="M66" s="56" t="n">
+      <c r="M66" s="65" t="n">
         <v>107</v>
       </c>
     </row>
@@ -3783,40 +3879,40 @@
       <c r="A67" s="1" t="n">
         <v>67</v>
       </c>
-      <c r="B67" s="57" t="n">
+      <c r="B67" s="66" t="n">
         <v>26</v>
       </c>
-      <c r="C67" s="57" t="n">
+      <c r="C67" s="66" t="n">
         <v>0.87</v>
       </c>
-      <c r="D67" s="57" t="n">
+      <c r="D67" s="66" t="n">
         <v>18.3</v>
       </c>
-      <c r="E67" s="57" t="n">
+      <c r="E67" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="F67" s="57" t="n">
+      <c r="F67" s="66" t="n">
         <v>1340</v>
       </c>
-      <c r="G67" s="57" t="n">
+      <c r="G67" s="66" t="n">
         <v>660</v>
       </c>
-      <c r="H67" s="57" t="n">
+      <c r="H67" s="66" t="n">
         <v>50</v>
       </c>
-      <c r="I67" s="57" t="n">
+      <c r="I67" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="J67" s="57" t="n">
+      <c r="J67" s="66" t="n">
         <v>55</v>
       </c>
-      <c r="K67" s="57" t="n">
+      <c r="K67" s="66" t="n">
         <v>209</v>
       </c>
-      <c r="L67" s="57" t="n">
+      <c r="L67" s="66" t="n">
         <v>147</v>
       </c>
-      <c r="M67" s="57" t="n">
+      <c r="M67" s="66" t="n">
         <v>107</v>
       </c>
     </row>
@@ -3824,40 +3920,40 @@
       <c r="A68" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B68" s="58" t="n">
+      <c r="B68" s="67" t="n">
         <v>26</v>
       </c>
-      <c r="C68" s="58" t="n">
+      <c r="C68" s="67" t="n">
         <v>0.87</v>
       </c>
-      <c r="D68" s="58" t="n">
+      <c r="D68" s="67" t="n">
         <v>18.3</v>
       </c>
-      <c r="E68" s="58" t="n">
+      <c r="E68" s="67" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F68" s="58" t="n">
+      <c r="F68" s="67" t="n">
         <v>1020</v>
       </c>
-      <c r="G68" s="58" t="n">
+      <c r="G68" s="67" t="n">
         <v>500</v>
       </c>
-      <c r="H68" s="58" t="n">
+      <c r="H68" s="67" t="n">
         <v>70</v>
       </c>
-      <c r="I68" s="58" t="n">
+      <c r="I68" s="67" t="n">
         <v>4.3</v>
       </c>
-      <c r="J68" s="58" t="n">
+      <c r="J68" s="67" t="n">
         <v>30</v>
       </c>
-      <c r="K68" s="58" t="n">
+      <c r="K68" s="67" t="n">
         <v>21.9</v>
       </c>
-      <c r="L68" s="58" t="n">
+      <c r="L68" s="67" t="n">
         <v>212</v>
       </c>
-      <c r="M68" s="58" t="n">
+      <c r="M68" s="67" t="n">
         <v>68</v>
       </c>
     </row>
@@ -3865,40 +3961,40 @@
       <c r="A69" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="B69" s="59" t="n">
+      <c r="B69" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="C69" s="59" t="n">
+      <c r="C69" s="68" t="n">
         <v>0.87</v>
       </c>
-      <c r="D69" s="59" t="n">
+      <c r="D69" s="68" t="n">
         <v>18.2</v>
       </c>
-      <c r="E69" s="59" t="n">
+      <c r="E69" s="68" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F69" s="59" t="n">
+      <c r="F69" s="68" t="n">
         <v>1040</v>
       </c>
-      <c r="G69" s="59" t="n">
+      <c r="G69" s="68" t="n">
         <v>510</v>
       </c>
-      <c r="H69" s="59" t="n">
+      <c r="H69" s="68" t="n">
         <v>70</v>
       </c>
-      <c r="I69" s="59" t="n">
+      <c r="I69" s="68" t="n">
         <v>4.02</v>
       </c>
-      <c r="J69" s="59" t="n">
+      <c r="J69" s="68" t="n">
         <v>30</v>
       </c>
-      <c r="K69" s="59" t="n">
+      <c r="K69" s="68" t="n">
         <v>65</v>
       </c>
-      <c r="L69" s="59" t="n">
+      <c r="L69" s="68" t="n">
         <v>216</v>
       </c>
-      <c r="M69" s="59" t="n">
+      <c r="M69" s="68" t="n">
         <v>70</v>
       </c>
     </row>
@@ -3906,40 +4002,40 @@
       <c r="A70" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B70" s="60" t="n">
+      <c r="B70" s="69" t="n">
         <v>26</v>
       </c>
-      <c r="C70" s="60" t="n">
+      <c r="C70" s="69" t="n">
         <v>0.87</v>
       </c>
-      <c r="D70" s="60" t="n">
+      <c r="D70" s="69" t="n">
         <v>18.2</v>
       </c>
-      <c r="E70" s="60" t="n">
+      <c r="E70" s="69" t="n">
         <v>8.1</v>
       </c>
-      <c r="F70" s="60" t="n">
+      <c r="F70" s="69" t="n">
         <v>1440</v>
       </c>
-      <c r="G70" s="60" t="n">
+      <c r="G70" s="69" t="n">
         <v>710</v>
       </c>
-      <c r="H70" s="60" t="n">
+      <c r="H70" s="69" t="n">
         <v>64</v>
       </c>
-      <c r="I70" s="60" t="n">
+      <c r="I70" s="69" t="n">
         <v>1.93</v>
       </c>
-      <c r="J70" s="60" t="n">
+      <c r="J70" s="69" t="n">
         <v>50</v>
       </c>
-      <c r="K70" s="60" t="n">
+      <c r="K70" s="69" t="n">
         <v>123</v>
       </c>
-      <c r="L70" s="60" t="n">
+      <c r="L70" s="69" t="n">
         <v>179</v>
       </c>
-      <c r="M70" s="60" t="n">
+      <c r="M70" s="69" t="n">
         <v>124</v>
       </c>
     </row>
@@ -3947,40 +4043,40 @@
       <c r="A71" s="1" t="n">
         <v>71</v>
       </c>
-      <c r="B71" s="61" t="n">
+      <c r="B71" s="70" t="n">
         <v>26</v>
       </c>
-      <c r="C71" s="61" t="n">
+      <c r="C71" s="70" t="n">
         <v>0.87</v>
       </c>
-      <c r="D71" s="61" t="n">
+      <c r="D71" s="70" t="n">
         <v>18.2</v>
       </c>
-      <c r="E71" s="61" t="n">
+      <c r="E71" s="70" t="n">
         <v>8.1</v>
       </c>
-      <c r="F71" s="61" t="n">
+      <c r="F71" s="70" t="n">
         <v>1450</v>
       </c>
-      <c r="G71" s="61" t="n">
+      <c r="G71" s="70" t="n">
         <v>720</v>
       </c>
-      <c r="H71" s="61" t="n">
+      <c r="H71" s="70" t="n">
         <v>64</v>
       </c>
-      <c r="I71" s="61" t="n">
+      <c r="I71" s="70" t="n">
         <v>1.84</v>
       </c>
-      <c r="J71" s="61" t="n">
+      <c r="J71" s="70" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="61" t="n">
+      <c r="K71" s="70" t="n">
         <v>148</v>
       </c>
-      <c r="L71" s="61" t="n">
+      <c r="L71" s="70" t="n">
         <v>175</v>
       </c>
-      <c r="M71" s="61" t="n">
+      <c r="M71" s="70" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3988,40 +4084,40 @@
       <c r="A72" s="1" t="n">
         <v>72</v>
       </c>
-      <c r="B72" s="62" t="n">
+      <c r="B72" s="71" t="n">
         <v>13.4</v>
       </c>
-      <c r="C72" s="62" t="n">
+      <c r="C72" s="71" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D72" s="62" t="n">
+      <c r="D72" s="71" t="n">
         <v>16.8</v>
       </c>
-      <c r="E72" s="62" t="n">
+      <c r="E72" s="71" t="n">
         <v>8.1</v>
       </c>
-      <c r="F72" s="62" t="n">
+      <c r="F72" s="71" t="n">
         <v>1470</v>
       </c>
-      <c r="G72" s="62" t="n">
+      <c r="G72" s="71" t="n">
         <v>730</v>
       </c>
-      <c r="H72" s="62" t="n">
+      <c r="H72" s="71" t="n">
         <v>128</v>
       </c>
-      <c r="I72" s="62" t="n">
+      <c r="I72" s="71" t="n">
         <v>0.68</v>
       </c>
-      <c r="J72" s="62" t="n">
+      <c r="J72" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="K72" s="62" t="n">
+      <c r="K72" s="71" t="n">
         <v>60.9</v>
       </c>
-      <c r="L72" s="62" t="n">
+      <c r="L72" s="71" t="n">
         <v>181</v>
       </c>
-      <c r="M72" s="62" t="n">
+      <c r="M72" s="71" t="n">
         <v>110</v>
       </c>
     </row>
@@ -4029,40 +4125,40 @@
       <c r="A73" s="1" t="n">
         <v>73</v>
       </c>
-      <c r="B73" s="62" t="n">
+      <c r="B73" s="72" t="n">
         <v>13.4</v>
       </c>
-      <c r="C73" s="62" t="n">
+      <c r="C73" s="72" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D73" s="62" t="n">
+      <c r="D73" s="72" t="n">
         <v>15.8</v>
       </c>
-      <c r="E73" s="62" t="n">
+      <c r="E73" s="72" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F73" s="62" t="n">
+      <c r="F73" s="72" t="n">
         <v>1460</v>
       </c>
-      <c r="G73" s="62" t="n">
+      <c r="G73" s="72" t="n">
         <v>720</v>
       </c>
-      <c r="H73" s="62" t="n">
+      <c r="H73" s="72" t="n">
         <v>128</v>
       </c>
-      <c r="I73" s="62" t="n">
+      <c r="I73" s="72" t="n">
         <v>0.73</v>
       </c>
-      <c r="J73" s="62" t="n">
+      <c r="J73" s="72" t="n">
         <v>30</v>
       </c>
-      <c r="K73" s="62" t="n">
+      <c r="K73" s="72" t="n">
         <v>53.4</v>
       </c>
-      <c r="L73" s="62" t="n">
+      <c r="L73" s="72" t="n">
         <v>181</v>
       </c>
-      <c r="M73" s="62" t="n">
+      <c r="M73" s="72" t="n">
         <v>110</v>
       </c>
     </row>
@@ -4070,40 +4166,40 @@
       <c r="A74" s="1" t="n">
         <v>74</v>
       </c>
-      <c r="B74" s="63" t="n">
+      <c r="B74" s="73" t="n">
         <v>13.4</v>
       </c>
-      <c r="C74" s="63" t="n">
+      <c r="C74" s="73" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D74" s="63" t="n">
+      <c r="D74" s="73" t="n">
         <v>16</v>
       </c>
-      <c r="E74" s="63" t="n">
+      <c r="E74" s="73" t="n">
         <v>8.6</v>
       </c>
-      <c r="F74" s="63" t="n">
+      <c r="F74" s="73" t="n">
         <v>1520</v>
       </c>
-      <c r="G74" s="63" t="n">
+      <c r="G74" s="73" t="n">
         <v>750</v>
       </c>
-      <c r="H74" s="63" t="n">
+      <c r="H74" s="73" t="n">
         <v>50</v>
       </c>
-      <c r="I74" s="63" t="n">
+      <c r="I74" s="73" t="n">
         <v>8.17</v>
       </c>
-      <c r="J74" s="63" t="n">
+      <c r="J74" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="K74" s="63" t="n">
+      <c r="K74" s="73" t="n">
         <v>25.2</v>
       </c>
-      <c r="L74" s="63" t="n">
+      <c r="L74" s="73" t="n">
         <v>263</v>
       </c>
-      <c r="M74" s="63" t="n">
+      <c r="M74" s="73" t="n">
         <v>125</v>
       </c>
     </row>
@@ -4111,40 +4207,40 @@
       <c r="A75" s="1" t="n">
         <v>75</v>
       </c>
-      <c r="B75" s="64" t="n">
+      <c r="B75" s="74" t="n">
         <v>13.4</v>
       </c>
-      <c r="C75" s="64" t="n">
+      <c r="C75" s="74" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D75" s="64" t="n">
+      <c r="D75" s="74" t="n">
         <v>15.8</v>
       </c>
-      <c r="E75" s="64" t="n">
+      <c r="E75" s="74" t="n">
         <v>8.4</v>
       </c>
-      <c r="F75" s="64" t="n">
+      <c r="F75" s="74" t="n">
         <v>1480</v>
       </c>
-      <c r="G75" s="64" t="n">
+      <c r="G75" s="74" t="n">
         <v>730</v>
       </c>
-      <c r="H75" s="64" t="n">
+      <c r="H75" s="74" t="n">
         <v>50</v>
       </c>
-      <c r="I75" s="64" t="n">
+      <c r="I75" s="74" t="n">
         <v>9.119999999999999</v>
       </c>
-      <c r="J75" s="64" t="n">
+      <c r="J75" s="74" t="n">
         <v>25</v>
       </c>
-      <c r="K75" s="64" t="n">
+      <c r="K75" s="74" t="n">
         <v>29.4</v>
       </c>
-      <c r="L75" s="64" t="n">
+      <c r="L75" s="74" t="n">
         <v>263</v>
       </c>
-      <c r="M75" s="64" t="n">
+      <c r="M75" s="74" t="n">
         <v>125</v>
       </c>
     </row>
@@ -4152,40 +4248,40 @@
       <c r="A76" s="1" t="n">
         <v>76</v>
       </c>
-      <c r="B76" s="65" t="n">
+      <c r="B76" s="75" t="n">
         <v>13.4</v>
       </c>
-      <c r="C76" s="65" t="n">
+      <c r="C76" s="75" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D76" s="65" t="n">
+      <c r="D76" s="75" t="n">
         <v>15.4</v>
       </c>
-      <c r="E76" s="65" t="n">
+      <c r="E76" s="75" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F76" s="65" t="n">
+      <c r="F76" s="75" t="n">
         <v>1550</v>
       </c>
-      <c r="G76" s="65" t="n">
+      <c r="G76" s="75" t="n">
         <v>770</v>
       </c>
-      <c r="H76" s="65" t="n">
+      <c r="H76" s="75" t="n">
         <v>40</v>
       </c>
-      <c r="I76" s="65" t="n">
+      <c r="I76" s="75" t="n">
         <v>1.11</v>
       </c>
-      <c r="J76" s="65" t="n">
+      <c r="J76" s="75" t="n">
         <v>55</v>
       </c>
-      <c r="K76" s="65" t="n">
+      <c r="K76" s="75" t="n">
         <v>62.7</v>
       </c>
-      <c r="L76" s="65" t="n">
+      <c r="L76" s="75" t="n">
         <v>222</v>
       </c>
-      <c r="M76" s="65" t="n">
+      <c r="M76" s="75" t="n">
         <v>133</v>
       </c>
     </row>
@@ -4193,40 +4289,40 @@
       <c r="A77" s="1" t="n">
         <v>77</v>
       </c>
-      <c r="B77" s="66" t="n">
+      <c r="B77" s="76" t="n">
         <v>13.4</v>
       </c>
-      <c r="C77" s="66" t="n">
+      <c r="C77" s="76" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D77" s="66" t="n">
+      <c r="D77" s="76" t="n">
         <v>15.8</v>
       </c>
-      <c r="E77" s="66" t="n">
+      <c r="E77" s="76" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F77" s="66" t="n">
+      <c r="F77" s="76" t="n">
         <v>1510</v>
       </c>
-      <c r="G77" s="66" t="n">
+      <c r="G77" s="76" t="n">
         <v>750</v>
       </c>
-      <c r="H77" s="66" t="n">
+      <c r="H77" s="76" t="n">
         <v>40</v>
       </c>
-      <c r="I77" s="66" t="n">
+      <c r="I77" s="76" t="n">
         <v>0.73</v>
       </c>
-      <c r="J77" s="66" t="n">
+      <c r="J77" s="76" t="n">
         <v>55</v>
       </c>
-      <c r="K77" s="66" t="n">
+      <c r="K77" s="76" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="L77" s="66" t="n">
+      <c r="L77" s="76" t="n">
         <v>222</v>
       </c>
-      <c r="M77" s="66" t="n">
+      <c r="M77" s="76" t="n">
         <v>133</v>
       </c>
     </row>
@@ -4234,40 +4330,40 @@
       <c r="A78" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="B78" s="67" t="n">
+      <c r="B78" s="77" t="n">
         <v>13.4</v>
       </c>
-      <c r="C78" s="67" t="n">
+      <c r="C78" s="77" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D78" s="67" t="n">
+      <c r="D78" s="77" t="n">
         <v>15.6</v>
       </c>
-      <c r="E78" s="67" t="n">
+      <c r="E78" s="77" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F78" s="67" t="n">
+      <c r="F78" s="77" t="n">
         <v>1140</v>
       </c>
-      <c r="G78" s="67" t="n">
+      <c r="G78" s="77" t="n">
         <v>570</v>
       </c>
-      <c r="H78" s="67" t="n">
+      <c r="H78" s="77" t="n">
         <v>36</v>
       </c>
-      <c r="I78" s="67" t="n">
+      <c r="I78" s="77" t="n">
         <v>2.74</v>
       </c>
-      <c r="J78" s="67" t="n">
+      <c r="J78" s="77" t="n">
         <v>30</v>
       </c>
-      <c r="K78" s="67" t="n">
+      <c r="K78" s="77" t="n">
         <v>5.47</v>
       </c>
-      <c r="L78" s="67" t="n">
+      <c r="L78" s="77" t="n">
         <v>316</v>
       </c>
-      <c r="M78" s="67" t="n">
+      <c r="M78" s="77" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4275,40 +4371,40 @@
       <c r="A79" s="1" t="n">
         <v>79</v>
       </c>
-      <c r="B79" s="68" t="n">
+      <c r="B79" s="78" t="n">
         <v>13.4</v>
       </c>
-      <c r="C79" s="68" t="n">
+      <c r="C79" s="78" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D79" s="68" t="n">
+      <c r="D79" s="78" t="n">
         <v>15.8</v>
       </c>
-      <c r="E79" s="68" t="n">
+      <c r="E79" s="78" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F79" s="68" t="n">
+      <c r="F79" s="78" t="n">
         <v>1150</v>
       </c>
-      <c r="G79" s="68" t="n">
+      <c r="G79" s="78" t="n">
         <v>560</v>
       </c>
-      <c r="H79" s="68" t="n">
+      <c r="H79" s="78" t="n">
         <v>36</v>
       </c>
-      <c r="I79" s="68" t="n">
+      <c r="I79" s="78" t="n">
         <v>2.44</v>
       </c>
-      <c r="J79" s="68" t="n">
+      <c r="J79" s="78" t="n">
         <v>30</v>
       </c>
-      <c r="K79" s="68" t="n">
+      <c r="K79" s="78" t="n">
         <v>22.7</v>
       </c>
-      <c r="L79" s="68" t="n">
+      <c r="L79" s="78" t="n">
         <v>316</v>
       </c>
-      <c r="M79" s="68" t="n">
+      <c r="M79" s="78" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4316,40 +4412,40 @@
       <c r="A80" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="B80" s="69" t="n">
+      <c r="B80" s="79" t="n">
         <v>13.4</v>
       </c>
-      <c r="C80" s="69" t="n">
+      <c r="C80" s="79" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D80" s="69" t="n">
+      <c r="D80" s="79" t="n">
         <v>15.5</v>
       </c>
-      <c r="E80" s="69" t="n">
+      <c r="E80" s="79" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F80" s="69" t="n">
+      <c r="F80" s="79" t="n">
         <v>1420</v>
       </c>
-      <c r="G80" s="69" t="n">
+      <c r="G80" s="79" t="n">
         <v>700</v>
       </c>
-      <c r="H80" s="69" t="n">
+      <c r="H80" s="79" t="n">
         <v>66</v>
       </c>
-      <c r="I80" s="69" t="n">
+      <c r="I80" s="79" t="n">
         <v>0.88</v>
       </c>
-      <c r="J80" s="69" t="n">
+      <c r="J80" s="79" t="n">
         <v>45</v>
       </c>
-      <c r="K80" s="69" t="n">
+      <c r="K80" s="79" t="n">
         <v>66</v>
       </c>
-      <c r="L80" s="69" t="n">
+      <c r="L80" s="79" t="n">
         <v>257</v>
       </c>
-      <c r="M80" s="69" t="n">
+      <c r="M80" s="79" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4357,40 +4453,40 @@
       <c r="A81" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B81" s="70" t="n">
+      <c r="B81" s="80" t="n">
         <v>13.4</v>
       </c>
-      <c r="C81" s="70" t="n">
+      <c r="C81" s="80" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D81" s="70" t="n">
+      <c r="D81" s="80" t="n">
         <v>15.9</v>
       </c>
-      <c r="E81" s="70" t="n">
+      <c r="E81" s="80" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F81" s="70" t="n">
+      <c r="F81" s="80" t="n">
         <v>1480</v>
       </c>
-      <c r="G81" s="70" t="n">
+      <c r="G81" s="80" t="n">
         <v>730</v>
       </c>
-      <c r="H81" s="70" t="n">
+      <c r="H81" s="80" t="n">
         <v>66</v>
       </c>
-      <c r="I81" s="70" t="n">
+      <c r="I81" s="80" t="n">
         <v>1.3</v>
       </c>
-      <c r="J81" s="70" t="n">
+      <c r="J81" s="80" t="n">
         <v>45</v>
       </c>
-      <c r="K81" s="70" t="n">
+      <c r="K81" s="80" t="n">
         <v>87.2</v>
       </c>
-      <c r="L81" s="70" t="n">
+      <c r="L81" s="80" t="n">
         <v>257</v>
       </c>
-      <c r="M81" s="70" t="n">
+      <c r="M81" s="80" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4398,40 +4494,40 @@
       <c r="A82" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="B82" s="71" t="n">
+      <c r="B82" s="81" t="n">
         <v>23</v>
       </c>
-      <c r="C82" s="71" t="n">
+      <c r="C82" s="81" t="n">
         <v>0.36</v>
       </c>
-      <c r="D82" s="71" t="n">
+      <c r="D82" s="81" t="n">
         <v>21</v>
       </c>
-      <c r="E82" s="71" t="n">
+      <c r="E82" s="81" t="n">
         <v>7.3</v>
       </c>
-      <c r="F82" s="71" t="n">
+      <c r="F82" s="81" t="n">
         <v>1590</v>
       </c>
-      <c r="G82" s="71" t="n">
+      <c r="G82" s="81" t="n">
         <v>790</v>
       </c>
-      <c r="H82" s="71" t="n">
+      <c r="H82" s="81" t="n">
         <v>620</v>
       </c>
-      <c r="I82" s="71" t="n">
+      <c r="I82" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="71" t="n">
+      <c r="J82" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="K82" s="71" t="n">
+      <c r="K82" s="81" t="n">
         <v>1000</v>
       </c>
-      <c r="L82" s="71" t="n">
+      <c r="L82" s="81" t="n">
         <v>228</v>
       </c>
-      <c r="M82" s="71" t="n">
+      <c r="M82" s="81" t="n">
         <v>118</v>
       </c>
     </row>
@@ -4439,40 +4535,40 @@
       <c r="A83" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B83" s="72" t="n">
+      <c r="B83" s="82" t="n">
         <v>23</v>
       </c>
-      <c r="C83" s="72" t="n">
+      <c r="C83" s="82" t="n">
         <v>0.36</v>
       </c>
-      <c r="D83" s="72" t="n">
+      <c r="D83" s="82" t="n">
         <v>20.8</v>
       </c>
-      <c r="E83" s="72" t="n">
+      <c r="E83" s="82" t="n">
         <v>7.3</v>
       </c>
-      <c r="F83" s="72" t="n">
+      <c r="F83" s="82" t="n">
         <v>1520</v>
       </c>
-      <c r="G83" s="72" t="n">
+      <c r="G83" s="82" t="n">
         <v>750</v>
       </c>
-      <c r="H83" s="72" t="n">
+      <c r="H83" s="82" t="n">
         <v>620</v>
       </c>
-      <c r="I83" s="72" t="n">
+      <c r="I83" s="82" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="72" t="n">
+      <c r="J83" s="82" t="n">
         <v>25</v>
       </c>
-      <c r="K83" s="72" t="n">
+      <c r="K83" s="82" t="n">
         <v>1000</v>
       </c>
-      <c r="L83" s="72" t="n">
+      <c r="L83" s="82" t="n">
         <v>228</v>
       </c>
-      <c r="M83" s="72" t="n">
+      <c r="M83" s="82" t="n">
         <v>118</v>
       </c>
     </row>
@@ -4480,40 +4576,40 @@
       <c r="A84" s="1" t="n">
         <v>84</v>
       </c>
-      <c r="B84" s="73" t="n">
+      <c r="B84" s="83" t="n">
         <v>23</v>
       </c>
-      <c r="C84" s="73" t="n">
+      <c r="C84" s="83" t="n">
         <v>0.36</v>
       </c>
-      <c r="D84" s="73" t="n">
+      <c r="D84" s="83" t="n">
         <v>21.2</v>
       </c>
-      <c r="E84" s="73" t="n">
+      <c r="E84" s="83" t="n">
         <v>8.5</v>
       </c>
-      <c r="F84" s="73" t="n">
+      <c r="F84" s="83" t="n">
         <v>1430</v>
       </c>
-      <c r="G84" s="73" t="n">
+      <c r="G84" s="83" t="n">
         <v>710</v>
       </c>
-      <c r="H84" s="73" t="n">
+      <c r="H84" s="83" t="n">
         <v>76</v>
       </c>
-      <c r="I84" s="73" t="n">
+      <c r="I84" s="83" t="n">
         <v>5.22</v>
       </c>
-      <c r="J84" s="73" t="n">
+      <c r="J84" s="83" t="n">
         <v>30</v>
       </c>
-      <c r="K84" s="73" t="n">
+      <c r="K84" s="83" t="n">
         <v>147</v>
       </c>
-      <c r="L84" s="73" t="n">
+      <c r="L84" s="83" t="n">
         <v>257</v>
       </c>
-      <c r="M84" s="73" t="n">
+      <c r="M84" s="83" t="n">
         <v>112</v>
       </c>
     </row>
@@ -4521,40 +4617,40 @@
       <c r="A85" s="1" t="n">
         <v>85</v>
       </c>
-      <c r="B85" s="74" t="n">
+      <c r="B85" s="84" t="n">
         <v>23</v>
       </c>
-      <c r="C85" s="74" t="n">
+      <c r="C85" s="84" t="n">
         <v>0.36</v>
       </c>
-      <c r="D85" s="74" t="n">
+      <c r="D85" s="84" t="n">
         <v>21.1</v>
       </c>
-      <c r="E85" s="74" t="n">
+      <c r="E85" s="84" t="n">
         <v>8.5</v>
       </c>
-      <c r="F85" s="74" t="n">
+      <c r="F85" s="84" t="n">
         <v>1410</v>
       </c>
-      <c r="G85" s="74" t="n">
+      <c r="G85" s="84" t="n">
         <v>700</v>
       </c>
-      <c r="H85" s="74" t="n">
+      <c r="H85" s="84" t="n">
         <v>76</v>
       </c>
-      <c r="I85" s="74" t="n">
+      <c r="I85" s="84" t="n">
         <v>4.25</v>
       </c>
-      <c r="J85" s="74" t="n">
+      <c r="J85" s="84" t="n">
         <v>30</v>
       </c>
-      <c r="K85" s="74" t="n">
+      <c r="K85" s="84" t="n">
         <v>150</v>
       </c>
-      <c r="L85" s="74" t="n">
+      <c r="L85" s="84" t="n">
         <v>257</v>
       </c>
-      <c r="M85" s="74" t="n">
+      <c r="M85" s="84" t="n">
         <v>112</v>
       </c>
     </row>
@@ -4562,40 +4658,40 @@
       <c r="A86" s="1" t="n">
         <v>86</v>
       </c>
-      <c r="B86" s="75" t="n">
+      <c r="B86" s="85" t="n">
         <v>23</v>
       </c>
-      <c r="C86" s="75" t="n">
+      <c r="C86" s="85" t="n">
         <v>0.36</v>
       </c>
-      <c r="D86" s="75" t="n">
+      <c r="D86" s="85" t="n">
         <v>21.3</v>
       </c>
-      <c r="E86" s="75" t="n">
+      <c r="E86" s="85" t="n">
         <v>8.1</v>
       </c>
-      <c r="F86" s="75" t="n">
+      <c r="F86" s="85" t="n">
         <v>1690</v>
       </c>
-      <c r="G86" s="75" t="n">
+      <c r="G86" s="85" t="n">
         <v>840</v>
       </c>
-      <c r="H86" s="75" t="n">
+      <c r="H86" s="85" t="n">
         <v>84</v>
       </c>
-      <c r="I86" s="75" t="n">
+      <c r="I86" s="85" t="n">
         <v>0.63</v>
       </c>
-      <c r="J86" s="75" t="n">
+      <c r="J86" s="85" t="n">
         <v>55</v>
       </c>
-      <c r="K86" s="75" t="n">
+      <c r="K86" s="85" t="n">
         <v>160</v>
       </c>
-      <c r="L86" s="75" t="n">
+      <c r="L86" s="85" t="n">
         <v>222</v>
       </c>
-      <c r="M86" s="75" t="n">
+      <c r="M86" s="85" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4603,40 +4699,40 @@
       <c r="A87" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B87" s="75" t="n">
+      <c r="B87" s="86" t="n">
         <v>23</v>
       </c>
-      <c r="C87" s="75" t="n">
+      <c r="C87" s="86" t="n">
         <v>0.36</v>
       </c>
-      <c r="D87" s="75" t="n">
+      <c r="D87" s="86" t="n">
         <v>21.2</v>
       </c>
-      <c r="E87" s="75" t="n">
+      <c r="E87" s="86" t="n">
         <v>8.1</v>
       </c>
-      <c r="F87" s="75" t="n">
+      <c r="F87" s="86" t="n">
         <v>1670</v>
       </c>
-      <c r="G87" s="75" t="n">
+      <c r="G87" s="86" t="n">
         <v>830</v>
       </c>
-      <c r="H87" s="75" t="n">
+      <c r="H87" s="86" t="n">
         <v>84</v>
       </c>
-      <c r="I87" s="75" t="n">
+      <c r="I87" s="86" t="n">
         <v>0.75</v>
       </c>
-      <c r="J87" s="75" t="n">
+      <c r="J87" s="86" t="n">
         <v>55</v>
       </c>
-      <c r="K87" s="75" t="n">
+      <c r="K87" s="86" t="n">
         <v>154</v>
       </c>
-      <c r="L87" s="75" t="n">
+      <c r="L87" s="86" t="n">
         <v>222</v>
       </c>
-      <c r="M87" s="75" t="n">
+      <c r="M87" s="86" t="n">
         <v>145</v>
       </c>
     </row>
@@ -4644,40 +4740,40 @@
       <c r="A88" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B88" s="67" t="n">
+      <c r="B88" s="87" t="n">
         <v>23</v>
       </c>
-      <c r="C88" s="67" t="n">
+      <c r="C88" s="87" t="n">
         <v>0.36</v>
       </c>
-      <c r="D88" s="67" t="n">
+      <c r="D88" s="87" t="n">
         <v>21.4</v>
       </c>
-      <c r="E88" s="67" t="n">
+      <c r="E88" s="87" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F88" s="67" t="n">
+      <c r="F88" s="87" t="n">
         <v>1120</v>
       </c>
-      <c r="G88" s="67" t="n">
+      <c r="G88" s="87" t="n">
         <v>550</v>
       </c>
-      <c r="H88" s="67" t="n">
+      <c r="H88" s="87" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="67" t="n">
+      <c r="I88" s="87" t="n">
         <v>2.68</v>
       </c>
-      <c r="J88" s="67" t="n">
+      <c r="J88" s="87" t="n">
         <v>45</v>
       </c>
-      <c r="K88" s="67" t="n">
+      <c r="K88" s="87" t="n">
         <v>4.52</v>
       </c>
-      <c r="L88" s="67" t="n">
+      <c r="L88" s="87" t="n">
         <v>293</v>
       </c>
-      <c r="M88" s="67" t="n">
+      <c r="M88" s="87" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4685,40 +4781,40 @@
       <c r="A89" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B89" s="76" t="n">
+      <c r="B89" s="88" t="n">
         <v>23</v>
       </c>
-      <c r="C89" s="76" t="n">
+      <c r="C89" s="88" t="n">
         <v>0.36</v>
       </c>
-      <c r="D89" s="76" t="n">
+      <c r="D89" s="88" t="n">
         <v>21.3</v>
       </c>
-      <c r="E89" s="76" t="n">
+      <c r="E89" s="88" t="n">
         <v>8.1</v>
       </c>
-      <c r="F89" s="76" t="n">
+      <c r="F89" s="88" t="n">
         <v>1100</v>
       </c>
-      <c r="G89" s="76" t="n">
+      <c r="G89" s="88" t="n">
         <v>540</v>
       </c>
-      <c r="H89" s="76" t="n">
+      <c r="H89" s="88" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="76" t="n">
+      <c r="I89" s="88" t="n">
         <v>1.75</v>
       </c>
-      <c r="J89" s="76" t="n">
+      <c r="J89" s="88" t="n">
         <v>45</v>
       </c>
-      <c r="K89" s="76" t="n">
+      <c r="K89" s="88" t="n">
         <v>4.91</v>
       </c>
-      <c r="L89" s="76" t="n">
+      <c r="L89" s="88" t="n">
         <v>293</v>
       </c>
-      <c r="M89" s="76" t="n">
+      <c r="M89" s="88" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4726,40 +4822,40 @@
       <c r="A90" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B90" s="77" t="n">
+      <c r="B90" s="89" t="n">
         <v>23</v>
       </c>
-      <c r="C90" s="77" t="n">
+      <c r="C90" s="89" t="n">
         <v>0.36</v>
       </c>
-      <c r="D90" s="77" t="n">
+      <c r="D90" s="89" t="n">
         <v>21.4</v>
       </c>
-      <c r="E90" s="77" t="n">
+      <c r="E90" s="89" t="n">
         <v>8.1</v>
       </c>
-      <c r="F90" s="77" t="n">
+      <c r="F90" s="89" t="n">
         <v>1500</v>
       </c>
-      <c r="G90" s="77" t="n">
+      <c r="G90" s="89" t="n">
         <v>740</v>
       </c>
-      <c r="H90" s="77" t="n">
+      <c r="H90" s="89" t="n">
         <v>50</v>
       </c>
-      <c r="I90" s="77" t="n">
+      <c r="I90" s="89" t="n">
         <v>0.26</v>
       </c>
-      <c r="J90" s="77" t="n">
+      <c r="J90" s="89" t="n">
         <v>45</v>
       </c>
-      <c r="K90" s="77" t="n">
+      <c r="K90" s="89" t="n">
         <v>116</v>
       </c>
-      <c r="L90" s="77" t="n">
+      <c r="L90" s="89" t="n">
         <v>257</v>
       </c>
-      <c r="M90" s="77" t="n">
+      <c r="M90" s="89" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4767,40 +4863,40 @@
       <c r="A91" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B91" s="62" t="n">
+      <c r="B91" s="90" t="n">
         <v>23</v>
       </c>
-      <c r="C91" s="62" t="n">
+      <c r="C91" s="90" t="n">
         <v>0.36</v>
       </c>
-      <c r="D91" s="62" t="n">
+      <c r="D91" s="90" t="n">
         <v>21.3</v>
       </c>
-      <c r="E91" s="62" t="n">
+      <c r="E91" s="90" t="n">
         <v>8</v>
       </c>
-      <c r="F91" s="62" t="n">
+      <c r="F91" s="90" t="n">
         <v>1440</v>
       </c>
-      <c r="G91" s="62" t="n">
+      <c r="G91" s="90" t="n">
         <v>710</v>
       </c>
-      <c r="H91" s="62" t="n">
+      <c r="H91" s="90" t="n">
         <v>50</v>
       </c>
-      <c r="I91" s="62" t="n">
+      <c r="I91" s="90" t="n">
         <v>0.25</v>
       </c>
-      <c r="J91" s="62" t="n">
+      <c r="J91" s="90" t="n">
         <v>45</v>
       </c>
-      <c r="K91" s="62" t="n">
+      <c r="K91" s="90" t="n">
         <v>38.5</v>
       </c>
-      <c r="L91" s="62" t="n">
+      <c r="L91" s="90" t="n">
         <v>257</v>
       </c>
-      <c r="M91" s="62" t="n">
+      <c r="M91" s="90" t="n">
         <v>99</v>
       </c>
     </row>
@@ -4808,40 +4904,40 @@
       <c r="A92" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B92" s="78" t="n">
+      <c r="B92" s="91" t="n">
         <v>15.2</v>
       </c>
-      <c r="C92" s="78" t="n">
+      <c r="C92" s="91" t="n">
         <v>0.52</v>
       </c>
-      <c r="D92" s="78" t="n">
+      <c r="D92" s="91" t="n">
         <v>17.4</v>
       </c>
-      <c r="E92" s="78" t="n">
+      <c r="E92" s="91" t="n">
         <v>8.1</v>
       </c>
-      <c r="F92" s="78" t="n">
+      <c r="F92" s="91" t="n">
         <v>1020</v>
       </c>
-      <c r="G92" s="78" t="n">
+      <c r="G92" s="91" t="n">
         <v>500</v>
       </c>
-      <c r="H92" s="78" t="n">
+      <c r="H92" s="91" t="n">
         <v>82</v>
       </c>
-      <c r="I92" s="78" t="n">
+      <c r="I92" s="91" t="n">
         <v>2.87</v>
       </c>
-      <c r="J92" s="78" t="n">
+      <c r="J92" s="91" t="n">
         <v>35</v>
       </c>
-      <c r="K92" s="78" t="n">
+      <c r="K92" s="91" t="n">
         <v>1000</v>
       </c>
-      <c r="L92" s="78" t="n">
+      <c r="L92" s="91" t="n">
         <v>135</v>
       </c>
-      <c r="M92" s="78" t="n">
+      <c r="M92" s="91" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4849,40 +4945,40 @@
       <c r="A93" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B93" s="79" t="n">
+      <c r="B93" s="92" t="n">
         <v>15.2</v>
       </c>
-      <c r="C93" s="79" t="n">
+      <c r="C93" s="92" t="n">
         <v>0.52</v>
       </c>
-      <c r="D93" s="79" t="n">
+      <c r="D93" s="92" t="n">
         <v>17.3</v>
       </c>
-      <c r="E93" s="79" t="n">
+      <c r="E93" s="92" t="n">
         <v>8</v>
       </c>
-      <c r="F93" s="79" t="n">
+      <c r="F93" s="92" t="n">
         <v>960</v>
       </c>
-      <c r="G93" s="79" t="n">
+      <c r="G93" s="92" t="n">
         <v>470</v>
       </c>
-      <c r="H93" s="79" t="n">
+      <c r="H93" s="92" t="n">
         <v>82</v>
       </c>
-      <c r="I93" s="79" t="n">
+      <c r="I93" s="92" t="n">
         <v>1.82</v>
       </c>
-      <c r="J93" s="79" t="n">
+      <c r="J93" s="92" t="n">
         <v>35</v>
       </c>
-      <c r="K93" s="79" t="n">
+      <c r="K93" s="92" t="n">
         <v>1000</v>
       </c>
-      <c r="L93" s="79" t="n">
+      <c r="L93" s="92" t="n">
         <v>135</v>
       </c>
-      <c r="M93" s="79" t="n">
+      <c r="M93" s="92" t="n">
         <v>64</v>
       </c>
     </row>
@@ -4890,40 +4986,40 @@
       <c r="A94" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B94" s="80" t="n">
+      <c r="B94" s="93" t="n">
         <v>15.2</v>
       </c>
-      <c r="C94" s="80" t="n">
+      <c r="C94" s="93" t="n">
         <v>0.52</v>
       </c>
-      <c r="D94" s="80" t="n">
+      <c r="D94" s="93" t="n">
         <v>17.5</v>
       </c>
-      <c r="E94" s="80" t="n">
+      <c r="E94" s="93" t="n">
         <v>8.1</v>
       </c>
-      <c r="F94" s="80" t="n">
+      <c r="F94" s="93" t="n">
         <v>640</v>
       </c>
-      <c r="G94" s="80" t="n">
+      <c r="G94" s="93" t="n">
         <v>310</v>
       </c>
-      <c r="H94" s="80" t="n">
+      <c r="H94" s="93" t="n">
         <v>66</v>
       </c>
-      <c r="I94" s="80" t="n">
+      <c r="I94" s="93" t="n">
         <v>5.35</v>
       </c>
-      <c r="J94" s="80" t="n">
+      <c r="J94" s="93" t="n">
         <v>40</v>
       </c>
-      <c r="K94" s="80" t="n">
+      <c r="K94" s="93" t="n">
         <v>161</v>
       </c>
-      <c r="L94" s="80" t="n">
+      <c r="L94" s="93" t="n">
         <v>152</v>
       </c>
-      <c r="M94" s="80" t="n">
+      <c r="M94" s="93" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4931,40 +5027,40 @@
       <c r="A95" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B95" s="81" t="n">
+      <c r="B95" s="94" t="n">
         <v>15.2</v>
       </c>
-      <c r="C95" s="81" t="n">
+      <c r="C95" s="94" t="n">
         <v>0.52</v>
       </c>
-      <c r="D95" s="81" t="n">
+      <c r="D95" s="94" t="n">
         <v>17.7</v>
       </c>
-      <c r="E95" s="81" t="n">
+      <c r="E95" s="94" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F95" s="81" t="n">
+      <c r="F95" s="94" t="n">
         <v>620</v>
       </c>
-      <c r="G95" s="81" t="n">
+      <c r="G95" s="94" t="n">
         <v>300</v>
       </c>
-      <c r="H95" s="81" t="n">
+      <c r="H95" s="94" t="n">
         <v>66</v>
       </c>
-      <c r="I95" s="81" t="n">
+      <c r="I95" s="94" t="n">
         <v>5.43</v>
       </c>
-      <c r="J95" s="81" t="n">
+      <c r="J95" s="94" t="n">
         <v>40</v>
       </c>
-      <c r="K95" s="81" t="n">
+      <c r="K95" s="94" t="n">
         <v>161</v>
       </c>
-      <c r="L95" s="81" t="n">
+      <c r="L95" s="94" t="n">
         <v>152</v>
       </c>
-      <c r="M95" s="81" t="n">
+      <c r="M95" s="94" t="n">
         <v>49</v>
       </c>
     </row>
@@ -4972,40 +5068,40 @@
       <c r="A96" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B96" s="82" t="n">
+      <c r="B96" s="95" t="n">
         <v>15.2</v>
       </c>
-      <c r="C96" s="82" t="n">
+      <c r="C96" s="95" t="n">
         <v>0.52</v>
       </c>
-      <c r="D96" s="82" t="n">
+      <c r="D96" s="95" t="n">
         <v>17.8</v>
       </c>
-      <c r="E96" s="82" t="n">
+      <c r="E96" s="95" t="n">
         <v>8.1</v>
       </c>
-      <c r="F96" s="82" t="n">
+      <c r="F96" s="95" t="n">
         <v>740</v>
       </c>
-      <c r="G96" s="82" t="n">
+      <c r="G96" s="95" t="n">
         <v>360</v>
       </c>
-      <c r="H96" s="82" t="n">
+      <c r="H96" s="95" t="n">
         <v>70</v>
       </c>
-      <c r="I96" s="82" t="n">
+      <c r="I96" s="95" t="n">
         <v>3.84</v>
       </c>
-      <c r="J96" s="82" t="n">
+      <c r="J96" s="95" t="n">
         <v>50</v>
       </c>
-      <c r="K96" s="82" t="n">
+      <c r="K96" s="95" t="n">
         <v>124</v>
       </c>
-      <c r="L96" s="82" t="n">
+      <c r="L96" s="95" t="n">
         <v>135</v>
       </c>
-      <c r="M96" s="82" t="n">
+      <c r="M96" s="95" t="n">
         <v>59</v>
       </c>
     </row>
@@ -5013,40 +5109,40 @@
       <c r="A97" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B97" s="82" t="n">
+      <c r="B97" s="96" t="n">
         <v>15.2</v>
       </c>
-      <c r="C97" s="82" t="n">
+      <c r="C97" s="96" t="n">
         <v>0.52</v>
       </c>
-      <c r="D97" s="82" t="n">
+      <c r="D97" s="96" t="n">
         <v>17.6</v>
       </c>
-      <c r="E97" s="82" t="n">
+      <c r="E97" s="96" t="n">
         <v>8.1</v>
       </c>
-      <c r="F97" s="82" t="n">
+      <c r="F97" s="96" t="n">
         <v>750</v>
       </c>
-      <c r="G97" s="82" t="n">
+      <c r="G97" s="96" t="n">
         <v>370</v>
       </c>
-      <c r="H97" s="82" t="n">
+      <c r="H97" s="96" t="n">
         <v>70</v>
       </c>
-      <c r="I97" s="82" t="n">
+      <c r="I97" s="96" t="n">
         <v>3.8</v>
       </c>
-      <c r="J97" s="82" t="n">
+      <c r="J97" s="96" t="n">
         <v>50</v>
       </c>
-      <c r="K97" s="82" t="n">
+      <c r="K97" s="96" t="n">
         <v>124</v>
       </c>
-      <c r="L97" s="82" t="n">
+      <c r="L97" s="96" t="n">
         <v>135</v>
       </c>
-      <c r="M97" s="82" t="n">
+      <c r="M97" s="96" t="n">
         <v>59</v>
       </c>
     </row>
@@ -5054,40 +5150,40 @@
       <c r="A98" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B98" s="83" t="n">
+      <c r="B98" s="97" t="n">
         <v>15.2</v>
       </c>
-      <c r="C98" s="83" t="n">
+      <c r="C98" s="97" t="n">
         <v>0.52</v>
       </c>
-      <c r="D98" s="83" t="n">
+      <c r="D98" s="97" t="n">
         <v>17.8</v>
       </c>
-      <c r="E98" s="83" t="n">
+      <c r="E98" s="97" t="n">
         <v>7.9</v>
       </c>
-      <c r="F98" s="83" t="n">
+      <c r="F98" s="97" t="n">
         <v>290</v>
       </c>
-      <c r="G98" s="83" t="n">
+      <c r="G98" s="97" t="n">
         <v>140</v>
       </c>
-      <c r="H98" s="83" t="n">
+      <c r="H98" s="97" t="n">
         <v>1.8</v>
       </c>
-      <c r="I98" s="83" t="n">
+      <c r="I98" s="97" t="n">
         <v>4.82</v>
       </c>
-      <c r="J98" s="83" t="n">
+      <c r="J98" s="97" t="n">
         <v>25</v>
       </c>
-      <c r="K98" s="83" t="n">
+      <c r="K98" s="97" t="n">
         <v>41.3</v>
       </c>
-      <c r="L98" s="83" t="n">
+      <c r="L98" s="97" t="n">
         <v>94</v>
       </c>
-      <c r="M98" s="83" t="n">
+      <c r="M98" s="97" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5095,40 +5191,40 @@
       <c r="A99" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B99" s="84" t="n">
+      <c r="B99" s="98" t="n">
         <v>15.2</v>
       </c>
-      <c r="C99" s="84" t="n">
+      <c r="C99" s="98" t="n">
         <v>0.52</v>
       </c>
-      <c r="D99" s="84" t="n">
+      <c r="D99" s="98" t="n">
         <v>17.9</v>
       </c>
-      <c r="E99" s="84" t="n">
+      <c r="E99" s="98" t="n">
         <v>7.9</v>
       </c>
-      <c r="F99" s="84" t="n">
+      <c r="F99" s="98" t="n">
         <v>200</v>
       </c>
-      <c r="G99" s="84" t="n">
+      <c r="G99" s="98" t="n">
         <v>140</v>
       </c>
-      <c r="H99" s="84" t="n">
+      <c r="H99" s="98" t="n">
         <v>1.8</v>
       </c>
-      <c r="I99" s="84" t="n">
+      <c r="I99" s="98" t="n">
         <v>5.47</v>
       </c>
-      <c r="J99" s="84" t="n">
+      <c r="J99" s="98" t="n">
         <v>25</v>
       </c>
-      <c r="K99" s="84" t="n">
+      <c r="K99" s="98" t="n">
         <v>41.3</v>
       </c>
-      <c r="L99" s="84" t="n">
+      <c r="L99" s="98" t="n">
         <v>94</v>
       </c>
-      <c r="M99" s="84" t="n">
+      <c r="M99" s="98" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5136,40 +5232,40 @@
       <c r="A100" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B100" s="85" t="n">
+      <c r="B100" s="99" t="n">
         <v>15.2</v>
       </c>
-      <c r="C100" s="85" t="n">
+      <c r="C100" s="99" t="n">
         <v>0.52</v>
       </c>
-      <c r="D100" s="85" t="n">
+      <c r="D100" s="99" t="n">
         <v>18.3</v>
       </c>
-      <c r="E100" s="85" t="n">
+      <c r="E100" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="F100" s="85" t="n">
+      <c r="F100" s="99" t="n">
         <v>990</v>
       </c>
-      <c r="G100" s="85" t="n">
+      <c r="G100" s="99" t="n">
         <v>490</v>
       </c>
-      <c r="H100" s="85" t="n">
+      <c r="H100" s="99" t="n">
         <v>48</v>
       </c>
-      <c r="I100" s="85" t="n">
+      <c r="I100" s="99" t="n">
         <v>1.92</v>
       </c>
-      <c r="J100" s="85" t="n">
+      <c r="J100" s="99" t="n">
         <v>55</v>
       </c>
-      <c r="K100" s="85" t="n">
+      <c r="K100" s="99" t="n">
         <v>87.2</v>
       </c>
-      <c r="L100" s="85" t="n">
+      <c r="L100" s="99" t="n">
         <v>146</v>
       </c>
-      <c r="M100" s="85" t="n">
+      <c r="M100" s="99" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5177,40 +5273,40 @@
       <c r="A101" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B101" s="85" t="n">
+      <c r="B101" s="100" t="n">
         <v>15.2</v>
       </c>
-      <c r="C101" s="85" t="n">
+      <c r="C101" s="100" t="n">
         <v>0.52</v>
       </c>
-      <c r="D101" s="85" t="n">
+      <c r="D101" s="100" t="n">
         <v>18.4</v>
       </c>
-      <c r="E101" s="85" t="n">
+      <c r="E101" s="100" t="n">
         <v>8.1</v>
       </c>
-      <c r="F101" s="85" t="n">
+      <c r="F101" s="100" t="n">
         <v>1000</v>
       </c>
-      <c r="G101" s="85" t="n">
+      <c r="G101" s="100" t="n">
         <v>490</v>
       </c>
-      <c r="H101" s="85" t="n">
+      <c r="H101" s="100" t="n">
         <v>48</v>
       </c>
-      <c r="I101" s="85" t="n">
+      <c r="I101" s="100" t="n">
         <v>1.89</v>
       </c>
-      <c r="J101" s="85" t="n">
+      <c r="J101" s="100" t="n">
         <v>55</v>
       </c>
-      <c r="K101" s="85" t="n">
+      <c r="K101" s="100" t="n">
         <v>87.2</v>
       </c>
-      <c r="L101" s="85" t="n">
+      <c r="L101" s="100" t="n">
         <v>146</v>
       </c>
-      <c r="M101" s="85" t="n">
+      <c r="M101" s="100" t="n">
         <v>77</v>
       </c>
     </row>
@@ -5218,40 +5314,40 @@
       <c r="A102" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B102" s="86" t="n">
+      <c r="B102" s="101" t="n">
         <v>14.4</v>
       </c>
-      <c r="C102" s="86" t="n">
+      <c r="C102" s="101" t="n">
         <v>0.48</v>
       </c>
-      <c r="D102" s="86" t="n">
+      <c r="D102" s="101" t="n">
         <v>16.9</v>
       </c>
-      <c r="E102" s="86" t="n">
+      <c r="E102" s="101" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F102" s="86" t="n">
+      <c r="F102" s="101" t="n">
         <v>1110</v>
       </c>
-      <c r="G102" s="86" t="n">
+      <c r="G102" s="101" t="n">
         <v>550</v>
       </c>
-      <c r="H102" s="86" t="n">
+      <c r="H102" s="101" t="n">
         <v>130</v>
       </c>
-      <c r="I102" s="86" t="n">
+      <c r="I102" s="101" t="n">
         <v>5.47</v>
       </c>
-      <c r="J102" s="86" t="n">
+      <c r="J102" s="101" t="n">
         <v>30</v>
       </c>
-      <c r="K102" s="86" t="n">
+      <c r="K102" s="101" t="n">
         <v>212</v>
       </c>
-      <c r="L102" s="86" t="n">
+      <c r="L102" s="101" t="n">
         <v>111</v>
       </c>
-      <c r="M102" s="86" t="n">
+      <c r="M102" s="101" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5259,40 +5355,40 @@
       <c r="A103" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B103" s="87" t="n">
+      <c r="B103" s="102" t="n">
         <v>14.4</v>
       </c>
-      <c r="C103" s="87" t="n">
+      <c r="C103" s="102" t="n">
         <v>0.48</v>
       </c>
-      <c r="D103" s="87" t="n">
+      <c r="D103" s="102" t="n">
         <v>16.8</v>
       </c>
-      <c r="E103" s="87" t="n">
+      <c r="E103" s="102" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F103" s="87" t="n">
+      <c r="F103" s="102" t="n">
         <v>1060</v>
       </c>
-      <c r="G103" s="87" t="n">
+      <c r="G103" s="102" t="n">
         <v>520</v>
       </c>
-      <c r="H103" s="87" t="n">
+      <c r="H103" s="102" t="n">
         <v>130</v>
       </c>
-      <c r="I103" s="87" t="n">
+      <c r="I103" s="102" t="n">
         <v>3.74</v>
       </c>
-      <c r="J103" s="87" t="n">
+      <c r="J103" s="102" t="n">
         <v>30</v>
       </c>
-      <c r="K103" s="87" t="n">
+      <c r="K103" s="102" t="n">
         <v>81</v>
       </c>
-      <c r="L103" s="87" t="n">
+      <c r="L103" s="102" t="n">
         <v>111</v>
       </c>
-      <c r="M103" s="87" t="n">
+      <c r="M103" s="102" t="n">
         <v>76</v>
       </c>
     </row>
@@ -5300,40 +5396,40 @@
       <c r="A104" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B104" s="88" t="n">
+      <c r="B104" s="103" t="n">
         <v>14.4</v>
       </c>
-      <c r="C104" s="88" t="n">
+      <c r="C104" s="103" t="n">
         <v>0.48</v>
       </c>
-      <c r="D104" s="88" t="n">
+      <c r="D104" s="103" t="n">
         <v>16.9</v>
       </c>
-      <c r="E104" s="88" t="n">
+      <c r="E104" s="103" t="n">
         <v>8.4</v>
       </c>
-      <c r="F104" s="88" t="n">
+      <c r="F104" s="103" t="n">
         <v>1440</v>
       </c>
-      <c r="G104" s="88" t="n">
+      <c r="G104" s="103" t="n">
         <v>710</v>
       </c>
-      <c r="H104" s="88" t="n">
+      <c r="H104" s="103" t="n">
         <v>64</v>
       </c>
-      <c r="I104" s="88" t="n">
+      <c r="I104" s="103" t="n">
         <v>5.11</v>
       </c>
-      <c r="J104" s="88" t="n">
+      <c r="J104" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="K104" s="88" t="n">
+      <c r="K104" s="103" t="n">
         <v>23.6</v>
       </c>
-      <c r="L104" s="88" t="n">
+      <c r="L104" s="103" t="n">
         <v>140</v>
       </c>
-      <c r="M104" s="88" t="n">
+      <c r="M104" s="103" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5341,40 +5437,40 @@
       <c r="A105" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B105" s="89" t="n">
+      <c r="B105" s="104" t="n">
         <v>14.4</v>
       </c>
-      <c r="C105" s="89" t="n">
+      <c r="C105" s="104" t="n">
         <v>0.48</v>
       </c>
-      <c r="D105" s="89" t="n">
+      <c r="D105" s="104" t="n">
         <v>16.9</v>
       </c>
-      <c r="E105" s="89" t="n">
+      <c r="E105" s="104" t="n">
         <v>8.4</v>
       </c>
-      <c r="F105" s="89" t="n">
+      <c r="F105" s="104" t="n">
         <v>1400</v>
       </c>
-      <c r="G105" s="89" t="n">
+      <c r="G105" s="104" t="n">
         <v>690</v>
       </c>
-      <c r="H105" s="89" t="n">
+      <c r="H105" s="104" t="n">
         <v>64</v>
       </c>
-      <c r="I105" s="89" t="n">
+      <c r="I105" s="104" t="n">
         <v>4.62</v>
       </c>
-      <c r="J105" s="89" t="n">
+      <c r="J105" s="104" t="n">
         <v>30</v>
       </c>
-      <c r="K105" s="89" t="n">
+      <c r="K105" s="104" t="n">
         <v>14.1</v>
       </c>
-      <c r="L105" s="89" t="n">
+      <c r="L105" s="104" t="n">
         <v>140</v>
       </c>
-      <c r="M105" s="89" t="n">
+      <c r="M105" s="104" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5382,40 +5478,40 @@
       <c r="A106" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B106" s="90" t="n">
+      <c r="B106" s="105" t="n">
         <v>14.4</v>
       </c>
-      <c r="C106" s="90" t="n">
+      <c r="C106" s="105" t="n">
         <v>0.48</v>
       </c>
-      <c r="D106" s="90" t="n">
+      <c r="D106" s="105" t="n">
         <v>16.9</v>
       </c>
-      <c r="E106" s="90" t="n">
+      <c r="E106" s="105" t="n">
         <v>8.4</v>
       </c>
-      <c r="F106" s="90" t="n">
+      <c r="F106" s="105" t="n">
         <v>1200</v>
       </c>
-      <c r="G106" s="90" t="n">
+      <c r="G106" s="105" t="n">
         <v>590</v>
       </c>
-      <c r="H106" s="90" t="n">
+      <c r="H106" s="105" t="n">
         <v>70</v>
       </c>
-      <c r="I106" s="90" t="n">
+      <c r="I106" s="105" t="n">
         <v>1.73</v>
       </c>
-      <c r="J106" s="90" t="n">
+      <c r="J106" s="105" t="n">
         <v>65</v>
       </c>
-      <c r="K106" s="90" t="n">
+      <c r="K106" s="105" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="L106" s="90" t="n">
+      <c r="L106" s="105" t="n">
         <v>111</v>
       </c>
-      <c r="M106" s="90" t="n">
+      <c r="M106" s="105" t="n">
         <v>85</v>
       </c>
     </row>
@@ -5423,40 +5519,40 @@
       <c r="A107" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B107" s="91" t="n">
+      <c r="B107" s="106" t="n">
         <v>14.4</v>
       </c>
-      <c r="C107" s="91" t="n">
+      <c r="C107" s="106" t="n">
         <v>0.48</v>
       </c>
-      <c r="D107" s="91" t="n">
+      <c r="D107" s="106" t="n">
         <v>16.9</v>
       </c>
-      <c r="E107" s="91" t="n">
+      <c r="E107" s="106" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F107" s="91" t="n">
+      <c r="F107" s="106" t="n">
         <v>1180</v>
       </c>
-      <c r="G107" s="91" t="n">
+      <c r="G107" s="106" t="n">
         <v>580</v>
       </c>
-      <c r="H107" s="91" t="n">
+      <c r="H107" s="106" t="n">
         <v>70</v>
       </c>
-      <c r="I107" s="91" t="n">
+      <c r="I107" s="106" t="n">
         <v>1.33</v>
       </c>
-      <c r="J107" s="91" t="n">
+      <c r="J107" s="106" t="n">
         <v>65</v>
       </c>
-      <c r="K107" s="91" t="n">
+      <c r="K107" s="106" t="n">
         <v>89.2</v>
       </c>
-      <c r="L107" s="91" t="n">
+      <c r="L107" s="106" t="n">
         <v>111</v>
       </c>
-      <c r="M107" s="91" t="n">
+      <c r="M107" s="106" t="n">
         <v>85</v>
       </c>
     </row>
@@ -5464,40 +5560,40 @@
       <c r="A108" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B108" s="92" t="n">
+      <c r="B108" s="107" t="n">
         <v>14.4</v>
       </c>
-      <c r="C108" s="92" t="n">
+      <c r="C108" s="107" t="n">
         <v>0.48</v>
       </c>
-      <c r="D108" s="92" t="n">
+      <c r="D108" s="107" t="n">
         <v>16.9</v>
       </c>
-      <c r="E108" s="92" t="n">
+      <c r="E108" s="107" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="F108" s="92" t="n">
+      <c r="F108" s="107" t="n">
         <v>1120</v>
       </c>
-      <c r="G108" s="92" t="n">
+      <c r="G108" s="107" t="n">
         <v>550</v>
       </c>
-      <c r="H108" s="92" t="n">
+      <c r="H108" s="107" t="n">
         <v>24</v>
       </c>
-      <c r="I108" s="92" t="n">
+      <c r="I108" s="107" t="n">
         <v>3.34</v>
       </c>
-      <c r="J108" s="92" t="n">
+      <c r="J108" s="107" t="n">
         <v>20</v>
       </c>
-      <c r="K108" s="92" t="n">
+      <c r="K108" s="107" t="n">
         <v>2.95</v>
       </c>
-      <c r="L108" s="92" t="n">
+      <c r="L108" s="107" t="n">
         <v>211</v>
       </c>
-      <c r="M108" s="92" t="n">
+      <c r="M108" s="107" t="n">
         <v>64</v>
       </c>
     </row>
@@ -5505,40 +5601,40 @@
       <c r="A109" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B109" s="93" t="n">
+      <c r="B109" s="108" t="n">
         <v>14.4</v>
       </c>
-      <c r="C109" s="93" t="n">
+      <c r="C109" s="108" t="n">
         <v>0.48</v>
       </c>
-      <c r="D109" s="93" t="n">
+      <c r="D109" s="108" t="n">
         <v>16.8</v>
       </c>
-      <c r="E109" s="93" t="n">
+      <c r="E109" s="108" t="n">
         <v>8.1</v>
       </c>
-      <c r="F109" s="93" t="n">
+      <c r="F109" s="108" t="n">
         <v>1140</v>
       </c>
-      <c r="G109" s="93" t="n">
+      <c r="G109" s="108" t="n">
         <v>560</v>
       </c>
-      <c r="H109" s="93" t="n">
+      <c r="H109" s="108" t="n">
         <v>24</v>
       </c>
-      <c r="I109" s="93" t="n">
+      <c r="I109" s="108" t="n">
         <v>2.82</v>
       </c>
-      <c r="J109" s="93" t="n">
+      <c r="J109" s="108" t="n">
         <v>20</v>
       </c>
-      <c r="K109" s="93" t="n">
+      <c r="K109" s="108" t="n">
         <v>3.63</v>
       </c>
-      <c r="L109" s="93" t="n">
+      <c r="L109" s="108" t="n">
         <v>211</v>
       </c>
-      <c r="M109" s="93" t="n">
+      <c r="M109" s="108" t="n">
         <v>64</v>
       </c>
     </row>
@@ -5546,40 +5642,40 @@
       <c r="A110" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B110" s="32" t="n">
+      <c r="B110" s="109" t="n">
         <v>14.4</v>
       </c>
-      <c r="C110" s="32" t="n">
+      <c r="C110" s="109" t="n">
         <v>0.48</v>
       </c>
-      <c r="D110" s="32" t="n">
+      <c r="D110" s="109" t="n">
         <v>17</v>
       </c>
-      <c r="E110" s="32" t="n">
+      <c r="E110" s="109" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F110" s="32" t="n">
+      <c r="F110" s="109" t="n">
         <v>1340</v>
       </c>
-      <c r="G110" s="32" t="n">
+      <c r="G110" s="109" t="n">
         <v>660</v>
       </c>
-      <c r="H110" s="32" t="n">
+      <c r="H110" s="109" t="n">
         <v>50</v>
       </c>
-      <c r="I110" s="32" t="n">
+      <c r="I110" s="109" t="n">
         <v>1.39</v>
       </c>
-      <c r="J110" s="32" t="n">
+      <c r="J110" s="109" t="n">
         <v>55</v>
       </c>
-      <c r="K110" s="32" t="n">
+      <c r="K110" s="109" t="n">
         <v>56.5</v>
       </c>
-      <c r="L110" s="32" t="n">
+      <c r="L110" s="109" t="n">
         <v>135</v>
       </c>
-      <c r="M110" s="32" t="n">
+      <c r="M110" s="109" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5587,40 +5683,40 @@
       <c r="A111" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B111" s="94" t="n">
+      <c r="B111" s="110" t="n">
         <v>14.4</v>
       </c>
-      <c r="C111" s="94" t="n">
+      <c r="C111" s="110" t="n">
         <v>0.48</v>
       </c>
-      <c r="D111" s="94" t="n">
+      <c r="D111" s="110" t="n">
         <v>17</v>
       </c>
-      <c r="E111" s="94" t="n">
+      <c r="E111" s="110" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F111" s="94" t="n">
+      <c r="F111" s="110" t="n">
         <v>1350</v>
       </c>
-      <c r="G111" s="94" t="n">
+      <c r="G111" s="110" t="n">
         <v>660</v>
       </c>
-      <c r="H111" s="94" t="n">
+      <c r="H111" s="110" t="n">
         <v>50</v>
       </c>
-      <c r="I111" s="94" t="n">
+      <c r="I111" s="110" t="n">
         <v>1.05</v>
       </c>
-      <c r="J111" s="94" t="n">
+      <c r="J111" s="110" t="n">
         <v>55</v>
       </c>
-      <c r="K111" s="94" t="n">
+      <c r="K111" s="110" t="n">
         <v>118</v>
       </c>
-      <c r="L111" s="94" t="n">
+      <c r="L111" s="110" t="n">
         <v>135</v>
       </c>
-      <c r="M111" s="94" t="n">
+      <c r="M111" s="110" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5628,40 +5724,40 @@
       <c r="A112" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B112" s="95" t="n">
+      <c r="B112" s="111" t="n">
         <v>12.8</v>
       </c>
-      <c r="C112" s="95" t="n">
+      <c r="C112" s="111" t="n">
         <v>0.57</v>
       </c>
-      <c r="D112" s="95" t="n">
+      <c r="D112" s="111" t="n">
         <v>15.2</v>
       </c>
-      <c r="E112" s="95" t="n">
+      <c r="E112" s="111" t="n">
         <v>8.6</v>
       </c>
-      <c r="F112" s="95" t="n">
+      <c r="F112" s="111" t="n">
         <v>940</v>
       </c>
-      <c r="G112" s="95" t="n">
+      <c r="G112" s="111" t="n">
         <v>460</v>
       </c>
-      <c r="H112" s="95" t="n">
+      <c r="H112" s="111" t="n">
         <v>60</v>
       </c>
-      <c r="I112" s="95" t="n">
+      <c r="I112" s="111" t="n">
         <v>5.64</v>
       </c>
-      <c r="J112" s="95" t="n">
+      <c r="J112" s="111" t="n">
         <v>55</v>
       </c>
-      <c r="K112" s="95" t="n">
+      <c r="K112" s="111" t="n">
         <v>177</v>
       </c>
-      <c r="L112" s="95" t="n">
+      <c r="L112" s="111" t="n">
         <v>117</v>
       </c>
-      <c r="M112" s="95" t="n">
+      <c r="M112" s="111" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5669,40 +5765,40 @@
       <c r="A113" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B113" s="96" t="n">
+      <c r="B113" s="112" t="n">
         <v>12.8</v>
       </c>
-      <c r="C113" s="96" t="n">
+      <c r="C113" s="112" t="n">
         <v>0.57</v>
       </c>
-      <c r="D113" s="96" t="n">
+      <c r="D113" s="112" t="n">
         <v>15.3</v>
       </c>
-      <c r="E113" s="96" t="n">
+      <c r="E113" s="112" t="n">
         <v>8.4</v>
       </c>
-      <c r="F113" s="96" t="n">
+      <c r="F113" s="112" t="n">
         <v>930</v>
       </c>
-      <c r="G113" s="96" t="n">
+      <c r="G113" s="112" t="n">
         <v>460</v>
       </c>
-      <c r="H113" s="96" t="n">
+      <c r="H113" s="112" t="n">
         <v>60</v>
       </c>
-      <c r="I113" s="96" t="n">
+      <c r="I113" s="112" t="n">
         <v>3.28</v>
       </c>
-      <c r="J113" s="96" t="n">
+      <c r="J113" s="112" t="n">
         <v>55</v>
       </c>
-      <c r="K113" s="96" t="n">
+      <c r="K113" s="112" t="n">
         <v>128</v>
       </c>
-      <c r="L113" s="96" t="n">
+      <c r="L113" s="112" t="n">
         <v>117</v>
       </c>
-      <c r="M113" s="96" t="n">
+      <c r="M113" s="112" t="n">
         <v>69</v>
       </c>
     </row>
@@ -5710,40 +5806,40 @@
       <c r="A114" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B114" s="97" t="n">
+      <c r="B114" s="113" t="n">
         <v>12.8</v>
       </c>
-      <c r="C114" s="97" t="n">
+      <c r="C114" s="113" t="n">
         <v>0.57</v>
       </c>
-      <c r="D114" s="97" t="n">
+      <c r="D114" s="113" t="n">
         <v>15.2</v>
       </c>
-      <c r="E114" s="97" t="n">
+      <c r="E114" s="113" t="n">
         <v>8.4</v>
       </c>
-      <c r="F114" s="97" t="n">
+      <c r="F114" s="113" t="n">
         <v>1300</v>
       </c>
-      <c r="G114" s="97" t="n">
+      <c r="G114" s="113" t="n">
         <v>640</v>
       </c>
-      <c r="H114" s="97" t="n">
+      <c r="H114" s="113" t="n">
         <v>80</v>
       </c>
-      <c r="I114" s="97" t="n">
+      <c r="I114" s="113" t="n">
         <v>7.93</v>
       </c>
-      <c r="J114" s="97" t="n">
+      <c r="J114" s="113" t="n">
         <v>35</v>
       </c>
-      <c r="K114" s="97" t="n">
+      <c r="K114" s="113" t="n">
         <v>33.4</v>
       </c>
-      <c r="L114" s="97" t="n">
+      <c r="L114" s="113" t="n">
         <v>263</v>
       </c>
-      <c r="M114" s="97" t="n">
+      <c r="M114" s="113" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5751,40 +5847,40 @@
       <c r="A115" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B115" s="98" t="n">
+      <c r="B115" s="114" t="n">
         <v>12.8</v>
       </c>
-      <c r="C115" s="98" t="n">
+      <c r="C115" s="114" t="n">
         <v>0.57</v>
       </c>
-      <c r="D115" s="98" t="n">
+      <c r="D115" s="114" t="n">
         <v>15.2</v>
       </c>
-      <c r="E115" s="98" t="n">
+      <c r="E115" s="114" t="n">
         <v>8.5</v>
       </c>
-      <c r="F115" s="98" t="n">
+      <c r="F115" s="114" t="n">
         <v>1320</v>
       </c>
-      <c r="G115" s="98" t="n">
+      <c r="G115" s="114" t="n">
         <v>650</v>
       </c>
-      <c r="H115" s="98" t="n">
+      <c r="H115" s="114" t="n">
         <v>80</v>
       </c>
-      <c r="I115" s="98" t="n">
+      <c r="I115" s="114" t="n">
         <v>7.9</v>
       </c>
-      <c r="J115" s="98" t="n">
+      <c r="J115" s="114" t="n">
         <v>35</v>
       </c>
-      <c r="K115" s="98" t="n">
+      <c r="K115" s="114" t="n">
         <v>31.7</v>
       </c>
-      <c r="L115" s="98" t="n">
+      <c r="L115" s="114" t="n">
         <v>263</v>
       </c>
-      <c r="M115" s="98" t="n">
+      <c r="M115" s="114" t="n">
         <v>104</v>
       </c>
     </row>
@@ -5792,40 +5888,40 @@
       <c r="A116" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B116" s="99" t="n">
+      <c r="B116" s="115" t="n">
         <v>12.8</v>
       </c>
-      <c r="C116" s="99" t="n">
+      <c r="C116" s="115" t="n">
         <v>0.57</v>
       </c>
-      <c r="D116" s="99" t="n">
+      <c r="D116" s="115" t="n">
         <v>15.1</v>
       </c>
-      <c r="E116" s="99" t="n">
+      <c r="E116" s="115" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F116" s="99" t="n">
+      <c r="F116" s="115" t="n">
         <v>1070</v>
       </c>
-      <c r="G116" s="99" t="n">
+      <c r="G116" s="115" t="n">
         <v>530</v>
       </c>
-      <c r="H116" s="99" t="n">
+      <c r="H116" s="115" t="n">
         <v>46</v>
       </c>
-      <c r="I116" s="99" t="n">
+      <c r="I116" s="115" t="n">
         <v>2.9</v>
       </c>
-      <c r="J116" s="99" t="n">
+      <c r="J116" s="115" t="n">
         <v>65</v>
       </c>
-      <c r="K116" s="99" t="n">
+      <c r="K116" s="115" t="n">
         <v>117</v>
       </c>
-      <c r="L116" s="99" t="n">
+      <c r="L116" s="115" t="n">
         <v>176</v>
       </c>
-      <c r="M116" s="99" t="n">
+      <c r="M116" s="115" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5833,40 +5929,40 @@
       <c r="A117" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B117" s="100" t="n">
+      <c r="B117" s="116" t="n">
         <v>12.8</v>
       </c>
-      <c r="C117" s="100" t="n">
+      <c r="C117" s="116" t="n">
         <v>0.57</v>
       </c>
-      <c r="D117" s="100" t="n">
+      <c r="D117" s="116" t="n">
         <v>15.2</v>
       </c>
-      <c r="E117" s="100" t="n">
+      <c r="E117" s="116" t="n">
         <v>8.4</v>
       </c>
-      <c r="F117" s="100" t="n">
+      <c r="F117" s="116" t="n">
         <v>1080</v>
       </c>
-      <c r="G117" s="100" t="n">
+      <c r="G117" s="116" t="n">
         <v>530</v>
       </c>
-      <c r="H117" s="100" t="n">
+      <c r="H117" s="116" t="n">
         <v>46</v>
       </c>
-      <c r="I117" s="100" t="n">
+      <c r="I117" s="116" t="n">
         <v>3.18</v>
       </c>
-      <c r="J117" s="100" t="n">
+      <c r="J117" s="116" t="n">
         <v>65</v>
       </c>
-      <c r="K117" s="100" t="n">
+      <c r="K117" s="116" t="n">
         <v>113</v>
       </c>
-      <c r="L117" s="100" t="n">
+      <c r="L117" s="116" t="n">
         <v>176</v>
       </c>
-      <c r="M117" s="100" t="n">
+      <c r="M117" s="116" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5874,40 +5970,40 @@
       <c r="A118" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B118" s="101" t="n">
+      <c r="B118" s="117" t="n">
         <v>12.8</v>
       </c>
-      <c r="C118" s="101" t="n">
+      <c r="C118" s="117" t="n">
         <v>0.57</v>
       </c>
-      <c r="D118" s="101" t="n">
+      <c r="D118" s="117" t="n">
         <v>15.3</v>
       </c>
-      <c r="E118" s="101" t="n">
+      <c r="E118" s="117" t="n">
         <v>8</v>
       </c>
-      <c r="F118" s="101" t="n">
+      <c r="F118" s="117" t="n">
         <v>1110</v>
       </c>
-      <c r="G118" s="101" t="n">
+      <c r="G118" s="117" t="n">
         <v>550</v>
       </c>
-      <c r="H118" s="101" t="n">
+      <c r="H118" s="117" t="n">
         <v>18</v>
       </c>
-      <c r="I118" s="101" t="n">
+      <c r="I118" s="117" t="n">
         <v>4.18</v>
       </c>
-      <c r="J118" s="101" t="n">
+      <c r="J118" s="117" t="n">
         <v>25</v>
       </c>
-      <c r="K118" s="101" t="n">
+      <c r="K118" s="117" t="n">
         <v>5.04</v>
       </c>
-      <c r="L118" s="101" t="n">
+      <c r="L118" s="117" t="n">
         <v>316</v>
       </c>
-      <c r="M118" s="101" t="n">
+      <c r="M118" s="117" t="n">
         <v>66</v>
       </c>
     </row>
@@ -5915,40 +6011,40 @@
       <c r="A119" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B119" s="102" t="n">
+      <c r="B119" s="118" t="n">
         <v>12.8</v>
       </c>
-      <c r="C119" s="102" t="n">
+      <c r="C119" s="118" t="n">
         <v>0.57</v>
       </c>
-      <c r="D119" s="102" t="n">
+      <c r="D119" s="118" t="n">
         <v>15.3</v>
       </c>
-      <c r="E119" s="102" t="n">
+      <c r="E119" s="118" t="n">
         <v>8.1</v>
       </c>
-      <c r="F119" s="102" t="n">
+      <c r="F119" s="118" t="n">
         <v>1080</v>
       </c>
-      <c r="G119" s="102" t="n">
+      <c r="G119" s="118" t="n">
         <v>550</v>
       </c>
-      <c r="H119" s="102" t="n">
+      <c r="H119" s="118" t="n">
         <v>18</v>
       </c>
-      <c r="I119" s="102" t="n">
+      <c r="I119" s="118" t="n">
         <v>4.23</v>
       </c>
-      <c r="J119" s="102" t="n">
+      <c r="J119" s="118" t="n">
         <v>25</v>
       </c>
-      <c r="K119" s="102" t="n">
+      <c r="K119" s="118" t="n">
         <v>5.69</v>
       </c>
-      <c r="L119" s="102" t="n">
+      <c r="L119" s="118" t="n">
         <v>316</v>
       </c>
-      <c r="M119" s="102" t="n">
+      <c r="M119" s="118" t="n">
         <v>66</v>
       </c>
     </row>
@@ -5956,40 +6052,40 @@
       <c r="A120" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B120" s="103" t="n">
+      <c r="B120" s="119" t="n">
         <v>12.8</v>
       </c>
-      <c r="C120" s="103" t="n">
+      <c r="C120" s="119" t="n">
         <v>0.57</v>
       </c>
-      <c r="D120" s="103" t="n">
+      <c r="D120" s="119" t="n">
         <v>15.4</v>
       </c>
-      <c r="E120" s="103" t="n">
+      <c r="E120" s="119" t="n">
         <v>8.4</v>
       </c>
-      <c r="F120" s="103" t="n">
+      <c r="F120" s="119" t="n">
         <v>1050</v>
       </c>
-      <c r="G120" s="103" t="n">
+      <c r="G120" s="119" t="n">
         <v>520</v>
       </c>
-      <c r="H120" s="103" t="n">
+      <c r="H120" s="119" t="n">
         <v>44</v>
       </c>
-      <c r="I120" s="103" t="n">
+      <c r="I120" s="119" t="n">
         <v>1.96</v>
       </c>
-      <c r="J120" s="103" t="n">
+      <c r="J120" s="119" t="n">
         <v>70</v>
       </c>
-      <c r="K120" s="103" t="n">
+      <c r="K120" s="119" t="n">
         <v>113</v>
       </c>
-      <c r="L120" s="103" t="n">
+      <c r="L120" s="119" t="n">
         <v>146</v>
       </c>
-      <c r="M120" s="103" t="n">
+      <c r="M120" s="119" t="n">
         <v>82</v>
       </c>
     </row>
@@ -5997,40 +6093,40 @@
       <c r="A121" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B121" s="104" t="n">
+      <c r="B121" s="120" t="n">
         <v>12.8</v>
       </c>
-      <c r="C121" s="104" t="n">
+      <c r="C121" s="120" t="n">
         <v>0.57</v>
       </c>
-      <c r="D121" s="104" t="n">
+      <c r="D121" s="120" t="n">
         <v>15.4</v>
       </c>
-      <c r="E121" s="104" t="n">
+      <c r="E121" s="120" t="n">
         <v>8.4</v>
       </c>
-      <c r="F121" s="104" t="n">
+      <c r="F121" s="120" t="n">
         <v>1070</v>
       </c>
-      <c r="G121" s="104" t="n">
+      <c r="G121" s="120" t="n">
         <v>530</v>
       </c>
-      <c r="H121" s="104" t="n">
+      <c r="H121" s="120" t="n">
         <v>44</v>
       </c>
-      <c r="I121" s="104" t="n">
+      <c r="I121" s="120" t="n">
         <v>1.67</v>
       </c>
-      <c r="J121" s="104" t="n">
+      <c r="J121" s="120" t="n">
         <v>70</v>
       </c>
-      <c r="K121" s="104" t="n">
+      <c r="K121" s="120" t="n">
         <v>133</v>
       </c>
-      <c r="L121" s="104" t="n">
+      <c r="L121" s="120" t="n">
         <v>146</v>
       </c>
-      <c r="M121" s="104" t="n">
+      <c r="M121" s="120" t="n">
         <v>82</v>
       </c>
     </row>
